--- a/input/Studies/C3/C3_Prototypical_Sites/P3_2stages_VRU.xlsx
+++ b/input/Studies/C3/C3_Prototypical_Sites/P3_2stages_VRU.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11207"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wmollel\Documents\MEET2\input\Studies\C3\C3_Prototypical_Sites\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kayarn/sources/xpower/csu/MAES/input/Studies/C3/C3_Prototypical_Sites/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7974B0F-B94D-40C9-9D70-843A4CEC99C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A13B2559-9DED-4B4B-BC1F-962A7541722E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="925" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4480" yWindow="500" windowWidth="31360" windowHeight="21900" tabRatio="925" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Global Simulation Parameters" sheetId="1" r:id="rId1"/>
@@ -1407,13 +1407,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B6"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="33.5703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="64.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="33.5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="64.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1421,7 +1421,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -1429,25 +1429,25 @@
         <v>365</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>3</v>
       </c>
       <c r="B3">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>204</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>205</v>
       </c>
@@ -1464,12 +1464,12 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
   <dimension ref="A1:B9"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="2" width="19.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="2" width="19.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>22</v>
       </c>
@@ -1477,7 +1477,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>24</v>
       </c>
@@ -1485,7 +1485,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>119</v>
       </c>
@@ -1493,7 +1493,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>160</v>
       </c>
@@ -1501,7 +1501,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>96</v>
       </c>
@@ -1509,7 +1509,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>19</v>
       </c>
@@ -1517,7 +1517,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>26</v>
       </c>
@@ -1525,7 +1525,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>25</v>
       </c>
@@ -1533,7 +1533,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>41</v>
       </c>
@@ -1549,16 +1549,16 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:E2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="12.85546875" customWidth="1"/>
-    <col min="2" max="2" width="7.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.7109375" customWidth="1"/>
+    <col min="1" max="1" width="12.83203125" customWidth="1"/>
+    <col min="2" max="2" width="7.83203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.6640625" customWidth="1"/>
     <col min="4" max="4" width="64" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="20" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" s="12" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" s="12" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A1" s="11" t="s">
         <v>4</v>
       </c>
@@ -1575,7 +1575,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>100</v>
       </c>
@@ -1600,14 +1600,14 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D2690304-5371-4DEF-8D7E-371EB1C22F96}">
   <dimension ref="A1:S9"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="15.42578125" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="19.85546875" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="63.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.5" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="19.83203125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="63.83203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" s="20" customFormat="1" ht="90" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:19" s="20" customFormat="1" ht="80" x14ac:dyDescent="0.2">
       <c r="A1" s="20" t="s">
         <v>4</v>
       </c>
@@ -1666,7 +1666,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>100</v>
       </c>
@@ -1725,7 +1725,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="3" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>100</v>
       </c>
@@ -1784,7 +1784,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="4" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>100</v>
       </c>
@@ -1843,7 +1843,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>100</v>
       </c>
@@ -1902,7 +1902,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>100</v>
       </c>
@@ -1961,7 +1961,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>100</v>
       </c>
@@ -2020,7 +2020,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>100</v>
       </c>
@@ -2079,7 +2079,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>100</v>
       </c>
@@ -2146,17 +2146,17 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:P19"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="5" width="15.7109375" customWidth="1"/>
-    <col min="6" max="13" width="15.7109375" style="4" customWidth="1"/>
-    <col min="14" max="14" width="24.42578125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="47.140625" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="15.7109375" customWidth="1"/>
-    <col min="17" max="17" width="18.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="5" width="15.6640625" customWidth="1"/>
+    <col min="6" max="13" width="15.6640625" style="4" customWidth="1"/>
+    <col min="14" max="14" width="24.5" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="47.1640625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="15.6640625" customWidth="1"/>
+    <col min="17" max="17" width="18.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" s="3" customFormat="1" ht="60" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:16" s="3" customFormat="1" ht="48" x14ac:dyDescent="0.2">
       <c r="A1" s="16" t="s">
         <v>4</v>
       </c>
@@ -2206,7 +2206,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>100</v>
       </c>
@@ -2256,7 +2256,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>100</v>
       </c>
@@ -2306,7 +2306,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>100</v>
       </c>
@@ -2356,7 +2356,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>100</v>
       </c>
@@ -2406,7 +2406,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>100</v>
       </c>
@@ -2456,7 +2456,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>100</v>
       </c>
@@ -2506,7 +2506,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>100</v>
       </c>
@@ -2556,7 +2556,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>100</v>
       </c>
@@ -2606,7 +2606,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
       <c r="F10"/>
       <c r="G10"/>
       <c r="H10"/>
@@ -2616,7 +2616,7 @@
       <c r="L10"/>
       <c r="M10"/>
     </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>100</v>
       </c>
@@ -2666,7 +2666,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>100</v>
       </c>
@@ -2716,7 +2716,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>100</v>
       </c>
@@ -2766,7 +2766,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>100</v>
       </c>
@@ -2816,7 +2816,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>100</v>
       </c>
@@ -2866,7 +2866,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>100</v>
       </c>
@@ -2916,7 +2916,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="17" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>100</v>
       </c>
@@ -2966,7 +2966,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="18" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>100</v>
       </c>
@@ -3016,7 +3016,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="19" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:16" x14ac:dyDescent="0.2">
       <c r="F19"/>
       <c r="G19"/>
       <c r="H19"/>
@@ -3033,26 +3033,26 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1:U16"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="16" bestFit="1" customWidth="1"/>
     <col min="3" max="5" width="12" customWidth="1"/>
-    <col min="6" max="6" width="8.5703125" style="4" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="19.85546875" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="13.85546875" customWidth="1"/>
-    <col min="11" max="12" width="26.42578125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="8.5" style="4" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.83203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="19.83203125" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="13.83203125" customWidth="1"/>
+    <col min="11" max="12" width="26.5" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="10" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="12.7109375" bestFit="1" customWidth="1"/>
-    <col min="15" max="17" width="17.85546875" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="18.140625" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="18.28515625" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="18.140625" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="12.6640625" bestFit="1" customWidth="1"/>
+    <col min="15" max="17" width="17.83203125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="18.1640625" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="18.33203125" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="18.1640625" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="9.83203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" s="12" customFormat="1" ht="75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:21" s="12" customFormat="1" ht="80" x14ac:dyDescent="0.2">
       <c r="A1" s="11" t="s">
         <v>4</v>
       </c>
@@ -3117,7 +3117,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="2" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>100</v>
       </c>
@@ -3182,34 +3182,34 @@
         <v>200</v>
       </c>
     </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:21" x14ac:dyDescent="0.2">
       <c r="F7"/>
     </row>
-    <row r="8" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:21" x14ac:dyDescent="0.2">
       <c r="F8"/>
     </row>
-    <row r="9" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:21" x14ac:dyDescent="0.2">
       <c r="F9"/>
     </row>
-    <row r="10" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:21" x14ac:dyDescent="0.2">
       <c r="F10"/>
     </row>
-    <row r="11" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:21" x14ac:dyDescent="0.2">
       <c r="F11"/>
     </row>
-    <row r="12" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:21" x14ac:dyDescent="0.2">
       <c r="F12"/>
     </row>
-    <row r="13" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:21" x14ac:dyDescent="0.2">
       <c r="F13"/>
     </row>
-    <row r="14" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:21" x14ac:dyDescent="0.2">
       <c r="F14"/>
     </row>
-    <row r="15" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:21" x14ac:dyDescent="0.2">
       <c r="F15"/>
     </row>
-    <row r="16" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:21" x14ac:dyDescent="0.2">
       <c r="F16"/>
     </row>
   </sheetData>
@@ -3221,42 +3221,40 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
   <dimension ref="A1:AF3"/>
-  <sheetFormatPr defaultColWidth="66.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="66.6640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="9.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.5" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="16" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="19.85546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.42578125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="17.28515625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.7109375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="17.42578125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="16.28515625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="17.28515625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="13.140625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="16.28515625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="13.85546875" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="15.85546875" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="11.42578125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="11.5703125" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.7109375" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="22.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.83203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.5" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="17.33203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.6640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="17.5" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="16.33203125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="17.33203125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="13.1640625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="16.33203125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="13.83203125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="15.83203125" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="11.5" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.6640625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="22.5" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="12" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="15.85546875" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="16.140625" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="18.5703125" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="18.42578125" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="16.85546875" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="13.28515625" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="18.5703125" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="13.28515625" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="18.5703125" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="12.28515625" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="12.140625" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="63.7109375" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="15.83203125" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="16.1640625" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="18.5" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="16.83203125" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="18.5" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="18.5" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="12.33203125" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="12.1640625" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="63.6640625" bestFit="1" customWidth="1"/>
     <col min="32" max="32" width="14" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:32" s="12" customFormat="1" ht="59.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:32" s="12" customFormat="1" ht="59.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="11" t="s">
         <v>4</v>
       </c>
@@ -3354,7 +3352,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="2" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>100</v>
       </c>
@@ -3452,7 +3450,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="3" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>100</v>
       </c>
@@ -3559,58 +3557,58 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0C00-000000000000}">
   <dimension ref="A1:BB9"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="8.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="7.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.7109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="11.42578125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.7109375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.28515625" customWidth="1"/>
-    <col min="8" max="8" width="11.5703125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.5703125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="9.5703125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="11.5703125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="11.5703125" customWidth="1"/>
-    <col min="13" max="13" width="14.28515625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="16.42578125" style="4" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="8.28515625" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="11.140625" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="9.85546875" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="10.42578125" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="11.28515625" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="11.42578125" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="10.28515625" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="11.42578125" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="13.140625" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.28515625" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.42578125" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="10.7109375" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="10.42578125" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="10.85546875" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="7.1640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="11.5" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.6640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.33203125" customWidth="1"/>
+    <col min="8" max="8" width="11.5" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.5" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="9.5" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="11.5" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="11.5" customWidth="1"/>
+    <col min="13" max="13" width="14.33203125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="16.5" style="4" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="8.33203125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="11.1640625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="9.83203125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="10.5" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="11.33203125" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="11.5" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="10.33203125" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="11.5" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="13.1640625" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.33203125" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.5" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="10.6640625" bestFit="1" customWidth="1"/>
+    <col min="27" max="28" width="10.5" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="10.83203125" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="12.5" bestFit="1" customWidth="1"/>
     <col min="31" max="31" width="15" bestFit="1" customWidth="1"/>
     <col min="32" max="32" width="11" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="15.7109375" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="11.42578125" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="15.6640625" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="11.5" bestFit="1" customWidth="1"/>
     <col min="36" max="36" width="10" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="10.28515625" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="10.33203125" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="9.5" bestFit="1" customWidth="1"/>
     <col min="39" max="39" width="15" customWidth="1"/>
-    <col min="40" max="41" width="13.85546875" bestFit="1" customWidth="1"/>
+    <col min="40" max="41" width="13.83203125" bestFit="1" customWidth="1"/>
     <col min="42" max="42" width="10" bestFit="1" customWidth="1"/>
-    <col min="43" max="43" width="11.7109375" bestFit="1" customWidth="1"/>
-    <col min="44" max="45" width="10.7109375" bestFit="1" customWidth="1"/>
-    <col min="46" max="46" width="9.7109375" bestFit="1" customWidth="1"/>
-    <col min="47" max="47" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="43" max="43" width="11.6640625" bestFit="1" customWidth="1"/>
+    <col min="44" max="45" width="10.6640625" bestFit="1" customWidth="1"/>
+    <col min="46" max="46" width="9.6640625" bestFit="1" customWidth="1"/>
+    <col min="47" max="47" width="17.5" bestFit="1" customWidth="1"/>
     <col min="48" max="49" width="15" bestFit="1" customWidth="1"/>
     <col min="50" max="50" width="14" bestFit="1" customWidth="1"/>
     <col min="51" max="51" width="16" bestFit="1" customWidth="1"/>
-    <col min="52" max="53" width="47.140625" bestFit="1" customWidth="1"/>
-    <col min="54" max="54" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="52" max="53" width="47.1640625" bestFit="1" customWidth="1"/>
+    <col min="54" max="54" width="9.83203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:54" s="18" customFormat="1" ht="63" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:54" s="18" customFormat="1" ht="63" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="16" t="s">
         <v>4</v>
       </c>
@@ -3774,7 +3772,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="2" spans="1:54" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:54" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>100</v>
       </c>
@@ -3937,7 +3935,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="3" spans="1:54" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:54" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>100</v>
       </c>
@@ -4100,7 +4098,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="4" spans="1:54" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:54" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>100</v>
       </c>
@@ -4263,7 +4261,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="5" spans="1:54" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:54" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>100</v>
       </c>
@@ -4426,7 +4424,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="6" spans="1:54" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:54" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>100</v>
       </c>
@@ -4589,7 +4587,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="7" spans="1:54" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:54" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>100</v>
       </c>
@@ -4752,7 +4750,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="8" spans="1:54" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:54" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>100</v>
       </c>
@@ -4915,7 +4913,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="9" spans="1:54" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:54" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>100</v>
       </c>
@@ -5088,18 +5086,18 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A904CBC9-E240-4A6F-BB4B-8DAB1536C2C9}">
   <dimension ref="A1:S3"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="4" max="4" width="12.28515625" customWidth="1"/>
-    <col min="6" max="6" width="10.28515625" customWidth="1"/>
-    <col min="9" max="9" width="11.85546875" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="11.28515625" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="11.28515625" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="47.140625" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.33203125" customWidth="1"/>
+    <col min="6" max="6" width="10.33203125" customWidth="1"/>
+    <col min="9" max="9" width="11.83203125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="11.33203125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="11.33203125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="47.1640625" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="13.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" ht="75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:19" ht="80" x14ac:dyDescent="0.2">
       <c r="A1" s="16" t="s">
         <v>4</v>
       </c>
@@ -5158,7 +5156,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>100</v>
       </c>
@@ -5217,7 +5215,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="3" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>100</v>
       </c>
@@ -5285,18 +5283,18 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{09131FE7-5CF0-4155-B869-9951A97BC4D6}">
   <dimension ref="A1:G130"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="20.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="19.85546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.85546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="19.85546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="16.28515625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="23.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="20.83203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.83203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.83203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="19.83203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="16.33203125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="23.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>7</v>
       </c>
@@ -5319,7 +5317,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>67</v>
       </c>
@@ -5340,7 +5338,7 @@
       </c>
       <c r="G2" s="6"/>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>67</v>
       </c>
@@ -5360,7 +5358,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>67</v>
       </c>
@@ -5380,7 +5378,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>67</v>
       </c>
@@ -5400,7 +5398,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>67</v>
       </c>
@@ -5420,7 +5418,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>67</v>
       </c>
@@ -5440,7 +5438,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>67</v>
       </c>
@@ -5460,7 +5458,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>67</v>
       </c>
@@ -5480,7 +5478,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>67</v>
       </c>
@@ -5500,7 +5498,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>67</v>
       </c>
@@ -5520,7 +5518,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>67</v>
       </c>
@@ -5540,7 +5538,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>67</v>
       </c>
@@ -5560,7 +5558,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>67</v>
       </c>
@@ -5580,7 +5578,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>67</v>
       </c>
@@ -5600,7 +5598,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>67</v>
       </c>
@@ -5620,7 +5618,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>67</v>
       </c>
@@ -5640,7 +5638,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>67</v>
       </c>
@@ -5663,7 +5661,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>67</v>
       </c>
@@ -5686,7 +5684,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>67</v>
       </c>
@@ -5709,7 +5707,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>67</v>
       </c>
@@ -5732,7 +5730,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>67</v>
       </c>
@@ -5755,7 +5753,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>67</v>
       </c>
@@ -5778,7 +5776,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>67</v>
       </c>
@@ -5801,7 +5799,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>67</v>
       </c>
@@ -5824,7 +5822,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>67</v>
       </c>
@@ -5847,7 +5845,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>67</v>
       </c>
@@ -5870,7 +5868,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>67</v>
       </c>
@@ -5893,7 +5891,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>67</v>
       </c>
@@ -5916,7 +5914,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>67</v>
       </c>
@@ -5939,7 +5937,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
         <v>67</v>
       </c>
@@ -5962,7 +5960,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
         <v>67</v>
       </c>
@@ -5985,7 +5983,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
         <v>67</v>
       </c>
@@ -6008,7 +6006,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
         <v>67</v>
       </c>
@@ -6031,7 +6029,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
         <v>67</v>
       </c>
@@ -6054,7 +6052,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
         <v>67</v>
       </c>
@@ -6077,7 +6075,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
         <v>67</v>
       </c>
@@ -6100,7 +6098,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
         <v>67</v>
       </c>
@@ -6123,7 +6121,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
         <v>67</v>
       </c>
@@ -6146,7 +6144,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
         <v>67</v>
       </c>
@@ -6169,7 +6167,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
         <v>67</v>
       </c>
@@ -6192,7 +6190,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
         <v>67</v>
       </c>
@@ -6215,7 +6213,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
         <v>67</v>
       </c>
@@ -6238,7 +6236,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
         <v>67</v>
       </c>
@@ -6261,7 +6259,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
         <v>67</v>
       </c>
@@ -6284,7 +6282,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
         <v>67</v>
       </c>
@@ -6307,7 +6305,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
         <v>67</v>
       </c>
@@ -6330,7 +6328,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
         <v>67</v>
       </c>
@@ -6353,7 +6351,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
         <v>67</v>
       </c>
@@ -6376,7 +6374,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
         <v>67</v>
       </c>
@@ -6399,7 +6397,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
         <v>67</v>
       </c>
@@ -6422,7 +6420,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
         <v>67</v>
       </c>
@@ -6445,7 +6443,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
         <v>67</v>
       </c>
@@ -6468,7 +6466,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
         <v>67</v>
       </c>
@@ -6491,7 +6489,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
         <v>67</v>
       </c>
@@ -6514,7 +6512,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
         <v>67</v>
       </c>
@@ -6537,7 +6535,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
         <v>67</v>
       </c>
@@ -6560,7 +6558,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
         <v>67</v>
       </c>
@@ -6583,7 +6581,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A62" t="s">
         <v>67</v>
       </c>
@@ -6606,7 +6604,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A63" t="s">
         <v>67</v>
       </c>
@@ -6629,7 +6627,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A64" t="s">
         <v>67</v>
       </c>
@@ -6652,7 +6650,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="65" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A65" t="s">
         <v>67</v>
       </c>
@@ -6675,7 +6673,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="66" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A66" t="s">
         <v>67</v>
       </c>
@@ -6698,7 +6696,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="67" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A67" t="s">
         <v>67</v>
       </c>
@@ -6721,7 +6719,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="68" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A68" t="s">
         <v>67</v>
       </c>
@@ -6744,7 +6742,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="69" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A69" t="s">
         <v>67</v>
       </c>
@@ -6767,7 +6765,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="70" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A70" t="s">
         <v>67</v>
       </c>
@@ -6790,7 +6788,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="71" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A71" t="s">
         <v>67</v>
       </c>
@@ -6813,7 +6811,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="72" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A72" t="s">
         <v>67</v>
       </c>
@@ -6836,7 +6834,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="73" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A73" t="s">
         <v>67</v>
       </c>
@@ -6859,7 +6857,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="74" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A74" t="s">
         <v>67</v>
       </c>
@@ -6882,7 +6880,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="75" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A75" t="s">
         <v>67</v>
       </c>
@@ -6905,7 +6903,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="76" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A76" t="s">
         <v>67</v>
       </c>
@@ -6928,7 +6926,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="77" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A77" t="s">
         <v>67</v>
       </c>
@@ -6951,7 +6949,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="78" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A78" t="s">
         <v>67</v>
       </c>
@@ -6974,7 +6972,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="79" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A79" t="s">
         <v>67</v>
       </c>
@@ -6997,7 +6995,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="80" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A80" t="s">
         <v>67</v>
       </c>
@@ -7020,7 +7018,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="81" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A81" t="s">
         <v>67</v>
       </c>
@@ -7043,7 +7041,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="82" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A82" t="s">
         <v>67</v>
       </c>
@@ -7066,7 +7064,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="83" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A83" t="s">
         <v>67</v>
       </c>
@@ -7089,7 +7087,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="84" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A84" t="s">
         <v>67</v>
       </c>
@@ -7112,7 +7110,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="85" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A85" t="s">
         <v>67</v>
       </c>
@@ -7135,7 +7133,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="86" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A86" t="s">
         <v>67</v>
       </c>
@@ -7158,7 +7156,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="87" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A87" t="s">
         <v>67</v>
       </c>
@@ -7181,7 +7179,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="88" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A88" t="s">
         <v>67</v>
       </c>
@@ -7204,7 +7202,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="89" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A89" t="s">
         <v>67</v>
       </c>
@@ -7227,7 +7225,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="90" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A90" t="s">
         <v>67</v>
       </c>
@@ -7250,7 +7248,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="91" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A91" t="s">
         <v>67</v>
       </c>
@@ -7273,7 +7271,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="92" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A92" t="s">
         <v>67</v>
       </c>
@@ -7296,7 +7294,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="94" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A94" t="s">
         <v>67</v>
       </c>
@@ -7319,7 +7317,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="95" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A95" t="s">
         <v>67</v>
       </c>
@@ -7342,7 +7340,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="96" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A96" t="s">
         <v>67</v>
       </c>
@@ -7365,7 +7363,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="97" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A97" t="s">
         <v>67</v>
       </c>
@@ -7388,7 +7386,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="98" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A98" t="s">
         <v>67</v>
       </c>
@@ -7411,7 +7409,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="99" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A99" t="s">
         <v>67</v>
       </c>
@@ -7434,7 +7432,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="100" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A100" t="s">
         <v>67</v>
       </c>
@@ -7457,7 +7455,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="101" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A101" t="s">
         <v>67</v>
       </c>
@@ -7480,7 +7478,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="102" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A102" t="s">
         <v>67</v>
       </c>
@@ -7503,7 +7501,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="103" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A103" t="s">
         <v>67</v>
       </c>
@@ -7526,7 +7524,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="104" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A104" t="s">
         <v>67</v>
       </c>
@@ -7549,7 +7547,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="105" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A105" t="s">
         <v>67</v>
       </c>
@@ -7572,7 +7570,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="106" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A106" t="s">
         <v>67</v>
       </c>
@@ -7595,7 +7593,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="107" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A107" t="s">
         <v>67</v>
       </c>
@@ -7618,7 +7616,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="108" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A108" t="s">
         <v>67</v>
       </c>
@@ -7641,7 +7639,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="109" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A109" t="s">
         <v>67</v>
       </c>
@@ -7664,7 +7662,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="110" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A110" t="s">
         <v>67</v>
       </c>
@@ -7687,7 +7685,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="111" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A111" t="s">
         <v>67</v>
       </c>
@@ -7710,7 +7708,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="112" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A112" t="s">
         <v>67</v>
       </c>
@@ -7733,7 +7731,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="113" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A113" t="s">
         <v>67</v>
       </c>
@@ -7756,7 +7754,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="114" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A114" t="s">
         <v>67</v>
       </c>
@@ -7779,7 +7777,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="115" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A115" t="s">
         <v>67</v>
       </c>
@@ -7802,7 +7800,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="116" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A116" t="s">
         <v>67</v>
       </c>
@@ -7825,7 +7823,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="117" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A117" t="s">
         <v>67</v>
       </c>
@@ -7848,7 +7846,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="119" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A119" t="s">
         <v>67</v>
       </c>
@@ -7871,7 +7869,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="120" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A120" t="s">
         <v>67</v>
       </c>
@@ -7894,7 +7892,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="121" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A121" t="s">
         <v>67</v>
       </c>
@@ -7917,7 +7915,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="122" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A122" t="s">
         <v>67</v>
       </c>
@@ -7940,7 +7938,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="123" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A123" t="s">
         <v>67</v>
       </c>
@@ -7963,7 +7961,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="124" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A124" t="s">
         <v>67</v>
       </c>
@@ -7986,7 +7984,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="125" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A125" t="s">
         <v>67</v>
       </c>
@@ -8009,7 +8007,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="126" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A126" t="s">
         <v>67</v>
       </c>
@@ -8032,7 +8030,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="128" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A128" t="s">
         <v>67</v>
       </c>
@@ -8055,7 +8053,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="129" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A129" t="s">
         <v>67</v>
       </c>
@@ -8078,7 +8076,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="130" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A130" t="s">
         <v>67</v>
       </c>

--- a/input/Studies/C3/C3_Prototypical_Sites/P3_2stages_VRU.xlsx
+++ b/input/Studies/C3/C3_Prototypical_Sites/P3_2stages_VRU.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11207"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28429"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kayarn/sources/xpower/csu/MAES/input/Studies/C3/C3_Prototypical_Sites/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\METEC\MAES2\input\Studies\C3\C3_Prototypical_Sites\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A13B2559-9DED-4B4B-BC1F-962A7541722E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05C12776-A8CD-4C41-8DF5-D8BFFD2CC108}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4480" yWindow="500" windowWidth="31360" windowHeight="21900" tabRatio="925" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="645" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Global Simulation Parameters" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1367" uniqueCount="227">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1375" uniqueCount="229">
   <si>
     <t>Simulation Start Date</t>
   </si>
@@ -323,9 +323,6 @@
     <t>Operating Destruction Efficiency</t>
   </si>
   <si>
-    <t>Activity / Emission Factor Name</t>
-  </si>
-  <si>
     <t>Factor Tag</t>
   </si>
   <si>
@@ -656,9 +653,6 @@
     <t>Leak Gas Composition</t>
   </si>
   <si>
-    <t>Output Directory Template</t>
-  </si>
-  <si>
     <t>Facility Type</t>
   </si>
   <si>
@@ -723,13 +717,25 @@
   </si>
   <si>
     <t>Max Downstream Equipment Capacity [scfh]</t>
+  </si>
+  <si>
+    <t>Crankcase Emissions Flag [TRUE, FALSE]</t>
+  </si>
+  <si>
+    <t>CCEE Ratio Distribution</t>
+  </si>
+  <si>
+    <t>Actuator Type [Gas, Air, Electric, Gas Mechanistic]</t>
+  </si>
+  <si>
+    <t>Common/CrankcaseDistributions/crankcaseTest.csv</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -777,6 +783,11 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="16">
@@ -948,13 +959,10 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="6" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="61">
+  <cellXfs count="62">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -989,9 +997,6 @@
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1100,6 +1105,15 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1406,14 +1420,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B6"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:B4"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="33.5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="64.5" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="33.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="64.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1421,7 +1435,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -1429,30 +1443,20 @@
         <v>365</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>3</v>
       </c>
       <c r="B3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
+        <v>203</v>
+      </c>
+      <c r="B4" t="s">
         <v>204</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A5" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A6" t="s">
-        <v>205</v>
-      </c>
-      <c r="B6" t="s">
-        <v>206</v>
       </c>
     </row>
   </sheetData>
@@ -1464,12 +1468,12 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
   <dimension ref="A1:B9"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="2" width="19.5" bestFit="1" customWidth="1"/>
+    <col min="1" max="2" width="19.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>22</v>
       </c>
@@ -1477,7 +1481,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>24</v>
       </c>
@@ -1485,31 +1489,31 @@
         <v>24</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B3" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B4" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B5" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>19</v>
       </c>
@@ -1517,7 +1521,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>26</v>
       </c>
@@ -1525,7 +1529,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>25</v>
       </c>
@@ -1533,7 +1537,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>41</v>
       </c>
@@ -1549,35 +1553,35 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:E2"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="12.83203125" customWidth="1"/>
-    <col min="2" max="2" width="7.83203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.6640625" customWidth="1"/>
+    <col min="1" max="1" width="12.85546875" customWidth="1"/>
+    <col min="2" max="2" width="7.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.7109375" customWidth="1"/>
     <col min="4" max="4" width="64" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="20" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" s="12" customFormat="1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A1" s="11" t="s">
+    <row r="1" spans="1:5" s="11" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="19" t="s">
+      <c r="B1" s="17" t="s">
         <v>5</v>
       </c>
-      <c r="C1" s="11" t="s">
+      <c r="C1" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="D1" s="11" t="s">
-        <v>203</v>
-      </c>
-      <c r="E1" s="11" t="s">
+      <c r="D1" s="10" t="s">
+        <v>202</v>
+      </c>
+      <c r="E1" s="10" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B2">
         <v>40.319454999999998</v>
@@ -1586,7 +1590,7 @@
         <v>-104.912887</v>
       </c>
       <c r="D2" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E2" t="s">
         <v>65</v>
@@ -1600,95 +1604,95 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D2690304-5371-4DEF-8D7E-371EB1C22F96}">
   <dimension ref="A1:S9"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="15.5" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="19.83203125" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="63.83203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.42578125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="19.85546875" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="63.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" s="20" customFormat="1" ht="80" x14ac:dyDescent="0.2">
-      <c r="A1" s="20" t="s">
+    <row r="1" spans="1:19" s="18" customFormat="1" ht="90" x14ac:dyDescent="0.25">
+      <c r="A1" s="18" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="20" t="s">
+      <c r="B1" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="C1" s="20" t="s">
+      <c r="C1" s="18" t="s">
         <v>8</v>
       </c>
-      <c r="D1" s="20" t="s">
+      <c r="D1" s="18" t="s">
         <v>5</v>
       </c>
-      <c r="E1" s="20" t="s">
+      <c r="E1" s="18" t="s">
         <v>6</v>
       </c>
-      <c r="F1" s="21" t="s">
+      <c r="F1" s="19" t="s">
         <v>68</v>
       </c>
-      <c r="G1" s="21" t="s">
+      <c r="G1" s="19" t="s">
         <v>9</v>
       </c>
-      <c r="H1" s="21" t="s">
+      <c r="H1" s="19" t="s">
         <v>10</v>
       </c>
-      <c r="I1" s="20" t="s">
+      <c r="I1" s="18" t="s">
+        <v>119</v>
+      </c>
+      <c r="J1" s="18" t="s">
         <v>120</v>
       </c>
-      <c r="J1" s="20" t="s">
+      <c r="K1" s="18" t="s">
         <v>121</v>
       </c>
-      <c r="K1" s="20" t="s">
+      <c r="L1" s="18" t="s">
         <v>122</v>
       </c>
-      <c r="L1" s="20" t="s">
+      <c r="M1" s="18" t="s">
         <v>123</v>
       </c>
-      <c r="M1" s="20" t="s">
+      <c r="N1" s="18" t="s">
         <v>124</v>
       </c>
-      <c r="N1" s="20" t="s">
+      <c r="O1" s="18" t="s">
+        <v>86</v>
+      </c>
+      <c r="P1" s="18" t="s">
+        <v>57</v>
+      </c>
+      <c r="Q1" s="18" t="s">
+        <v>189</v>
+      </c>
+      <c r="R1" s="18" t="s">
+        <v>87</v>
+      </c>
+      <c r="S1" s="18" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="2" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>99</v>
+      </c>
+      <c r="B2" t="s">
         <v>125</v>
       </c>
-      <c r="O1" s="20" t="s">
-        <v>86</v>
-      </c>
-      <c r="P1" s="20" t="s">
-        <v>57</v>
-      </c>
-      <c r="Q1" s="20" t="s">
-        <v>190</v>
-      </c>
-      <c r="R1" s="20" t="s">
-        <v>87</v>
-      </c>
-      <c r="S1" s="20" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
+      <c r="C2" t="s">
         <v>100</v>
       </c>
-      <c r="B2" t="s">
-        <v>126</v>
-      </c>
-      <c r="C2" t="s">
-        <v>101</v>
-      </c>
       <c r="D2">
         <v>0</v>
       </c>
       <c r="E2">
         <v>0</v>
       </c>
-      <c r="F2" s="22">
+      <c r="F2" s="20">
         <v>365</v>
       </c>
-      <c r="G2" s="22">
+      <c r="G2" s="20">
         <v>48</v>
       </c>
-      <c r="H2" s="22">
+      <c r="H2" s="20">
         <v>5.0000000000000001E-3</v>
       </c>
       <c r="I2">
@@ -1716,24 +1720,24 @@
         <v>58</v>
       </c>
       <c r="Q2" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="R2" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="S2" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="3" spans="1:19" x14ac:dyDescent="0.2">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B3" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C3" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D3">
         <v>0</v>
@@ -1741,13 +1745,13 @@
       <c r="E3">
         <v>0</v>
       </c>
-      <c r="F3" s="22">
+      <c r="F3" s="20">
         <v>365</v>
       </c>
-      <c r="G3" s="22">
+      <c r="G3" s="20">
         <v>48</v>
       </c>
-      <c r="H3" s="22">
+      <c r="H3" s="20">
         <v>5.0000000000000001E-3</v>
       </c>
       <c r="I3">
@@ -1775,24 +1779,24 @@
         <v>58</v>
       </c>
       <c r="Q3" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="R3" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="S3" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="4" spans="1:19" x14ac:dyDescent="0.2">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B4" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C4" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D4">
         <v>0</v>
@@ -1800,13 +1804,13 @@
       <c r="E4">
         <v>0</v>
       </c>
-      <c r="F4" s="22">
+      <c r="F4" s="20">
         <v>365</v>
       </c>
-      <c r="G4" s="22">
+      <c r="G4" s="20">
         <v>48</v>
       </c>
-      <c r="H4" s="22">
+      <c r="H4" s="20">
         <v>5.0000000000000001E-3</v>
       </c>
       <c r="I4">
@@ -1834,24 +1838,24 @@
         <v>58</v>
       </c>
       <c r="Q4" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="R4" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="S4" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B5" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C5" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D5">
         <v>0</v>
@@ -1859,13 +1863,13 @@
       <c r="E5">
         <v>0</v>
       </c>
-      <c r="F5" s="22">
+      <c r="F5" s="20">
         <v>365</v>
       </c>
-      <c r="G5" s="22">
+      <c r="G5" s="20">
         <v>48</v>
       </c>
-      <c r="H5" s="22">
+      <c r="H5" s="20">
         <v>5.0000000000000001E-3</v>
       </c>
       <c r="I5">
@@ -1893,24 +1897,24 @@
         <v>58</v>
       </c>
       <c r="Q5" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="R5" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="S5" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B6" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C6" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D6">
         <v>0</v>
@@ -1918,13 +1922,13 @@
       <c r="E6">
         <v>0</v>
       </c>
-      <c r="F6" s="22">
+      <c r="F6" s="20">
         <v>365</v>
       </c>
-      <c r="G6" s="22">
+      <c r="G6" s="20">
         <v>48</v>
       </c>
-      <c r="H6" s="22">
+      <c r="H6" s="20">
         <v>5.0000000000000001E-3</v>
       </c>
       <c r="I6">
@@ -1952,24 +1956,24 @@
         <v>58</v>
       </c>
       <c r="Q6" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="R6" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="S6" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B7" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C7" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D7">
         <v>0</v>
@@ -1977,13 +1981,13 @@
       <c r="E7">
         <v>0</v>
       </c>
-      <c r="F7" s="22">
+      <c r="F7" s="20">
         <v>365</v>
       </c>
-      <c r="G7" s="22">
+      <c r="G7" s="20">
         <v>48</v>
       </c>
-      <c r="H7" s="22">
+      <c r="H7" s="20">
         <v>5.0000000000000001E-3</v>
       </c>
       <c r="I7">
@@ -2011,24 +2015,24 @@
         <v>58</v>
       </c>
       <c r="Q7" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="R7" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="S7" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B8" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C8" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D8">
         <v>0</v>
@@ -2036,13 +2040,13 @@
       <c r="E8">
         <v>0</v>
       </c>
-      <c r="F8" s="22">
+      <c r="F8" s="20">
         <v>365</v>
       </c>
-      <c r="G8" s="22">
+      <c r="G8" s="20">
         <v>48</v>
       </c>
-      <c r="H8" s="22">
+      <c r="H8" s="20">
         <v>5.0000000000000001E-3</v>
       </c>
       <c r="I8">
@@ -2070,24 +2074,24 @@
         <v>58</v>
       </c>
       <c r="Q8" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="R8" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="S8" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B9" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C9" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D9">
         <v>0</v>
@@ -2095,13 +2099,13 @@
       <c r="E9">
         <v>0</v>
       </c>
-      <c r="F9" s="22">
+      <c r="F9" s="20">
         <v>365</v>
       </c>
-      <c r="G9" s="22">
+      <c r="G9" s="20">
         <v>48</v>
       </c>
-      <c r="H9" s="22">
+      <c r="H9" s="20">
         <v>5.0000000000000001E-3</v>
       </c>
       <c r="I9">
@@ -2129,13 +2133,13 @@
         <v>58</v>
       </c>
       <c r="Q9" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="R9" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="S9" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
     </row>
   </sheetData>
@@ -2146,467 +2150,467 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:P19"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="5" width="15.6640625" customWidth="1"/>
-    <col min="6" max="13" width="15.6640625" style="4" customWidth="1"/>
-    <col min="14" max="14" width="24.5" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="47.1640625" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="15.6640625" customWidth="1"/>
-    <col min="17" max="17" width="18.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="5" width="15.7109375" customWidth="1"/>
+    <col min="6" max="13" width="15.7109375" style="3" customWidth="1"/>
+    <col min="14" max="14" width="24.42578125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="47.140625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="15.7109375" customWidth="1"/>
+    <col min="17" max="17" width="18.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" s="3" customFormat="1" ht="48" x14ac:dyDescent="0.2">
-      <c r="A1" s="16" t="s">
+    <row r="1" spans="1:16" s="2" customFormat="1" ht="60" x14ac:dyDescent="0.25">
+      <c r="A1" s="15" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="16" t="s">
+      <c r="B1" s="15" t="s">
         <v>8</v>
       </c>
-      <c r="C1" s="17" t="s">
+      <c r="C1" s="16" t="s">
         <v>68</v>
       </c>
-      <c r="D1" s="17" t="s">
+      <c r="D1" s="16" t="s">
         <v>9</v>
       </c>
-      <c r="E1" s="17" t="s">
+      <c r="E1" s="16" t="s">
         <v>10</v>
       </c>
-      <c r="F1" s="16" t="s">
+      <c r="F1" s="15" t="s">
         <v>86</v>
       </c>
-      <c r="G1" s="23" t="s">
+      <c r="G1" s="21" t="s">
+        <v>126</v>
+      </c>
+      <c r="H1" s="21" t="s">
         <v>127</v>
       </c>
-      <c r="H1" s="23" t="s">
+      <c r="I1" s="21" t="s">
         <v>128</v>
       </c>
-      <c r="I1" s="23" t="s">
+      <c r="J1" s="21" t="s">
         <v>129</v>
       </c>
-      <c r="J1" s="23" t="s">
+      <c r="K1" s="21" t="s">
         <v>130</v>
       </c>
-      <c r="K1" s="23" t="s">
-        <v>131</v>
-      </c>
-      <c r="L1" s="16" t="s">
+      <c r="L1" s="15" t="s">
         <v>32</v>
       </c>
-      <c r="M1" s="16" t="s">
+      <c r="M1" s="15" t="s">
         <v>59</v>
       </c>
-      <c r="N1" s="16" t="s">
+      <c r="N1" s="15" t="s">
         <v>7</v>
       </c>
-      <c r="O1" s="16" t="s">
-        <v>190</v>
-      </c>
-      <c r="P1" s="16" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="O1" s="15" t="s">
+        <v>189</v>
+      </c>
+      <c r="P1" s="15" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B2" t="s">
         <v>33</v>
       </c>
-      <c r="C2" s="8">
+      <c r="C2" s="7">
         <v>365</v>
       </c>
-      <c r="D2" s="8">
+      <c r="D2" s="7">
         <v>62</v>
       </c>
-      <c r="E2" s="8">
+      <c r="E2" s="7">
         <v>5.9867000000000002E-3</v>
       </c>
-      <c r="F2" s="4" t="s">
+      <c r="F2" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="G2" s="24">
-        <v>1</v>
-      </c>
-      <c r="H2" s="24">
+      <c r="G2" s="22">
+        <v>1</v>
+      </c>
+      <c r="H2" s="22">
         <v>0.01</v>
       </c>
-      <c r="I2" s="24">
-        <v>1</v>
-      </c>
-      <c r="J2" s="24">
+      <c r="I2" s="22">
+        <v>1</v>
+      </c>
+      <c r="J2" s="22">
         <v>20</v>
       </c>
-      <c r="K2" s="24" t="s">
-        <v>207</v>
-      </c>
-      <c r="L2" s="4">
+      <c r="K2" s="22" t="s">
+        <v>205</v>
+      </c>
+      <c r="L2" s="3">
         <v>0.75</v>
       </c>
-      <c r="M2" s="4" t="s">
+      <c r="M2" s="3" t="s">
         <v>60</v>
       </c>
       <c r="N2" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="O2" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="P2" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.2">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B3" t="s">
         <v>34</v>
       </c>
-      <c r="C3" s="8">
+      <c r="C3" s="7">
         <v>365</v>
       </c>
-      <c r="D3" s="8">
+      <c r="D3" s="7">
         <v>62</v>
       </c>
-      <c r="E3" s="8">
+      <c r="E3" s="7">
         <v>5.9867000000000002E-3</v>
       </c>
-      <c r="F3" s="4" t="s">
+      <c r="F3" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="G3" s="24">
-        <v>1</v>
-      </c>
-      <c r="H3" s="24">
+      <c r="G3" s="22">
+        <v>1</v>
+      </c>
+      <c r="H3" s="22">
         <v>0.01</v>
       </c>
-      <c r="I3" s="24">
-        <v>1</v>
-      </c>
-      <c r="J3" s="24">
+      <c r="I3" s="22">
+        <v>1</v>
+      </c>
+      <c r="J3" s="22">
         <v>20</v>
       </c>
-      <c r="K3" s="24" t="s">
-        <v>207</v>
-      </c>
-      <c r="L3" s="4">
+      <c r="K3" s="22" t="s">
+        <v>205</v>
+      </c>
+      <c r="L3" s="3">
         <v>0.75</v>
       </c>
-      <c r="M3" s="4" t="s">
+      <c r="M3" s="3" t="s">
         <v>60</v>
       </c>
       <c r="N3" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="O3" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="P3" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.2">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B4" t="s">
         <v>35</v>
       </c>
-      <c r="C4" s="8">
+      <c r="C4" s="7">
         <v>365</v>
       </c>
-      <c r="D4" s="8">
+      <c r="D4" s="7">
         <v>62</v>
       </c>
-      <c r="E4" s="8">
+      <c r="E4" s="7">
         <v>5.9867000000000002E-3</v>
       </c>
-      <c r="F4" s="4" t="s">
+      <c r="F4" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="G4" s="24">
-        <v>1</v>
-      </c>
-      <c r="H4" s="24">
+      <c r="G4" s="22">
+        <v>1</v>
+      </c>
+      <c r="H4" s="22">
         <v>0.01</v>
       </c>
-      <c r="I4" s="24">
-        <v>1</v>
-      </c>
-      <c r="J4" s="24">
+      <c r="I4" s="22">
+        <v>1</v>
+      </c>
+      <c r="J4" s="22">
         <v>20</v>
       </c>
-      <c r="K4" s="24" t="s">
-        <v>207</v>
-      </c>
-      <c r="L4" s="4">
+      <c r="K4" s="22" t="s">
+        <v>205</v>
+      </c>
+      <c r="L4" s="3">
         <v>0.75</v>
       </c>
-      <c r="M4" s="4" t="s">
+      <c r="M4" s="3" t="s">
         <v>60</v>
       </c>
       <c r="N4" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="O4" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="P4" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B5" t="s">
         <v>36</v>
       </c>
-      <c r="C5" s="8">
+      <c r="C5" s="7">
         <v>365</v>
       </c>
-      <c r="D5" s="8">
+      <c r="D5" s="7">
         <v>62</v>
       </c>
-      <c r="E5" s="8">
+      <c r="E5" s="7">
         <v>5.9867000000000002E-3</v>
       </c>
-      <c r="F5" s="4" t="s">
+      <c r="F5" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="G5" s="24">
-        <v>1</v>
-      </c>
-      <c r="H5" s="24">
+      <c r="G5" s="22">
+        <v>1</v>
+      </c>
+      <c r="H5" s="22">
         <v>0.01</v>
       </c>
-      <c r="I5" s="24">
-        <v>1</v>
-      </c>
-      <c r="J5" s="24">
+      <c r="I5" s="22">
+        <v>1</v>
+      </c>
+      <c r="J5" s="22">
         <v>20</v>
       </c>
-      <c r="K5" s="24" t="s">
-        <v>207</v>
-      </c>
-      <c r="L5" s="4">
+      <c r="K5" s="22" t="s">
+        <v>205</v>
+      </c>
+      <c r="L5" s="3">
         <v>0.75</v>
       </c>
-      <c r="M5" s="4" t="s">
+      <c r="M5" s="3" t="s">
         <v>60</v>
       </c>
       <c r="N5" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="O5" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="P5" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B6" t="s">
         <v>37</v>
       </c>
-      <c r="C6" s="8">
+      <c r="C6" s="7">
         <v>365</v>
       </c>
-      <c r="D6" s="8">
+      <c r="D6" s="7">
         <v>62</v>
       </c>
-      <c r="E6" s="8">
+      <c r="E6" s="7">
         <v>5.9867000000000002E-3</v>
       </c>
-      <c r="F6" s="4" t="s">
+      <c r="F6" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="G6" s="24">
-        <v>1</v>
-      </c>
-      <c r="H6" s="24">
+      <c r="G6" s="22">
+        <v>1</v>
+      </c>
+      <c r="H6" s="22">
         <v>0.01</v>
       </c>
-      <c r="I6" s="24">
-        <v>1</v>
-      </c>
-      <c r="J6" s="24">
+      <c r="I6" s="22">
+        <v>1</v>
+      </c>
+      <c r="J6" s="22">
         <v>20</v>
       </c>
-      <c r="K6" s="24" t="s">
-        <v>207</v>
-      </c>
-      <c r="L6" s="4">
+      <c r="K6" s="22" t="s">
+        <v>205</v>
+      </c>
+      <c r="L6" s="3">
         <v>0.75</v>
       </c>
-      <c r="M6" s="4" t="s">
+      <c r="M6" s="3" t="s">
         <v>60</v>
       </c>
       <c r="N6" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="O6" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="P6" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B7" t="s">
         <v>38</v>
       </c>
-      <c r="C7" s="8">
+      <c r="C7" s="7">
         <v>365</v>
       </c>
-      <c r="D7" s="8">
+      <c r="D7" s="7">
         <v>62</v>
       </c>
-      <c r="E7" s="8">
+      <c r="E7" s="7">
         <v>5.9867000000000002E-3</v>
       </c>
-      <c r="F7" s="4" t="s">
+      <c r="F7" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="G7" s="24">
-        <v>1</v>
-      </c>
-      <c r="H7" s="24">
+      <c r="G7" s="22">
+        <v>1</v>
+      </c>
+      <c r="H7" s="22">
         <v>0.01</v>
       </c>
-      <c r="I7" s="24">
-        <v>1</v>
-      </c>
-      <c r="J7" s="24">
+      <c r="I7" s="22">
+        <v>1</v>
+      </c>
+      <c r="J7" s="22">
         <v>20</v>
       </c>
-      <c r="K7" s="24" t="s">
-        <v>207</v>
-      </c>
-      <c r="L7" s="4">
+      <c r="K7" s="22" t="s">
+        <v>205</v>
+      </c>
+      <c r="L7" s="3">
         <v>0.75</v>
       </c>
-      <c r="M7" s="4" t="s">
+      <c r="M7" s="3" t="s">
         <v>60</v>
       </c>
       <c r="N7" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="O7" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="P7" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B8" t="s">
         <v>39</v>
       </c>
-      <c r="C8" s="8">
+      <c r="C8" s="7">
         <v>365</v>
       </c>
-      <c r="D8" s="8">
+      <c r="D8" s="7">
         <v>62</v>
       </c>
-      <c r="E8" s="8">
+      <c r="E8" s="7">
         <v>5.9867000000000002E-3</v>
       </c>
-      <c r="F8" s="4" t="s">
+      <c r="F8" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="G8" s="24">
-        <v>1</v>
-      </c>
-      <c r="H8" s="24">
+      <c r="G8" s="22">
+        <v>1</v>
+      </c>
+      <c r="H8" s="22">
         <v>0.01</v>
       </c>
-      <c r="I8" s="24">
-        <v>1</v>
-      </c>
-      <c r="J8" s="24">
+      <c r="I8" s="22">
+        <v>1</v>
+      </c>
+      <c r="J8" s="22">
         <v>20</v>
       </c>
-      <c r="K8" s="24" t="s">
-        <v>207</v>
-      </c>
-      <c r="L8" s="4">
+      <c r="K8" s="22" t="s">
+        <v>205</v>
+      </c>
+      <c r="L8" s="3">
         <v>0.75</v>
       </c>
-      <c r="M8" s="4" t="s">
+      <c r="M8" s="3" t="s">
         <v>60</v>
       </c>
       <c r="N8" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="O8" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="P8" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B9" t="s">
         <v>40</v>
       </c>
-      <c r="C9" s="8">
+      <c r="C9" s="7">
         <v>365</v>
       </c>
-      <c r="D9" s="8">
+      <c r="D9" s="7">
         <v>62</v>
       </c>
-      <c r="E9" s="8">
+      <c r="E9" s="7">
         <v>5.9867000000000002E-3</v>
       </c>
-      <c r="F9" s="4" t="s">
+      <c r="F9" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="G9" s="24">
-        <v>1</v>
-      </c>
-      <c r="H9" s="24">
+      <c r="G9" s="22">
+        <v>1</v>
+      </c>
+      <c r="H9" s="22">
         <v>0.01</v>
       </c>
-      <c r="I9" s="24">
-        <v>1</v>
-      </c>
-      <c r="J9" s="24">
+      <c r="I9" s="22">
+        <v>1</v>
+      </c>
+      <c r="J9" s="22">
         <v>20</v>
       </c>
-      <c r="K9" s="24" t="s">
-        <v>207</v>
-      </c>
-      <c r="L9" s="4">
+      <c r="K9" s="22" t="s">
+        <v>205</v>
+      </c>
+      <c r="L9" s="3">
         <v>0.75</v>
       </c>
-      <c r="M9" s="4" t="s">
+      <c r="M9" s="3" t="s">
         <v>60</v>
       </c>
       <c r="N9" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="O9" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="P9" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
       <c r="F10"/>
       <c r="G10"/>
       <c r="H10"/>
@@ -2616,407 +2620,407 @@
       <c r="L10"/>
       <c r="M10"/>
     </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B11" t="s">
         <v>49</v>
       </c>
-      <c r="C11" s="8">
+      <c r="C11" s="7">
         <v>365</v>
       </c>
-      <c r="D11" s="8">
+      <c r="D11" s="7">
         <v>62</v>
       </c>
-      <c r="E11" s="8">
+      <c r="E11" s="7">
         <v>5.9867000000000002E-3</v>
       </c>
-      <c r="F11" s="4" t="s">
+      <c r="F11" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="G11" s="24">
-        <v>1</v>
-      </c>
-      <c r="H11" s="24">
+      <c r="G11" s="22">
+        <v>1</v>
+      </c>
+      <c r="H11" s="22">
         <v>0.01</v>
       </c>
-      <c r="I11" s="24">
-        <v>1</v>
-      </c>
-      <c r="J11" s="24">
+      <c r="I11" s="22">
+        <v>1</v>
+      </c>
+      <c r="J11" s="22">
         <v>20</v>
       </c>
-      <c r="K11" s="24" t="s">
-        <v>207</v>
-      </c>
-      <c r="L11" s="4">
-        <v>1</v>
-      </c>
-      <c r="M11" s="4" t="s">
+      <c r="K11" s="22" t="s">
+        <v>205</v>
+      </c>
+      <c r="L11" s="3">
+        <v>1</v>
+      </c>
+      <c r="M11" s="3" t="s">
         <v>61</v>
       </c>
       <c r="N11" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="O11" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="P11" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B12" t="s">
         <v>50</v>
       </c>
-      <c r="C12" s="8">
+      <c r="C12" s="7">
         <v>365</v>
       </c>
-      <c r="D12" s="8">
+      <c r="D12" s="7">
         <v>62</v>
       </c>
-      <c r="E12" s="8">
+      <c r="E12" s="7">
         <v>5.9867000000000002E-3</v>
       </c>
-      <c r="F12" s="4" t="s">
+      <c r="F12" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="G12" s="24">
-        <v>1</v>
-      </c>
-      <c r="H12" s="24">
+      <c r="G12" s="22">
+        <v>1</v>
+      </c>
+      <c r="H12" s="22">
         <v>0.01</v>
       </c>
-      <c r="I12" s="24">
-        <v>1</v>
-      </c>
-      <c r="J12" s="24">
+      <c r="I12" s="22">
+        <v>1</v>
+      </c>
+      <c r="J12" s="22">
         <v>20</v>
       </c>
-      <c r="K12" s="24" t="s">
-        <v>207</v>
-      </c>
-      <c r="L12" s="4">
-        <v>1</v>
-      </c>
-      <c r="M12" s="4" t="s">
+      <c r="K12" s="22" t="s">
+        <v>205</v>
+      </c>
+      <c r="L12" s="3">
+        <v>1</v>
+      </c>
+      <c r="M12" s="3" t="s">
         <v>61</v>
       </c>
       <c r="N12" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="O12" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="P12" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B13" t="s">
         <v>51</v>
       </c>
-      <c r="C13" s="8">
+      <c r="C13" s="7">
         <v>365</v>
       </c>
-      <c r="D13" s="8">
+      <c r="D13" s="7">
         <v>62</v>
       </c>
-      <c r="E13" s="8">
+      <c r="E13" s="7">
         <v>5.9867000000000002E-3</v>
       </c>
-      <c r="F13" s="4" t="s">
+      <c r="F13" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="G13" s="24">
-        <v>1</v>
-      </c>
-      <c r="H13" s="24">
+      <c r="G13" s="22">
+        <v>1</v>
+      </c>
+      <c r="H13" s="22">
         <v>0.01</v>
       </c>
-      <c r="I13" s="24">
-        <v>1</v>
-      </c>
-      <c r="J13" s="24">
+      <c r="I13" s="22">
+        <v>1</v>
+      </c>
+      <c r="J13" s="22">
         <v>20</v>
       </c>
-      <c r="K13" s="24" t="s">
-        <v>207</v>
-      </c>
-      <c r="L13" s="4">
-        <v>1</v>
-      </c>
-      <c r="M13" s="4" t="s">
+      <c r="K13" s="22" t="s">
+        <v>205</v>
+      </c>
+      <c r="L13" s="3">
+        <v>1</v>
+      </c>
+      <c r="M13" s="3" t="s">
         <v>61</v>
       </c>
       <c r="N13" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="O13" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="P13" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B14" t="s">
         <v>52</v>
       </c>
-      <c r="C14" s="8">
+      <c r="C14" s="7">
         <v>365</v>
       </c>
-      <c r="D14" s="8">
+      <c r="D14" s="7">
         <v>62</v>
       </c>
-      <c r="E14" s="8">
+      <c r="E14" s="7">
         <v>5.9867000000000002E-3</v>
       </c>
-      <c r="F14" s="4" t="s">
+      <c r="F14" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="G14" s="24">
-        <v>1</v>
-      </c>
-      <c r="H14" s="24">
+      <c r="G14" s="22">
+        <v>1</v>
+      </c>
+      <c r="H14" s="22">
         <v>0.01</v>
       </c>
-      <c r="I14" s="24">
-        <v>1</v>
-      </c>
-      <c r="J14" s="24">
+      <c r="I14" s="22">
+        <v>1</v>
+      </c>
+      <c r="J14" s="22">
         <v>20</v>
       </c>
-      <c r="K14" s="24" t="s">
-        <v>207</v>
-      </c>
-      <c r="L14" s="4">
-        <v>1</v>
-      </c>
-      <c r="M14" s="4" t="s">
+      <c r="K14" s="22" t="s">
+        <v>205</v>
+      </c>
+      <c r="L14" s="3">
+        <v>1</v>
+      </c>
+      <c r="M14" s="3" t="s">
         <v>61</v>
       </c>
       <c r="N14" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="O14" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="P14" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B15" t="s">
         <v>53</v>
       </c>
-      <c r="C15" s="8">
+      <c r="C15" s="7">
         <v>365</v>
       </c>
-      <c r="D15" s="8">
+      <c r="D15" s="7">
         <v>62</v>
       </c>
-      <c r="E15" s="8">
+      <c r="E15" s="7">
         <v>5.9867000000000002E-3</v>
       </c>
-      <c r="F15" s="4" t="s">
+      <c r="F15" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="G15" s="24">
-        <v>1</v>
-      </c>
-      <c r="H15" s="24">
+      <c r="G15" s="22">
+        <v>1</v>
+      </c>
+      <c r="H15" s="22">
         <v>0.01</v>
       </c>
-      <c r="I15" s="24">
-        <v>1</v>
-      </c>
-      <c r="J15" s="24">
+      <c r="I15" s="22">
+        <v>1</v>
+      </c>
+      <c r="J15" s="22">
         <v>20</v>
       </c>
-      <c r="K15" s="24" t="s">
-        <v>207</v>
-      </c>
-      <c r="L15" s="4">
-        <v>1</v>
-      </c>
-      <c r="M15" s="4" t="s">
+      <c r="K15" s="22" t="s">
+        <v>205</v>
+      </c>
+      <c r="L15" s="3">
+        <v>1</v>
+      </c>
+      <c r="M15" s="3" t="s">
         <v>61</v>
       </c>
       <c r="N15" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="O15" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="P15" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B16" t="s">
         <v>54</v>
       </c>
-      <c r="C16" s="8">
+      <c r="C16" s="7">
         <v>365</v>
       </c>
-      <c r="D16" s="8">
+      <c r="D16" s="7">
         <v>62</v>
       </c>
-      <c r="E16" s="8">
+      <c r="E16" s="7">
         <v>5.9867000000000002E-3</v>
       </c>
-      <c r="F16" s="4" t="s">
+      <c r="F16" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="G16" s="24">
-        <v>1</v>
-      </c>
-      <c r="H16" s="24">
+      <c r="G16" s="22">
+        <v>1</v>
+      </c>
+      <c r="H16" s="22">
         <v>0.01</v>
       </c>
-      <c r="I16" s="24">
-        <v>1</v>
-      </c>
-      <c r="J16" s="24">
+      <c r="I16" s="22">
+        <v>1</v>
+      </c>
+      <c r="J16" s="22">
         <v>20</v>
       </c>
-      <c r="K16" s="24" t="s">
-        <v>207</v>
-      </c>
-      <c r="L16" s="4">
-        <v>1</v>
-      </c>
-      <c r="M16" s="4" t="s">
+      <c r="K16" s="22" t="s">
+        <v>205</v>
+      </c>
+      <c r="L16" s="3">
+        <v>1</v>
+      </c>
+      <c r="M16" s="3" t="s">
         <v>61</v>
       </c>
       <c r="N16" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="O16" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="P16" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="17" spans="1:16" x14ac:dyDescent="0.2">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="17" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B17" t="s">
         <v>55</v>
       </c>
-      <c r="C17" s="8">
+      <c r="C17" s="7">
         <v>365</v>
       </c>
-      <c r="D17" s="8">
+      <c r="D17" s="7">
         <v>62</v>
       </c>
-      <c r="E17" s="8">
+      <c r="E17" s="7">
         <v>5.9867000000000002E-3</v>
       </c>
-      <c r="F17" s="4" t="s">
+      <c r="F17" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="G17" s="24">
-        <v>1</v>
-      </c>
-      <c r="H17" s="24">
+      <c r="G17" s="22">
+        <v>1</v>
+      </c>
+      <c r="H17" s="22">
         <v>0.01</v>
       </c>
-      <c r="I17" s="24">
-        <v>1</v>
-      </c>
-      <c r="J17" s="24">
+      <c r="I17" s="22">
+        <v>1</v>
+      </c>
+      <c r="J17" s="22">
         <v>20</v>
       </c>
-      <c r="K17" s="24" t="s">
-        <v>207</v>
-      </c>
-      <c r="L17" s="4">
-        <v>1</v>
-      </c>
-      <c r="M17" s="4" t="s">
+      <c r="K17" s="22" t="s">
+        <v>205</v>
+      </c>
+      <c r="L17" s="3">
+        <v>1</v>
+      </c>
+      <c r="M17" s="3" t="s">
         <v>61</v>
       </c>
       <c r="N17" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="O17" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="P17" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="18" spans="1:16" x14ac:dyDescent="0.2">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="18" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B18" t="s">
         <v>56</v>
       </c>
-      <c r="C18" s="8">
+      <c r="C18" s="7">
         <v>365</v>
       </c>
-      <c r="D18" s="8">
+      <c r="D18" s="7">
         <v>62</v>
       </c>
-      <c r="E18" s="8">
+      <c r="E18" s="7">
         <v>5.9867000000000002E-3</v>
       </c>
-      <c r="F18" s="4" t="s">
+      <c r="F18" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="G18" s="24">
-        <v>1</v>
-      </c>
-      <c r="H18" s="24">
+      <c r="G18" s="22">
+        <v>1</v>
+      </c>
+      <c r="H18" s="22">
         <v>0.01</v>
       </c>
-      <c r="I18" s="24">
-        <v>1</v>
-      </c>
-      <c r="J18" s="24">
+      <c r="I18" s="22">
+        <v>1</v>
+      </c>
+      <c r="J18" s="22">
         <v>20</v>
       </c>
-      <c r="K18" s="24" t="s">
-        <v>207</v>
-      </c>
-      <c r="L18" s="4">
-        <v>1</v>
-      </c>
-      <c r="M18" s="4" t="s">
+      <c r="K18" s="22" t="s">
+        <v>205</v>
+      </c>
+      <c r="L18" s="3">
+        <v>1</v>
+      </c>
+      <c r="M18" s="3" t="s">
         <v>61</v>
       </c>
       <c r="N18" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="O18" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="P18" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="19" spans="1:16" x14ac:dyDescent="0.2">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="19" spans="1:16" x14ac:dyDescent="0.25">
       <c r="F19"/>
       <c r="G19"/>
       <c r="H19"/>
@@ -3033,183 +3037,183 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1:U16"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="16" bestFit="1" customWidth="1"/>
     <col min="3" max="5" width="12" customWidth="1"/>
-    <col min="6" max="6" width="8.5" style="4" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.83203125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="19.83203125" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="13.83203125" customWidth="1"/>
-    <col min="11" max="12" width="26.5" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="8.42578125" style="3" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="19.85546875" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="13.85546875" customWidth="1"/>
+    <col min="11" max="12" width="26.42578125" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="10" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="12.6640625" bestFit="1" customWidth="1"/>
-    <col min="15" max="17" width="17.83203125" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="18.1640625" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="18.33203125" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="18.1640625" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="9.83203125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="15" max="17" width="17.85546875" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="18.140625" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="18.28515625" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="18.140625" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="9.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" s="12" customFormat="1" ht="80" x14ac:dyDescent="0.2">
-      <c r="A1" s="11" t="s">
+    <row r="1" spans="1:21" s="11" customFormat="1" ht="75" x14ac:dyDescent="0.25">
+      <c r="A1" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="11" t="s">
+      <c r="B1" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="C1" s="13" t="s">
+      <c r="C1" s="12" t="s">
         <v>68</v>
       </c>
-      <c r="D1" s="13" t="s">
+      <c r="D1" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="E1" s="13" t="s">
+      <c r="E1" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="F1" s="11" t="s">
+      <c r="F1" s="10" t="s">
         <v>86</v>
       </c>
-      <c r="G1" s="11" t="s">
+      <c r="G1" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="H1" s="11" t="s">
-        <v>190</v>
-      </c>
-      <c r="I1" s="11" t="s">
+      <c r="H1" s="10" t="s">
+        <v>189</v>
+      </c>
+      <c r="I1" s="10" t="s">
+        <v>168</v>
+      </c>
+      <c r="J1" s="55" t="s">
         <v>169</v>
       </c>
-      <c r="J1" s="57" t="s">
+      <c r="K1" s="56" t="s">
         <v>170</v>
       </c>
-      <c r="K1" s="58" t="s">
+      <c r="L1" s="56" t="s">
         <v>171</v>
       </c>
-      <c r="L1" s="58" t="s">
+      <c r="M1" s="25" t="s">
         <v>172</v>
       </c>
-      <c r="M1" s="27" t="s">
+      <c r="N1" s="10" t="s">
         <v>173</v>
       </c>
-      <c r="N1" s="11" t="s">
+      <c r="O1" s="57" t="s">
         <v>174</v>
       </c>
-      <c r="O1" s="59" t="s">
+      <c r="P1" s="57" t="s">
         <v>175</v>
       </c>
-      <c r="P1" s="59" t="s">
+      <c r="Q1" s="40" t="s">
         <v>176</v>
       </c>
-      <c r="Q1" s="42" t="s">
+      <c r="R1" s="58" t="s">
         <v>177</v>
       </c>
-      <c r="R1" s="60" t="s">
+      <c r="S1" s="58" t="s">
         <v>178</v>
       </c>
-      <c r="S1" s="60" t="s">
+      <c r="T1" s="36" t="s">
         <v>179</v>
       </c>
-      <c r="T1" s="38" t="s">
+      <c r="U1" s="10" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="2" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>99</v>
+      </c>
+      <c r="B2" t="s">
+        <v>96</v>
+      </c>
+      <c r="C2" s="6">
+        <v>365</v>
+      </c>
+      <c r="D2" s="6">
+        <v>60</v>
+      </c>
+      <c r="E2" s="6">
+        <v>3.7499999999999999E-2</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="G2" t="s">
         <v>180</v>
       </c>
-      <c r="U1" s="11" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="2" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
-        <v>100</v>
-      </c>
-      <c r="B2" t="s">
-        <v>97</v>
-      </c>
-      <c r="C2" s="7">
-        <v>365</v>
-      </c>
-      <c r="D2" s="7">
-        <v>60</v>
-      </c>
-      <c r="E2" s="7">
-        <v>3.7499999999999999E-2</v>
-      </c>
-      <c r="F2" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="G2" t="s">
-        <v>181</v>
-      </c>
       <c r="H2" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="I2" t="b">
         <v>0</v>
       </c>
-      <c r="J2" s="30">
-        <v>0</v>
-      </c>
-      <c r="K2" s="30">
-        <v>0</v>
-      </c>
-      <c r="L2" s="30">
-        <v>0</v>
-      </c>
-      <c r="M2" s="30">
+      <c r="J2" s="28">
+        <v>0</v>
+      </c>
+      <c r="K2" s="28">
+        <v>0</v>
+      </c>
+      <c r="L2" s="28">
+        <v>0</v>
+      </c>
+      <c r="M2" s="28">
         <v>0.1</v>
       </c>
       <c r="N2" t="b">
         <v>0</v>
       </c>
-      <c r="O2" s="7">
-        <v>0</v>
-      </c>
-      <c r="P2" s="7">
-        <v>0</v>
-      </c>
-      <c r="Q2" s="7">
+      <c r="O2" s="6">
+        <v>0</v>
+      </c>
+      <c r="P2" s="6">
+        <v>0</v>
+      </c>
+      <c r="Q2" s="6">
         <v>0.1</v>
       </c>
-      <c r="R2" s="9">
-        <v>0</v>
-      </c>
-      <c r="S2" s="9">
-        <v>0</v>
-      </c>
-      <c r="T2" s="9">
+      <c r="R2" s="8">
+        <v>0</v>
+      </c>
+      <c r="S2" s="8">
+        <v>0</v>
+      </c>
+      <c r="T2" s="8">
         <v>0.1</v>
       </c>
       <c r="U2" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.2">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="7" spans="1:21" x14ac:dyDescent="0.25">
       <c r="F7"/>
     </row>
-    <row r="8" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:21" x14ac:dyDescent="0.25">
       <c r="F8"/>
     </row>
-    <row r="9" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:21" x14ac:dyDescent="0.25">
       <c r="F9"/>
     </row>
-    <row r="10" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:21" x14ac:dyDescent="0.25">
       <c r="F10"/>
     </row>
-    <row r="11" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:21" x14ac:dyDescent="0.25">
       <c r="F11"/>
     </row>
-    <row r="12" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:21" x14ac:dyDescent="0.25">
       <c r="F12"/>
     </row>
-    <row r="13" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:21" x14ac:dyDescent="0.25">
       <c r="F13"/>
     </row>
-    <row r="14" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:21" x14ac:dyDescent="0.25">
       <c r="F14"/>
     </row>
-    <row r="15" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:21" x14ac:dyDescent="0.25">
       <c r="F15"/>
     </row>
-    <row r="16" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:21" x14ac:dyDescent="0.25">
       <c r="F16"/>
     </row>
   </sheetData>
@@ -3221,140 +3225,140 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
   <dimension ref="A1:AF3"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="66.6640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="66.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.5" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.42578125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="16" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="19.83203125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.5" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="17.33203125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.6640625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="17.5" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="16.33203125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="17.33203125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="13.1640625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="16.33203125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="13.83203125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="15.83203125" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="11.5" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.6640625" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="22.5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="17.28515625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="16.28515625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="17.28515625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="16.28515625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="13.85546875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="15.85546875" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="11.42578125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.7109375" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="22.42578125" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="12" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="15.83203125" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="16.1640625" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="18.5" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="16.83203125" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="13.33203125" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="18.5" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="13.33203125" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="18.5" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="12.33203125" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="12.1640625" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="63.6640625" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="15.85546875" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="16.140625" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="18.42578125" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="16.85546875" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="18.42578125" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="18.42578125" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="12.28515625" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="63.7109375" bestFit="1" customWidth="1"/>
     <col min="32" max="32" width="14" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:32" s="12" customFormat="1" ht="59.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="11" t="s">
+    <row r="1" spans="1:32" s="11" customFormat="1" ht="59.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="11" t="s">
+      <c r="B1" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="C1" s="11" t="s">
+      <c r="C1" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="D1" s="11" t="s">
+      <c r="D1" s="10" t="s">
         <v>86</v>
       </c>
-      <c r="E1" s="11" t="s">
+      <c r="E1" s="10" t="s">
+        <v>163</v>
+      </c>
+      <c r="F1" s="23" t="s">
         <v>164</v>
       </c>
-      <c r="F1" s="25" t="s">
-        <v>165</v>
-      </c>
-      <c r="G1" s="14" t="s">
+      <c r="G1" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="H1" s="13" t="s">
+      <c r="H1" s="12" t="s">
         <v>68</v>
       </c>
-      <c r="I1" s="13" t="s">
+      <c r="I1" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="J1" s="26" t="s">
+      <c r="J1" s="24" t="s">
+        <v>97</v>
+      </c>
+      <c r="K1" s="24" t="s">
         <v>98</v>
       </c>
-      <c r="K1" s="26" t="s">
-        <v>99</v>
-      </c>
-      <c r="L1" s="26" t="s">
+      <c r="L1" s="24" t="s">
+        <v>206</v>
+      </c>
+      <c r="M1" s="25" t="s">
+        <v>76</v>
+      </c>
+      <c r="N1" s="25" t="s">
+        <v>77</v>
+      </c>
+      <c r="O1" s="25" t="s">
+        <v>17</v>
+      </c>
+      <c r="P1" s="26" t="s">
+        <v>78</v>
+      </c>
+      <c r="Q1" s="26" t="s">
+        <v>79</v>
+      </c>
+      <c r="R1" s="26" t="s">
+        <v>18</v>
+      </c>
+      <c r="S1" s="25" t="s">
+        <v>207</v>
+      </c>
+      <c r="T1" s="25" t="s">
         <v>208</v>
       </c>
-      <c r="M1" s="27" t="s">
-        <v>76</v>
-      </c>
-      <c r="N1" s="27" t="s">
-        <v>77</v>
-      </c>
-      <c r="O1" s="27" t="s">
-        <v>17</v>
-      </c>
-      <c r="P1" s="28" t="s">
-        <v>78</v>
-      </c>
-      <c r="Q1" s="28" t="s">
-        <v>79</v>
-      </c>
-      <c r="R1" s="28" t="s">
-        <v>18</v>
-      </c>
-      <c r="S1" s="27" t="s">
+      <c r="U1" s="25" t="s">
         <v>209</v>
       </c>
-      <c r="T1" s="27" t="s">
+      <c r="V1" s="26" t="s">
         <v>210</v>
       </c>
-      <c r="U1" s="27" t="s">
+      <c r="W1" s="26" t="s">
         <v>211</v>
       </c>
-      <c r="V1" s="28" t="s">
+      <c r="X1" s="26" t="s">
         <v>212</v>
       </c>
-      <c r="W1" s="28" t="s">
-        <v>213</v>
-      </c>
-      <c r="X1" s="28" t="s">
-        <v>214</v>
-      </c>
-      <c r="Y1" s="29" t="s">
+      <c r="Y1" s="27" t="s">
+        <v>219</v>
+      </c>
+      <c r="Z1" s="27" t="s">
+        <v>220</v>
+      </c>
+      <c r="AA1" s="27" t="s">
         <v>221</v>
       </c>
-      <c r="Z1" s="29" t="s">
+      <c r="AB1" s="27" t="s">
         <v>222</v>
       </c>
-      <c r="AA1" s="29" t="s">
+      <c r="AC1" s="27" t="s">
         <v>223</v>
       </c>
-      <c r="AB1" s="29" t="s">
+      <c r="AD1" s="27" t="s">
         <v>224</v>
       </c>
-      <c r="AC1" s="29" t="s">
-        <v>225</v>
-      </c>
-      <c r="AD1" s="29" t="s">
-        <v>226</v>
-      </c>
-      <c r="AE1" s="11" t="s">
-        <v>190</v>
-      </c>
-      <c r="AF1" s="11" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="2" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AE1" s="10" t="s">
+        <v>189</v>
+      </c>
+      <c r="AF1" s="10" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="2" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B2" t="s">
         <v>69</v>
@@ -3362,7 +3366,7 @@
       <c r="C2" t="s">
         <v>27</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="D2" s="3" t="s">
         <v>29</v>
       </c>
       <c r="E2" t="s">
@@ -3371,13 +3375,13 @@
       <c r="F2" t="s">
         <v>63</v>
       </c>
-      <c r="G2" s="8">
+      <c r="G2" s="7">
         <v>50</v>
       </c>
-      <c r="H2" s="8">
+      <c r="H2" s="7">
         <v>365</v>
       </c>
-      <c r="I2" s="8">
+      <c r="I2" s="7">
         <v>4.3276E-3</v>
       </c>
       <c r="J2">
@@ -3389,70 +3393,70 @@
       <c r="L2" t="b">
         <v>1</v>
       </c>
-      <c r="M2" s="30">
-        <v>0</v>
-      </c>
-      <c r="N2" s="30">
+      <c r="M2" s="28">
+        <v>0</v>
+      </c>
+      <c r="N2" s="28">
         <v>365</v>
       </c>
-      <c r="O2" s="30">
+      <c r="O2" s="28">
         <v>0.34166999999999997</v>
       </c>
-      <c r="P2" s="31">
-        <v>0</v>
-      </c>
-      <c r="Q2" s="31">
+      <c r="P2" s="29">
+        <v>0</v>
+      </c>
+      <c r="Q2" s="29">
         <v>365</v>
       </c>
-      <c r="R2" s="31">
+      <c r="R2" s="29">
         <v>0.14960999999999999</v>
       </c>
-      <c r="S2" s="30">
+      <c r="S2" s="28">
         <v>3</v>
       </c>
-      <c r="T2" s="30">
+      <c r="T2" s="28">
         <v>7</v>
       </c>
-      <c r="U2" s="30">
+      <c r="U2" s="28">
         <v>0.34166999999999997</v>
       </c>
-      <c r="V2" s="31">
+      <c r="V2" s="29">
         <v>7</v>
       </c>
-      <c r="W2" s="31">
+      <c r="W2" s="29">
         <v>7</v>
       </c>
-      <c r="X2" s="31">
+      <c r="X2" s="29">
         <v>0.14960999999999999</v>
       </c>
-      <c r="Y2" s="32">
-        <v>1</v>
-      </c>
-      <c r="Z2" s="32">
+      <c r="Y2" s="30">
+        <v>1</v>
+      </c>
+      <c r="Z2" s="30">
         <v>2</v>
       </c>
-      <c r="AA2" s="32">
+      <c r="AA2" s="30">
         <v>0.5</v>
       </c>
-      <c r="AB2" s="56">
+      <c r="AB2" s="54">
         <v>3000</v>
       </c>
-      <c r="AC2" s="56">
+      <c r="AC2" s="54">
         <v>10000</v>
       </c>
-      <c r="AD2" s="56">
+      <c r="AD2" s="54">
         <v>5000</v>
       </c>
       <c r="AE2" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="AF2" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="3" spans="1:32" x14ac:dyDescent="0.2">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="3" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B3" t="s">
         <v>69</v>
@@ -3460,7 +3464,7 @@
       <c r="C3" t="s">
         <v>28</v>
       </c>
-      <c r="D3" s="4" t="s">
+      <c r="D3" s="3" t="s">
         <v>29</v>
       </c>
       <c r="E3" t="s">
@@ -3469,13 +3473,13 @@
       <c r="F3" t="s">
         <v>62</v>
       </c>
-      <c r="G3" s="8">
+      <c r="G3" s="7">
         <v>50</v>
       </c>
-      <c r="H3" s="8">
+      <c r="H3" s="7">
         <v>365</v>
       </c>
-      <c r="I3" s="8">
+      <c r="I3" s="7">
         <v>4.3276E-3</v>
       </c>
       <c r="J3">
@@ -3487,65 +3491,65 @@
       <c r="L3" t="b">
         <v>1</v>
       </c>
-      <c r="M3" s="30">
-        <v>0</v>
-      </c>
-      <c r="N3" s="30">
+      <c r="M3" s="28">
+        <v>0</v>
+      </c>
+      <c r="N3" s="28">
         <v>365</v>
       </c>
-      <c r="O3" s="30">
+      <c r="O3" s="28">
         <v>0.34166999999999997</v>
       </c>
-      <c r="P3" s="31">
-        <v>0</v>
-      </c>
-      <c r="Q3" s="31">
+      <c r="P3" s="29">
+        <v>0</v>
+      </c>
+      <c r="Q3" s="29">
         <v>365</v>
       </c>
-      <c r="R3" s="31">
+      <c r="R3" s="29">
         <v>0.14960999999999999</v>
       </c>
-      <c r="S3" s="30">
+      <c r="S3" s="28">
         <v>3</v>
       </c>
-      <c r="T3" s="30">
+      <c r="T3" s="28">
         <v>7</v>
       </c>
-      <c r="U3" s="30">
+      <c r="U3" s="28">
         <v>0.34166999999999997</v>
       </c>
-      <c r="V3" s="31">
+      <c r="V3" s="29">
         <v>7</v>
       </c>
-      <c r="W3" s="31">
+      <c r="W3" s="29">
         <v>7</v>
       </c>
-      <c r="X3" s="31">
+      <c r="X3" s="29">
         <v>0.14960999999999999</v>
       </c>
-      <c r="Y3" s="32">
-        <v>1</v>
-      </c>
-      <c r="Z3" s="32">
+      <c r="Y3" s="30">
+        <v>1</v>
+      </c>
+      <c r="Z3" s="30">
         <v>2</v>
       </c>
-      <c r="AA3" s="32">
+      <c r="AA3" s="30">
         <v>0.5</v>
       </c>
-      <c r="AB3" s="56">
+      <c r="AB3" s="54">
         <v>3000</v>
       </c>
-      <c r="AC3" s="56">
+      <c r="AC3" s="54">
         <v>10000</v>
       </c>
-      <c r="AD3" s="56">
+      <c r="AD3" s="54">
         <v>5000</v>
       </c>
       <c r="AE3" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="AF3" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
     </row>
   </sheetData>
@@ -3556,1524 +3560,1578 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0C00-000000000000}">
-  <dimension ref="A1:BB9"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:BD9"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="8.6640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="7.1640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.6640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="11.5" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.6640625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.33203125" customWidth="1"/>
-    <col min="8" max="8" width="11.5" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.5" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="9.5" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="11.5" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="11.5" customWidth="1"/>
-    <col min="13" max="13" width="14.33203125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="16.5" style="4" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="8.33203125" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="11.1640625" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="9.83203125" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="10.5" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="11.33203125" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="11.5" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="10.33203125" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="11.5" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="13.1640625" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.33203125" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.5" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="10.6640625" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="10.5" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="10.83203125" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="12.5" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="7.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="11.42578125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.7109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.28515625" customWidth="1"/>
+    <col min="8" max="8" width="11.42578125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="11.42578125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="11.42578125" customWidth="1"/>
+    <col min="13" max="13" width="14.28515625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="16.42578125" style="3" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="8.28515625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="11.140625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="11.42578125" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="10.28515625" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="11.42578125" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.28515625" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.42578125" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="27" max="28" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="12.42578125" bestFit="1" customWidth="1"/>
     <col min="31" max="31" width="15" bestFit="1" customWidth="1"/>
     <col min="32" max="32" width="11" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="15.6640625" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="11.5" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="15.7109375" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="11.42578125" bestFit="1" customWidth="1"/>
     <col min="36" max="36" width="10" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="10.33203125" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="9.5" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="10.28515625" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="9.42578125" bestFit="1" customWidth="1"/>
     <col min="39" max="39" width="15" customWidth="1"/>
-    <col min="40" max="41" width="13.83203125" bestFit="1" customWidth="1"/>
+    <col min="40" max="41" width="13.85546875" bestFit="1" customWidth="1"/>
     <col min="42" max="42" width="10" bestFit="1" customWidth="1"/>
-    <col min="43" max="43" width="11.6640625" bestFit="1" customWidth="1"/>
-    <col min="44" max="45" width="10.6640625" bestFit="1" customWidth="1"/>
-    <col min="46" max="46" width="9.6640625" bestFit="1" customWidth="1"/>
-    <col min="47" max="47" width="17.5" bestFit="1" customWidth="1"/>
+    <col min="43" max="43" width="11.7109375" bestFit="1" customWidth="1"/>
+    <col min="44" max="45" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="46" max="46" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="47" max="47" width="17.42578125" bestFit="1" customWidth="1"/>
     <col min="48" max="49" width="15" bestFit="1" customWidth="1"/>
     <col min="50" max="50" width="14" bestFit="1" customWidth="1"/>
     <col min="51" max="51" width="16" bestFit="1" customWidth="1"/>
-    <col min="52" max="53" width="47.1640625" bestFit="1" customWidth="1"/>
-    <col min="54" max="54" width="9.83203125" bestFit="1" customWidth="1"/>
+    <col min="52" max="53" width="47.140625" bestFit="1" customWidth="1"/>
+    <col min="54" max="54" width="9.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:54" s="18" customFormat="1" ht="63" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="16" t="s">
+    <row r="1" spans="1:56" s="61" customFormat="1" ht="120" x14ac:dyDescent="0.25">
+      <c r="A1" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="16" t="s">
+      <c r="B1" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="C1" s="17" t="s">
+      <c r="C1" s="59" t="s">
+        <v>225</v>
+      </c>
+      <c r="D1" s="60" t="s">
+        <v>226</v>
+      </c>
+      <c r="E1" s="12" t="s">
+        <v>68</v>
+      </c>
+      <c r="F1" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="D1" s="17" t="s">
-        <v>68</v>
-      </c>
-      <c r="E1" s="17" t="s">
+      <c r="G1" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="F1" s="23" t="s">
-        <v>86</v>
-      </c>
-      <c r="G1" s="33" t="s">
+      <c r="H1" s="10" t="s">
+        <v>188</v>
+      </c>
+      <c r="I1" s="21" t="s">
+        <v>227</v>
+      </c>
+      <c r="J1" s="32" t="s">
         <v>166</v>
       </c>
-      <c r="H1" s="34" t="s">
+      <c r="K1" s="38" t="s">
+        <v>214</v>
+      </c>
+      <c r="L1" s="38" t="s">
+        <v>215</v>
+      </c>
+      <c r="M1" s="10" t="s">
+        <v>184</v>
+      </c>
+      <c r="N1" s="10" t="s">
+        <v>185</v>
+      </c>
+      <c r="O1" s="33" t="s">
+        <v>131</v>
+      </c>
+      <c r="P1" s="31" t="s">
+        <v>165</v>
+      </c>
+      <c r="Q1" s="35" t="s">
+        <v>134</v>
+      </c>
+      <c r="R1" s="32" t="s">
+        <v>11</v>
+      </c>
+      <c r="S1" s="32" t="s">
+        <v>12</v>
+      </c>
+      <c r="T1" s="34" t="s">
+        <v>132</v>
+      </c>
+      <c r="U1" s="34" t="s">
+        <v>133</v>
+      </c>
+      <c r="V1" s="34" t="s">
+        <v>186</v>
+      </c>
+      <c r="W1" s="34" t="s">
+        <v>187</v>
+      </c>
+      <c r="X1" s="27" t="s">
+        <v>135</v>
+      </c>
+      <c r="Y1" s="27" t="s">
+        <v>136</v>
+      </c>
+      <c r="Z1" s="10" t="s">
+        <v>137</v>
+      </c>
+      <c r="AA1" s="10" t="s">
+        <v>138</v>
+      </c>
+      <c r="AB1" s="36" t="s">
+        <v>139</v>
+      </c>
+      <c r="AC1" s="37" t="s">
+        <v>140</v>
+      </c>
+      <c r="AD1" s="37" t="s">
+        <v>141</v>
+      </c>
+      <c r="AE1" s="37" t="s">
+        <v>13</v>
+      </c>
+      <c r="AF1" s="10" t="s">
+        <v>167</v>
+      </c>
+      <c r="AG1" s="39" t="s">
+        <v>142</v>
+      </c>
+      <c r="AH1" s="25" t="s">
+        <v>80</v>
+      </c>
+      <c r="AI1" s="25" t="s">
+        <v>81</v>
+      </c>
+      <c r="AJ1" s="39" t="s">
+        <v>14</v>
+      </c>
+      <c r="AK1" s="40" t="s">
+        <v>143</v>
+      </c>
+      <c r="AL1" s="41" t="s">
+        <v>82</v>
+      </c>
+      <c r="AM1" s="40" t="s">
+        <v>83</v>
+      </c>
+      <c r="AN1" s="41" t="s">
+        <v>30</v>
+      </c>
+      <c r="AO1" s="42" t="s">
+        <v>144</v>
+      </c>
+      <c r="AP1" s="43" t="s">
+        <v>84</v>
+      </c>
+      <c r="AQ1" s="43" t="s">
+        <v>85</v>
+      </c>
+      <c r="AR1" s="43" t="s">
+        <v>31</v>
+      </c>
+      <c r="AS1" s="44" t="s">
+        <v>145</v>
+      </c>
+      <c r="AT1" s="44" t="s">
+        <v>146</v>
+      </c>
+      <c r="AU1" s="44" t="s">
+        <v>147</v>
+      </c>
+      <c r="AV1" s="44" t="s">
+        <v>148</v>
+      </c>
+      <c r="AW1" s="45" t="s">
+        <v>149</v>
+      </c>
+      <c r="AX1" s="46" t="s">
+        <v>150</v>
+      </c>
+      <c r="AY1" s="46" t="s">
+        <v>151</v>
+      </c>
+      <c r="AZ1" s="46" t="s">
+        <v>152</v>
+      </c>
+      <c r="BA1" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="BB1" s="38" t="s">
         <v>189</v>
       </c>
-      <c r="I1" s="34" t="s">
-        <v>167</v>
-      </c>
-      <c r="J1" s="2" t="s">
-        <v>185</v>
-      </c>
-      <c r="K1" s="2" t="s">
-        <v>216</v>
-      </c>
-      <c r="L1" s="40" t="s">
-        <v>217</v>
-      </c>
-      <c r="M1" s="2" t="s">
-        <v>186</v>
-      </c>
-      <c r="N1" s="35" t="s">
-        <v>132</v>
-      </c>
-      <c r="O1" s="34" t="s">
-        <v>11</v>
-      </c>
-      <c r="P1" s="34" t="s">
-        <v>12</v>
-      </c>
-      <c r="Q1" s="36" t="s">
-        <v>133</v>
-      </c>
-      <c r="R1" s="36" t="s">
-        <v>134</v>
-      </c>
-      <c r="S1" s="36" t="s">
-        <v>187</v>
-      </c>
-      <c r="T1" s="36" t="s">
-        <v>188</v>
-      </c>
-      <c r="U1" s="37" t="s">
-        <v>135</v>
-      </c>
-      <c r="V1" s="29" t="s">
-        <v>136</v>
-      </c>
-      <c r="W1" s="29" t="s">
-        <v>137</v>
-      </c>
-      <c r="X1" s="11" t="s">
-        <v>138</v>
-      </c>
-      <c r="Y1" s="11" t="s">
-        <v>139</v>
-      </c>
-      <c r="Z1" s="38" t="s">
-        <v>140</v>
-      </c>
-      <c r="AA1" s="39" t="s">
-        <v>141</v>
-      </c>
-      <c r="AB1" s="39" t="s">
-        <v>142</v>
-      </c>
-      <c r="AC1" s="39" t="s">
-        <v>13</v>
-      </c>
-      <c r="AD1" s="11" t="s">
-        <v>168</v>
-      </c>
-      <c r="AE1" s="41" t="s">
-        <v>143</v>
-      </c>
-      <c r="AF1" s="27" t="s">
-        <v>80</v>
-      </c>
-      <c r="AG1" s="27" t="s">
-        <v>81</v>
-      </c>
-      <c r="AH1" s="41" t="s">
-        <v>14</v>
-      </c>
-      <c r="AI1" s="42" t="s">
-        <v>144</v>
-      </c>
-      <c r="AJ1" s="43" t="s">
-        <v>82</v>
-      </c>
-      <c r="AK1" s="42" t="s">
-        <v>83</v>
-      </c>
-      <c r="AL1" s="43" t="s">
-        <v>30</v>
-      </c>
-      <c r="AM1" s="44" t="s">
-        <v>145</v>
-      </c>
-      <c r="AN1" s="45" t="s">
-        <v>84</v>
-      </c>
-      <c r="AO1" s="45" t="s">
-        <v>85</v>
-      </c>
-      <c r="AP1" s="45" t="s">
-        <v>31</v>
-      </c>
-      <c r="AQ1" s="46" t="s">
-        <v>146</v>
-      </c>
-      <c r="AR1" s="46" t="s">
-        <v>147</v>
-      </c>
-      <c r="AS1" s="46" t="s">
-        <v>148</v>
-      </c>
-      <c r="AT1" s="46" t="s">
-        <v>149</v>
-      </c>
-      <c r="AU1" s="47" t="s">
-        <v>150</v>
-      </c>
-      <c r="AV1" s="48" t="s">
-        <v>151</v>
-      </c>
-      <c r="AW1" s="48" t="s">
-        <v>152</v>
-      </c>
-      <c r="AX1" s="48" t="s">
-        <v>153</v>
-      </c>
-      <c r="AY1" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="AZ1" s="40" t="s">
-        <v>190</v>
-      </c>
-      <c r="BA1" s="49" t="s">
+      <c r="BC1" s="47" t="s">
         <v>89</v>
       </c>
-      <c r="BB1" s="11" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="2" spans="1:54" x14ac:dyDescent="0.2">
+      <c r="BD1" s="10" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="2" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B2" t="s">
-        <v>111</v>
-      </c>
-      <c r="C2" s="8">
+        <v>110</v>
+      </c>
+      <c r="C2" t="b">
+        <v>0</v>
+      </c>
+      <c r="D2" t="s">
+        <v>228</v>
+      </c>
+      <c r="E2" s="7">
         <v>45</v>
       </c>
-      <c r="D2" s="8">
+      <c r="F2" s="7">
         <v>365</v>
       </c>
-      <c r="E2" s="8">
+      <c r="G2" s="7">
         <v>0.02</v>
       </c>
-      <c r="F2" s="50" t="s">
+      <c r="H2" s="49">
+        <v>32</v>
+      </c>
+      <c r="I2" s="48" t="s">
         <v>29</v>
       </c>
-      <c r="G2" s="24" t="s">
-        <v>215</v>
-      </c>
-      <c r="H2" s="51">
-        <v>32</v>
-      </c>
-      <c r="I2" s="15" t="s">
+      <c r="J2" s="14" t="s">
         <v>88</v>
-      </c>
-      <c r="J2">
-        <v>0.35</v>
       </c>
       <c r="K2">
         <v>0.7</v>
       </c>
-      <c r="M2" t="s">
-        <v>218</v>
-      </c>
-      <c r="N2" s="51" t="s">
-        <v>156</v>
-      </c>
-      <c r="O2" s="15">
+      <c r="M2">
+        <v>0.35</v>
+      </c>
+      <c r="N2" t="s">
+        <v>216</v>
+      </c>
+      <c r="O2" s="49" t="s">
+        <v>155</v>
+      </c>
+      <c r="P2" s="22" t="s">
+        <v>213</v>
+      </c>
+      <c r="Q2" s="51" t="s">
+        <v>153</v>
+      </c>
+      <c r="R2" s="14">
         <v>0.9</v>
       </c>
-      <c r="P2" s="15">
+      <c r="S2" s="14">
         <v>3.5000000000000003E-2</v>
       </c>
-      <c r="Q2" s="52">
+      <c r="T2" s="50">
         <v>0.9</v>
       </c>
-      <c r="R2" s="52">
+      <c r="U2" s="50">
         <v>0.71</v>
       </c>
-      <c r="S2" s="52">
+      <c r="V2" s="50">
         <f>24*21</f>
         <v>504</v>
       </c>
-      <c r="T2" s="52">
+      <c r="W2" s="50">
         <f>24*7*6</f>
         <v>1008</v>
       </c>
-      <c r="U2" s="53" t="s">
+      <c r="X2" s="30">
+        <v>3</v>
+      </c>
+      <c r="Y2" s="30">
+        <v>0</v>
+      </c>
+      <c r="Z2">
+        <v>90</v>
+      </c>
+      <c r="AA2">
+        <v>100</v>
+      </c>
+      <c r="AB2" s="8">
+        <v>1</v>
+      </c>
+      <c r="AC2" s="8">
+        <v>0</v>
+      </c>
+      <c r="AD2" s="8">
+        <v>182.5</v>
+      </c>
+      <c r="AE2" s="8">
+        <v>0.21634999999999999</v>
+      </c>
+      <c r="AF2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG2" s="28">
+        <v>1</v>
+      </c>
+      <c r="AH2" s="28">
+        <v>0</v>
+      </c>
+      <c r="AI2" s="28">
+        <v>182.5</v>
+      </c>
+      <c r="AJ2" s="28">
+        <v>8.3141000000000007E-2</v>
+      </c>
+      <c r="AK2" s="6">
+        <v>1</v>
+      </c>
+      <c r="AL2" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM2" s="6">
+        <v>182.5</v>
+      </c>
+      <c r="AN2" s="6">
+        <v>0.47815999999999997</v>
+      </c>
+      <c r="AO2" s="52">
+        <v>1</v>
+      </c>
+      <c r="AP2" s="52">
+        <v>0</v>
+      </c>
+      <c r="AQ2" s="52">
+        <v>121.66670000000001</v>
+      </c>
+      <c r="AR2" s="52">
+        <v>2.6738E-3</v>
+      </c>
+      <c r="AS2" s="53">
+        <v>1</v>
+      </c>
+      <c r="AT2" s="53">
+        <v>0</v>
+      </c>
+      <c r="AU2" s="53">
+        <v>182.5</v>
+      </c>
+      <c r="AV2" s="53">
+        <v>0.11268</v>
+      </c>
+      <c r="AW2" s="9">
+        <v>1</v>
+      </c>
+      <c r="AX2" s="9">
+        <v>0</v>
+      </c>
+      <c r="AY2" s="9">
+        <v>121.66670000000001</v>
+      </c>
+      <c r="AZ2" s="9">
+        <v>2.7855000000000002E-3</v>
+      </c>
+      <c r="BA2" t="s">
         <v>154</v>
       </c>
-      <c r="V2" s="32">
-        <v>3</v>
-      </c>
-      <c r="W2" s="32">
-        <v>0</v>
-      </c>
-      <c r="X2">
-        <v>90</v>
-      </c>
-      <c r="Y2">
-        <v>100</v>
-      </c>
-      <c r="Z2" s="9">
-        <v>1</v>
-      </c>
-      <c r="AA2" s="9">
-        <v>0</v>
-      </c>
-      <c r="AB2" s="9">
-        <v>182.5</v>
-      </c>
-      <c r="AC2" s="9">
-        <v>0.21634999999999999</v>
-      </c>
-      <c r="AD2" t="b">
-        <v>1</v>
-      </c>
-      <c r="AE2" s="30">
-        <v>1</v>
-      </c>
-      <c r="AF2" s="30">
-        <v>0</v>
-      </c>
-      <c r="AG2" s="30">
-        <v>182.5</v>
-      </c>
-      <c r="AH2" s="30">
-        <v>8.3141000000000007E-2</v>
-      </c>
-      <c r="AI2" s="7">
-        <v>1</v>
-      </c>
-      <c r="AJ2" s="7">
-        <v>0</v>
-      </c>
-      <c r="AK2" s="7">
-        <v>182.5</v>
-      </c>
-      <c r="AL2" s="7">
-        <v>0.47815999999999997</v>
-      </c>
-      <c r="AM2" s="54">
-        <v>1</v>
-      </c>
-      <c r="AN2" s="54">
-        <v>0</v>
-      </c>
-      <c r="AO2" s="54">
-        <v>121.66670000000001</v>
-      </c>
-      <c r="AP2" s="54">
-        <v>2.6738E-3</v>
-      </c>
-      <c r="AQ2" s="55">
-        <v>1</v>
-      </c>
-      <c r="AR2" s="55">
-        <v>0</v>
-      </c>
-      <c r="AS2" s="55">
-        <v>182.5</v>
-      </c>
-      <c r="AT2" s="55">
-        <v>0.11268</v>
-      </c>
-      <c r="AU2" s="10">
-        <v>1</v>
-      </c>
-      <c r="AV2" s="10">
-        <v>0</v>
-      </c>
-      <c r="AW2" s="10">
-        <v>121.66670000000001</v>
-      </c>
-      <c r="AX2" s="10">
-        <v>2.7855000000000002E-3</v>
-      </c>
-      <c r="AY2" t="s">
-        <v>155</v>
-      </c>
-      <c r="AZ2" t="s">
-        <v>193</v>
-      </c>
-      <c r="BA2" t="s">
-        <v>193</v>
-      </c>
       <c r="BB2" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="3" spans="1:54" x14ac:dyDescent="0.2">
+        <v>192</v>
+      </c>
+      <c r="BC2" t="s">
+        <v>192</v>
+      </c>
+      <c r="BD2" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="3" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B3" t="s">
-        <v>112</v>
-      </c>
-      <c r="C3" s="8">
+        <v>111</v>
+      </c>
+      <c r="C3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D3" t="s">
+        <v>228</v>
+      </c>
+      <c r="E3" s="7">
         <v>45</v>
       </c>
-      <c r="D3" s="8">
+      <c r="F3" s="7">
         <v>365</v>
       </c>
-      <c r="E3" s="8">
+      <c r="G3" s="7">
         <v>0.02</v>
       </c>
-      <c r="F3" s="50" t="s">
+      <c r="H3" s="49">
+        <v>32</v>
+      </c>
+      <c r="I3" s="48" t="s">
         <v>29</v>
       </c>
-      <c r="G3" s="24" t="s">
-        <v>215</v>
-      </c>
-      <c r="H3" s="51">
-        <v>32</v>
-      </c>
-      <c r="I3" s="15" t="s">
+      <c r="J3" s="14" t="s">
         <v>88</v>
-      </c>
-      <c r="J3">
-        <v>0.35</v>
       </c>
       <c r="K3">
         <v>0.7</v>
       </c>
-      <c r="M3" t="s">
-        <v>218</v>
-      </c>
-      <c r="N3" s="51" t="s">
-        <v>156</v>
-      </c>
-      <c r="O3" s="15">
+      <c r="M3">
+        <v>0.35</v>
+      </c>
+      <c r="N3" t="s">
+        <v>216</v>
+      </c>
+      <c r="O3" s="49" t="s">
+        <v>155</v>
+      </c>
+      <c r="P3" s="22" t="s">
+        <v>213</v>
+      </c>
+      <c r="Q3" s="51" t="s">
+        <v>153</v>
+      </c>
+      <c r="R3" s="14">
         <v>0.9</v>
       </c>
-      <c r="P3" s="15">
+      <c r="S3" s="14">
         <v>3.5000000000000003E-2</v>
       </c>
-      <c r="Q3" s="52">
+      <c r="T3" s="50">
         <v>0.9</v>
       </c>
-      <c r="R3" s="52">
+      <c r="U3" s="50">
         <v>0.71</v>
       </c>
-      <c r="S3" s="52">
+      <c r="V3" s="50">
         <f>24*21</f>
         <v>504</v>
       </c>
-      <c r="T3" s="52">
+      <c r="W3" s="50">
         <f>24*7*6</f>
         <v>1008</v>
       </c>
-      <c r="U3" s="53" t="s">
+      <c r="X3" s="30">
+        <v>3</v>
+      </c>
+      <c r="Y3" s="30">
+        <v>0</v>
+      </c>
+      <c r="Z3">
+        <v>90</v>
+      </c>
+      <c r="AA3">
+        <v>100</v>
+      </c>
+      <c r="AB3" s="8">
+        <v>1</v>
+      </c>
+      <c r="AC3" s="8">
+        <v>0</v>
+      </c>
+      <c r="AD3" s="8">
+        <v>182.5</v>
+      </c>
+      <c r="AE3" s="8">
+        <v>0.21634999999999999</v>
+      </c>
+      <c r="AF3" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG3" s="28">
+        <v>1</v>
+      </c>
+      <c r="AH3" s="28">
+        <v>0</v>
+      </c>
+      <c r="AI3" s="28">
+        <v>182.5</v>
+      </c>
+      <c r="AJ3" s="28">
+        <v>8.3141000000000007E-2</v>
+      </c>
+      <c r="AK3" s="6">
+        <v>1</v>
+      </c>
+      <c r="AL3" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM3" s="6">
+        <v>182.5</v>
+      </c>
+      <c r="AN3" s="6">
+        <v>0.47815999999999997</v>
+      </c>
+      <c r="AO3" s="52">
+        <v>1</v>
+      </c>
+      <c r="AP3" s="52">
+        <v>0</v>
+      </c>
+      <c r="AQ3" s="52">
+        <v>121.66670000000001</v>
+      </c>
+      <c r="AR3" s="52">
+        <v>2.6738E-3</v>
+      </c>
+      <c r="AS3" s="53">
+        <v>1</v>
+      </c>
+      <c r="AT3" s="53">
+        <v>0</v>
+      </c>
+      <c r="AU3" s="53">
+        <v>182.5</v>
+      </c>
+      <c r="AV3" s="53">
+        <v>0.11268</v>
+      </c>
+      <c r="AW3" s="9">
+        <v>1</v>
+      </c>
+      <c r="AX3" s="9">
+        <v>0</v>
+      </c>
+      <c r="AY3" s="9">
+        <v>121.66670000000001</v>
+      </c>
+      <c r="AZ3" s="9">
+        <v>2.7855000000000002E-3</v>
+      </c>
+      <c r="BA3" t="s">
         <v>154</v>
       </c>
-      <c r="V3" s="32">
-        <v>3</v>
-      </c>
-      <c r="W3" s="32">
-        <v>0</v>
-      </c>
-      <c r="X3">
-        <v>90</v>
-      </c>
-      <c r="Y3">
-        <v>100</v>
-      </c>
-      <c r="Z3" s="9">
-        <v>1</v>
-      </c>
-      <c r="AA3" s="9">
-        <v>0</v>
-      </c>
-      <c r="AB3" s="9">
-        <v>182.5</v>
-      </c>
-      <c r="AC3" s="9">
-        <v>0.21634999999999999</v>
-      </c>
-      <c r="AD3" t="b">
-        <v>1</v>
-      </c>
-      <c r="AE3" s="30">
-        <v>1</v>
-      </c>
-      <c r="AF3" s="30">
-        <v>0</v>
-      </c>
-      <c r="AG3" s="30">
-        <v>182.5</v>
-      </c>
-      <c r="AH3" s="30">
-        <v>8.3141000000000007E-2</v>
-      </c>
-      <c r="AI3" s="7">
-        <v>1</v>
-      </c>
-      <c r="AJ3" s="7">
-        <v>0</v>
-      </c>
-      <c r="AK3" s="7">
-        <v>182.5</v>
-      </c>
-      <c r="AL3" s="7">
-        <v>0.47815999999999997</v>
-      </c>
-      <c r="AM3" s="54">
-        <v>1</v>
-      </c>
-      <c r="AN3" s="54">
-        <v>0</v>
-      </c>
-      <c r="AO3" s="54">
-        <v>121.66670000000001</v>
-      </c>
-      <c r="AP3" s="54">
-        <v>2.6738E-3</v>
-      </c>
-      <c r="AQ3" s="55">
-        <v>1</v>
-      </c>
-      <c r="AR3" s="55">
-        <v>0</v>
-      </c>
-      <c r="AS3" s="55">
-        <v>182.5</v>
-      </c>
-      <c r="AT3" s="55">
-        <v>0.11268</v>
-      </c>
-      <c r="AU3" s="10">
-        <v>1</v>
-      </c>
-      <c r="AV3" s="10">
-        <v>0</v>
-      </c>
-      <c r="AW3" s="10">
-        <v>121.66670000000001</v>
-      </c>
-      <c r="AX3" s="10">
-        <v>2.7855000000000002E-3</v>
-      </c>
-      <c r="AY3" t="s">
-        <v>155</v>
-      </c>
-      <c r="AZ3" t="s">
-        <v>193</v>
-      </c>
-      <c r="BA3" t="s">
-        <v>193</v>
-      </c>
       <c r="BB3" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="4" spans="1:54" x14ac:dyDescent="0.2">
+        <v>192</v>
+      </c>
+      <c r="BC3" t="s">
+        <v>192</v>
+      </c>
+      <c r="BD3" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="4" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B4" t="s">
-        <v>113</v>
-      </c>
-      <c r="C4" s="8">
+        <v>112</v>
+      </c>
+      <c r="C4" t="b">
+        <v>0</v>
+      </c>
+      <c r="D4" t="s">
+        <v>228</v>
+      </c>
+      <c r="E4" s="7">
         <v>45</v>
       </c>
-      <c r="D4" s="8">
+      <c r="F4" s="7">
         <v>365</v>
       </c>
-      <c r="E4" s="8">
+      <c r="G4" s="7">
         <v>0.02</v>
       </c>
-      <c r="F4" s="50" t="s">
+      <c r="H4" s="49">
+        <v>32</v>
+      </c>
+      <c r="I4" s="48" t="s">
         <v>29</v>
       </c>
-      <c r="G4" s="24" t="s">
-        <v>215</v>
-      </c>
-      <c r="H4" s="51">
-        <v>32</v>
-      </c>
-      <c r="I4" s="15" t="s">
+      <c r="J4" s="14" t="s">
         <v>88</v>
-      </c>
-      <c r="J4">
-        <v>0.35</v>
       </c>
       <c r="K4">
         <v>0.7</v>
       </c>
-      <c r="M4" t="s">
-        <v>218</v>
-      </c>
-      <c r="N4" s="51" t="s">
-        <v>156</v>
-      </c>
-      <c r="O4" s="15">
+      <c r="M4">
+        <v>0.35</v>
+      </c>
+      <c r="N4" t="s">
+        <v>216</v>
+      </c>
+      <c r="O4" s="49" t="s">
+        <v>155</v>
+      </c>
+      <c r="P4" s="22" t="s">
+        <v>213</v>
+      </c>
+      <c r="Q4" s="51" t="s">
+        <v>153</v>
+      </c>
+      <c r="R4" s="14">
         <v>0.9</v>
       </c>
-      <c r="P4" s="15">
+      <c r="S4" s="14">
         <v>3.5000000000000003E-2</v>
       </c>
-      <c r="Q4" s="52">
+      <c r="T4" s="50">
         <v>0.9</v>
       </c>
-      <c r="R4" s="52">
+      <c r="U4" s="50">
         <v>0.71</v>
       </c>
-      <c r="S4" s="52">
-        <f t="shared" ref="S4:S9" si="0">24*21</f>
+      <c r="V4" s="50">
+        <f t="shared" ref="V4:V9" si="0">24*21</f>
         <v>504</v>
       </c>
-      <c r="T4" s="52">
-        <f t="shared" ref="T4:T9" si="1">24*7*6</f>
+      <c r="W4" s="50">
+        <f t="shared" ref="W4:W9" si="1">24*7*6</f>
         <v>1008</v>
       </c>
-      <c r="U4" s="53" t="s">
+      <c r="X4" s="30">
+        <v>3</v>
+      </c>
+      <c r="Y4" s="30">
+        <v>0</v>
+      </c>
+      <c r="Z4">
+        <v>90</v>
+      </c>
+      <c r="AA4">
+        <v>100</v>
+      </c>
+      <c r="AB4" s="8">
+        <v>1</v>
+      </c>
+      <c r="AC4" s="8">
+        <v>0</v>
+      </c>
+      <c r="AD4" s="8">
+        <v>182.5</v>
+      </c>
+      <c r="AE4" s="8">
+        <v>0.21634999999999999</v>
+      </c>
+      <c r="AF4" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG4" s="28">
+        <v>1</v>
+      </c>
+      <c r="AH4" s="28">
+        <v>0</v>
+      </c>
+      <c r="AI4" s="28">
+        <v>182.5</v>
+      </c>
+      <c r="AJ4" s="28">
+        <v>8.3141000000000007E-2</v>
+      </c>
+      <c r="AK4" s="6">
+        <v>1</v>
+      </c>
+      <c r="AL4" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM4" s="6">
+        <v>182.5</v>
+      </c>
+      <c r="AN4" s="6">
+        <v>0.47815999999999997</v>
+      </c>
+      <c r="AO4" s="52">
+        <v>1</v>
+      </c>
+      <c r="AP4" s="52">
+        <v>0</v>
+      </c>
+      <c r="AQ4" s="52">
+        <v>121.66670000000001</v>
+      </c>
+      <c r="AR4" s="52">
+        <v>2.6738E-3</v>
+      </c>
+      <c r="AS4" s="53">
+        <v>1</v>
+      </c>
+      <c r="AT4" s="53">
+        <v>0</v>
+      </c>
+      <c r="AU4" s="53">
+        <v>182.5</v>
+      </c>
+      <c r="AV4" s="53">
+        <v>0.11268</v>
+      </c>
+      <c r="AW4" s="9">
+        <v>1</v>
+      </c>
+      <c r="AX4" s="9">
+        <v>0</v>
+      </c>
+      <c r="AY4" s="9">
+        <v>121.66670000000001</v>
+      </c>
+      <c r="AZ4" s="9">
+        <v>2.7855000000000002E-3</v>
+      </c>
+      <c r="BA4" t="s">
         <v>154</v>
       </c>
-      <c r="V4" s="32">
-        <v>3</v>
-      </c>
-      <c r="W4" s="32">
-        <v>0</v>
-      </c>
-      <c r="X4">
-        <v>90</v>
-      </c>
-      <c r="Y4">
-        <v>100</v>
-      </c>
-      <c r="Z4" s="9">
-        <v>1</v>
-      </c>
-      <c r="AA4" s="9">
-        <v>0</v>
-      </c>
-      <c r="AB4" s="9">
-        <v>182.5</v>
-      </c>
-      <c r="AC4" s="9">
-        <v>0.21634999999999999</v>
-      </c>
-      <c r="AD4" t="b">
-        <v>1</v>
-      </c>
-      <c r="AE4" s="30">
-        <v>1</v>
-      </c>
-      <c r="AF4" s="30">
-        <v>0</v>
-      </c>
-      <c r="AG4" s="30">
-        <v>182.5</v>
-      </c>
-      <c r="AH4" s="30">
-        <v>8.3141000000000007E-2</v>
-      </c>
-      <c r="AI4" s="7">
-        <v>1</v>
-      </c>
-      <c r="AJ4" s="7">
-        <v>0</v>
-      </c>
-      <c r="AK4" s="7">
-        <v>182.5</v>
-      </c>
-      <c r="AL4" s="7">
-        <v>0.47815999999999997</v>
-      </c>
-      <c r="AM4" s="54">
-        <v>1</v>
-      </c>
-      <c r="AN4" s="54">
-        <v>0</v>
-      </c>
-      <c r="AO4" s="54">
-        <v>121.66670000000001</v>
-      </c>
-      <c r="AP4" s="54">
-        <v>2.6738E-3</v>
-      </c>
-      <c r="AQ4" s="55">
-        <v>1</v>
-      </c>
-      <c r="AR4" s="55">
-        <v>0</v>
-      </c>
-      <c r="AS4" s="55">
-        <v>182.5</v>
-      </c>
-      <c r="AT4" s="55">
-        <v>0.11268</v>
-      </c>
-      <c r="AU4" s="10">
-        <v>1</v>
-      </c>
-      <c r="AV4" s="10">
-        <v>0</v>
-      </c>
-      <c r="AW4" s="10">
-        <v>121.66670000000001</v>
-      </c>
-      <c r="AX4" s="10">
-        <v>2.7855000000000002E-3</v>
-      </c>
-      <c r="AY4" t="s">
-        <v>155</v>
-      </c>
-      <c r="AZ4" t="s">
-        <v>193</v>
-      </c>
-      <c r="BA4" t="s">
-        <v>193</v>
-      </c>
       <c r="BB4" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="5" spans="1:54" x14ac:dyDescent="0.2">
+        <v>192</v>
+      </c>
+      <c r="BC4" t="s">
+        <v>192</v>
+      </c>
+      <c r="BD4" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="5" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B5" t="s">
-        <v>114</v>
-      </c>
-      <c r="C5" s="8">
+        <v>113</v>
+      </c>
+      <c r="C5" t="b">
+        <v>0</v>
+      </c>
+      <c r="D5" t="s">
+        <v>228</v>
+      </c>
+      <c r="E5" s="7">
         <v>45</v>
       </c>
-      <c r="D5" s="8">
+      <c r="F5" s="7">
         <v>365</v>
       </c>
-      <c r="E5" s="8">
+      <c r="G5" s="7">
         <v>0.02</v>
       </c>
-      <c r="F5" s="50" t="s">
+      <c r="H5" s="49">
+        <v>32</v>
+      </c>
+      <c r="I5" s="48" t="s">
         <v>29</v>
       </c>
-      <c r="G5" s="24" t="s">
-        <v>215</v>
-      </c>
-      <c r="H5" s="51">
-        <v>32</v>
-      </c>
-      <c r="I5" s="15" t="s">
+      <c r="J5" s="14" t="s">
         <v>88</v>
-      </c>
-      <c r="J5">
-        <v>0.35</v>
       </c>
       <c r="K5">
         <v>0.7</v>
       </c>
-      <c r="M5" t="s">
-        <v>218</v>
-      </c>
-      <c r="N5" s="51" t="s">
-        <v>156</v>
-      </c>
-      <c r="O5" s="15">
+      <c r="M5">
+        <v>0.35</v>
+      </c>
+      <c r="N5" t="s">
+        <v>216</v>
+      </c>
+      <c r="O5" s="49" t="s">
+        <v>155</v>
+      </c>
+      <c r="P5" s="22" t="s">
+        <v>213</v>
+      </c>
+      <c r="Q5" s="51" t="s">
+        <v>153</v>
+      </c>
+      <c r="R5" s="14">
         <v>0.9</v>
       </c>
-      <c r="P5" s="15">
+      <c r="S5" s="14">
         <v>3.5000000000000003E-2</v>
       </c>
-      <c r="Q5" s="52">
+      <c r="T5" s="50">
         <v>0.9</v>
       </c>
-      <c r="R5" s="52">
+      <c r="U5" s="50">
         <v>0.71</v>
       </c>
-      <c r="S5" s="52">
+      <c r="V5" s="50">
         <f t="shared" si="0"/>
         <v>504</v>
       </c>
-      <c r="T5" s="52">
+      <c r="W5" s="50">
         <f t="shared" si="1"/>
         <v>1008</v>
       </c>
-      <c r="U5" s="53" t="s">
+      <c r="X5" s="30">
+        <v>3</v>
+      </c>
+      <c r="Y5" s="30">
+        <v>0</v>
+      </c>
+      <c r="Z5">
+        <v>90</v>
+      </c>
+      <c r="AA5">
+        <v>100</v>
+      </c>
+      <c r="AB5" s="8">
+        <v>1</v>
+      </c>
+      <c r="AC5" s="8">
+        <v>0</v>
+      </c>
+      <c r="AD5" s="8">
+        <v>182.5</v>
+      </c>
+      <c r="AE5" s="8">
+        <v>0.21634999999999999</v>
+      </c>
+      <c r="AF5" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG5" s="28">
+        <v>1</v>
+      </c>
+      <c r="AH5" s="28">
+        <v>0</v>
+      </c>
+      <c r="AI5" s="28">
+        <v>182.5</v>
+      </c>
+      <c r="AJ5" s="28">
+        <v>8.3141000000000007E-2</v>
+      </c>
+      <c r="AK5" s="6">
+        <v>1</v>
+      </c>
+      <c r="AL5" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM5" s="6">
+        <v>182.5</v>
+      </c>
+      <c r="AN5" s="6">
+        <v>0.47815999999999997</v>
+      </c>
+      <c r="AO5" s="52">
+        <v>1</v>
+      </c>
+      <c r="AP5" s="52">
+        <v>0</v>
+      </c>
+      <c r="AQ5" s="52">
+        <v>121.66670000000001</v>
+      </c>
+      <c r="AR5" s="52">
+        <v>2.6738E-3</v>
+      </c>
+      <c r="AS5" s="53">
+        <v>1</v>
+      </c>
+      <c r="AT5" s="53">
+        <v>0</v>
+      </c>
+      <c r="AU5" s="53">
+        <v>182.5</v>
+      </c>
+      <c r="AV5" s="53">
+        <v>0.11268</v>
+      </c>
+      <c r="AW5" s="9">
+        <v>1</v>
+      </c>
+      <c r="AX5" s="9">
+        <v>0</v>
+      </c>
+      <c r="AY5" s="9">
+        <v>121.66670000000001</v>
+      </c>
+      <c r="AZ5" s="9">
+        <v>2.7855000000000002E-3</v>
+      </c>
+      <c r="BA5" t="s">
         <v>154</v>
       </c>
-      <c r="V5" s="32">
-        <v>3</v>
-      </c>
-      <c r="W5" s="32">
-        <v>0</v>
-      </c>
-      <c r="X5">
-        <v>90</v>
-      </c>
-      <c r="Y5">
-        <v>100</v>
-      </c>
-      <c r="Z5" s="9">
-        <v>1</v>
-      </c>
-      <c r="AA5" s="9">
-        <v>0</v>
-      </c>
-      <c r="AB5" s="9">
-        <v>182.5</v>
-      </c>
-      <c r="AC5" s="9">
-        <v>0.21634999999999999</v>
-      </c>
-      <c r="AD5" t="b">
-        <v>1</v>
-      </c>
-      <c r="AE5" s="30">
-        <v>1</v>
-      </c>
-      <c r="AF5" s="30">
-        <v>0</v>
-      </c>
-      <c r="AG5" s="30">
-        <v>182.5</v>
-      </c>
-      <c r="AH5" s="30">
-        <v>8.3141000000000007E-2</v>
-      </c>
-      <c r="AI5" s="7">
-        <v>1</v>
-      </c>
-      <c r="AJ5" s="7">
-        <v>0</v>
-      </c>
-      <c r="AK5" s="7">
-        <v>182.5</v>
-      </c>
-      <c r="AL5" s="7">
-        <v>0.47815999999999997</v>
-      </c>
-      <c r="AM5" s="54">
-        <v>1</v>
-      </c>
-      <c r="AN5" s="54">
-        <v>0</v>
-      </c>
-      <c r="AO5" s="54">
-        <v>121.66670000000001</v>
-      </c>
-      <c r="AP5" s="54">
-        <v>2.6738E-3</v>
-      </c>
-      <c r="AQ5" s="55">
-        <v>1</v>
-      </c>
-      <c r="AR5" s="55">
-        <v>0</v>
-      </c>
-      <c r="AS5" s="55">
-        <v>182.5</v>
-      </c>
-      <c r="AT5" s="55">
-        <v>0.11268</v>
-      </c>
-      <c r="AU5" s="10">
-        <v>1</v>
-      </c>
-      <c r="AV5" s="10">
-        <v>0</v>
-      </c>
-      <c r="AW5" s="10">
-        <v>121.66670000000001</v>
-      </c>
-      <c r="AX5" s="10">
-        <v>2.7855000000000002E-3</v>
-      </c>
-      <c r="AY5" t="s">
-        <v>155</v>
-      </c>
-      <c r="AZ5" t="s">
-        <v>193</v>
-      </c>
-      <c r="BA5" t="s">
-        <v>193</v>
-      </c>
       <c r="BB5" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="6" spans="1:54" x14ac:dyDescent="0.2">
+        <v>192</v>
+      </c>
+      <c r="BC5" t="s">
+        <v>192</v>
+      </c>
+      <c r="BD5" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="6" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B6" t="s">
-        <v>115</v>
-      </c>
-      <c r="C6" s="8">
+        <v>114</v>
+      </c>
+      <c r="C6" t="b">
+        <v>0</v>
+      </c>
+      <c r="D6" t="s">
+        <v>228</v>
+      </c>
+      <c r="E6" s="7">
         <v>45</v>
       </c>
-      <c r="D6" s="8">
+      <c r="F6" s="7">
         <v>365</v>
       </c>
-      <c r="E6" s="8">
+      <c r="G6" s="7">
         <v>0.02</v>
       </c>
-      <c r="F6" s="50" t="s">
+      <c r="H6" s="49">
+        <v>32</v>
+      </c>
+      <c r="I6" s="48" t="s">
         <v>29</v>
       </c>
-      <c r="G6" s="24" t="s">
-        <v>215</v>
-      </c>
-      <c r="H6" s="51">
-        <v>32</v>
-      </c>
-      <c r="I6" s="15" t="s">
+      <c r="J6" s="14" t="s">
         <v>88</v>
-      </c>
-      <c r="J6">
-        <v>0.35</v>
       </c>
       <c r="K6">
         <v>0.7</v>
       </c>
-      <c r="M6" t="s">
-        <v>218</v>
-      </c>
-      <c r="N6" s="51" t="s">
-        <v>156</v>
-      </c>
-      <c r="O6" s="15">
+      <c r="M6">
+        <v>0.35</v>
+      </c>
+      <c r="N6" t="s">
+        <v>216</v>
+      </c>
+      <c r="O6" s="49" t="s">
+        <v>155</v>
+      </c>
+      <c r="P6" s="22" t="s">
+        <v>213</v>
+      </c>
+      <c r="Q6" s="51" t="s">
+        <v>153</v>
+      </c>
+      <c r="R6" s="14">
         <v>0.9</v>
       </c>
-      <c r="P6" s="15">
+      <c r="S6" s="14">
         <v>3.5000000000000003E-2</v>
       </c>
-      <c r="Q6" s="52">
+      <c r="T6" s="50">
         <v>0.9</v>
       </c>
-      <c r="R6" s="52">
+      <c r="U6" s="50">
         <v>0.71</v>
       </c>
-      <c r="S6" s="52">
+      <c r="V6" s="50">
         <f t="shared" si="0"/>
         <v>504</v>
       </c>
-      <c r="T6" s="52">
+      <c r="W6" s="50">
         <f t="shared" si="1"/>
         <v>1008</v>
       </c>
-      <c r="U6" s="53" t="s">
+      <c r="X6" s="30">
+        <v>3</v>
+      </c>
+      <c r="Y6" s="30">
+        <v>0</v>
+      </c>
+      <c r="Z6">
+        <v>90</v>
+      </c>
+      <c r="AA6">
+        <v>100</v>
+      </c>
+      <c r="AB6" s="8">
+        <v>1</v>
+      </c>
+      <c r="AC6" s="8">
+        <v>0</v>
+      </c>
+      <c r="AD6" s="8">
+        <v>182.5</v>
+      </c>
+      <c r="AE6" s="8">
+        <v>0.21634999999999999</v>
+      </c>
+      <c r="AF6" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG6" s="28">
+        <v>1</v>
+      </c>
+      <c r="AH6" s="28">
+        <v>0</v>
+      </c>
+      <c r="AI6" s="28">
+        <v>182.5</v>
+      </c>
+      <c r="AJ6" s="28">
+        <v>8.3141000000000007E-2</v>
+      </c>
+      <c r="AK6" s="6">
+        <v>1</v>
+      </c>
+      <c r="AL6" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM6" s="6">
+        <v>182.5</v>
+      </c>
+      <c r="AN6" s="6">
+        <v>0.47815999999999997</v>
+      </c>
+      <c r="AO6" s="52">
+        <v>1</v>
+      </c>
+      <c r="AP6" s="52">
+        <v>0</v>
+      </c>
+      <c r="AQ6" s="52">
+        <v>121.66670000000001</v>
+      </c>
+      <c r="AR6" s="52">
+        <v>2.6738E-3</v>
+      </c>
+      <c r="AS6" s="53">
+        <v>1</v>
+      </c>
+      <c r="AT6" s="53">
+        <v>0</v>
+      </c>
+      <c r="AU6" s="53">
+        <v>182.5</v>
+      </c>
+      <c r="AV6" s="53">
+        <v>0.11268</v>
+      </c>
+      <c r="AW6" s="9">
+        <v>1</v>
+      </c>
+      <c r="AX6" s="9">
+        <v>0</v>
+      </c>
+      <c r="AY6" s="9">
+        <v>121.66670000000001</v>
+      </c>
+      <c r="AZ6" s="9">
+        <v>2.7855000000000002E-3</v>
+      </c>
+      <c r="BA6" t="s">
         <v>154</v>
       </c>
-      <c r="V6" s="32">
-        <v>3</v>
-      </c>
-      <c r="W6" s="32">
-        <v>0</v>
-      </c>
-      <c r="X6">
-        <v>90</v>
-      </c>
-      <c r="Y6">
-        <v>100</v>
-      </c>
-      <c r="Z6" s="9">
-        <v>1</v>
-      </c>
-      <c r="AA6" s="9">
-        <v>0</v>
-      </c>
-      <c r="AB6" s="9">
-        <v>182.5</v>
-      </c>
-      <c r="AC6" s="9">
-        <v>0.21634999999999999</v>
-      </c>
-      <c r="AD6" t="b">
-        <v>1</v>
-      </c>
-      <c r="AE6" s="30">
-        <v>1</v>
-      </c>
-      <c r="AF6" s="30">
-        <v>0</v>
-      </c>
-      <c r="AG6" s="30">
-        <v>182.5</v>
-      </c>
-      <c r="AH6" s="30">
-        <v>8.3141000000000007E-2</v>
-      </c>
-      <c r="AI6" s="7">
-        <v>1</v>
-      </c>
-      <c r="AJ6" s="7">
-        <v>0</v>
-      </c>
-      <c r="AK6" s="7">
-        <v>182.5</v>
-      </c>
-      <c r="AL6" s="7">
-        <v>0.47815999999999997</v>
-      </c>
-      <c r="AM6" s="54">
-        <v>1</v>
-      </c>
-      <c r="AN6" s="54">
-        <v>0</v>
-      </c>
-      <c r="AO6" s="54">
-        <v>121.66670000000001</v>
-      </c>
-      <c r="AP6" s="54">
-        <v>2.6738E-3</v>
-      </c>
-      <c r="AQ6" s="55">
-        <v>1</v>
-      </c>
-      <c r="AR6" s="55">
-        <v>0</v>
-      </c>
-      <c r="AS6" s="55">
-        <v>182.5</v>
-      </c>
-      <c r="AT6" s="55">
-        <v>0.11268</v>
-      </c>
-      <c r="AU6" s="10">
-        <v>1</v>
-      </c>
-      <c r="AV6" s="10">
-        <v>0</v>
-      </c>
-      <c r="AW6" s="10">
-        <v>121.66670000000001</v>
-      </c>
-      <c r="AX6" s="10">
-        <v>2.7855000000000002E-3</v>
-      </c>
-      <c r="AY6" t="s">
-        <v>155</v>
-      </c>
-      <c r="AZ6" t="s">
-        <v>193</v>
-      </c>
-      <c r="BA6" t="s">
-        <v>193</v>
-      </c>
       <c r="BB6" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="7" spans="1:54" x14ac:dyDescent="0.2">
+        <v>192</v>
+      </c>
+      <c r="BC6" t="s">
+        <v>192</v>
+      </c>
+      <c r="BD6" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="7" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B7" t="s">
-        <v>116</v>
-      </c>
-      <c r="C7" s="8">
+        <v>115</v>
+      </c>
+      <c r="C7" t="b">
+        <v>0</v>
+      </c>
+      <c r="D7" t="s">
+        <v>228</v>
+      </c>
+      <c r="E7" s="7">
         <v>45</v>
       </c>
-      <c r="D7" s="8">
+      <c r="F7" s="7">
         <v>365</v>
       </c>
-      <c r="E7" s="8">
+      <c r="G7" s="7">
         <v>0.02</v>
       </c>
-      <c r="F7" s="50" t="s">
+      <c r="H7" s="49">
+        <v>32</v>
+      </c>
+      <c r="I7" s="48" t="s">
         <v>29</v>
       </c>
-      <c r="G7" s="24" t="s">
-        <v>215</v>
-      </c>
-      <c r="H7" s="51">
-        <v>32</v>
-      </c>
-      <c r="I7" s="15" t="s">
+      <c r="J7" s="14" t="s">
         <v>88</v>
-      </c>
-      <c r="J7">
-        <v>0.35</v>
       </c>
       <c r="K7">
         <v>0.7</v>
       </c>
-      <c r="M7" t="s">
-        <v>218</v>
-      </c>
-      <c r="N7" s="51" t="s">
-        <v>156</v>
-      </c>
-      <c r="O7" s="15">
+      <c r="M7">
+        <v>0.35</v>
+      </c>
+      <c r="N7" t="s">
+        <v>216</v>
+      </c>
+      <c r="O7" s="49" t="s">
+        <v>155</v>
+      </c>
+      <c r="P7" s="22" t="s">
+        <v>213</v>
+      </c>
+      <c r="Q7" s="51" t="s">
+        <v>153</v>
+      </c>
+      <c r="R7" s="14">
         <v>0.9</v>
       </c>
-      <c r="P7" s="15">
+      <c r="S7" s="14">
         <v>3.5000000000000003E-2</v>
       </c>
-      <c r="Q7" s="52">
+      <c r="T7" s="50">
         <v>0.9</v>
       </c>
-      <c r="R7" s="52">
+      <c r="U7" s="50">
         <v>0.71</v>
       </c>
-      <c r="S7" s="52">
+      <c r="V7" s="50">
         <f t="shared" si="0"/>
         <v>504</v>
       </c>
-      <c r="T7" s="52">
+      <c r="W7" s="50">
         <f t="shared" si="1"/>
         <v>1008</v>
       </c>
-      <c r="U7" s="53" t="s">
+      <c r="X7" s="30">
+        <v>3</v>
+      </c>
+      <c r="Y7" s="30">
+        <v>0</v>
+      </c>
+      <c r="Z7">
+        <v>90</v>
+      </c>
+      <c r="AA7">
+        <v>100</v>
+      </c>
+      <c r="AB7" s="8">
+        <v>1</v>
+      </c>
+      <c r="AC7" s="8">
+        <v>0</v>
+      </c>
+      <c r="AD7" s="8">
+        <v>182.5</v>
+      </c>
+      <c r="AE7" s="8">
+        <v>0.21634999999999999</v>
+      </c>
+      <c r="AF7" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG7" s="28">
+        <v>1</v>
+      </c>
+      <c r="AH7" s="28">
+        <v>0</v>
+      </c>
+      <c r="AI7" s="28">
+        <v>182.5</v>
+      </c>
+      <c r="AJ7" s="28">
+        <v>8.3141000000000007E-2</v>
+      </c>
+      <c r="AK7" s="6">
+        <v>1</v>
+      </c>
+      <c r="AL7" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM7" s="6">
+        <v>182.5</v>
+      </c>
+      <c r="AN7" s="6">
+        <v>0.47815999999999997</v>
+      </c>
+      <c r="AO7" s="52">
+        <v>1</v>
+      </c>
+      <c r="AP7" s="52">
+        <v>0</v>
+      </c>
+      <c r="AQ7" s="52">
+        <v>121.66670000000001</v>
+      </c>
+      <c r="AR7" s="52">
+        <v>2.6738E-3</v>
+      </c>
+      <c r="AS7" s="53">
+        <v>1</v>
+      </c>
+      <c r="AT7" s="53">
+        <v>0</v>
+      </c>
+      <c r="AU7" s="53">
+        <v>182.5</v>
+      </c>
+      <c r="AV7" s="53">
+        <v>0.11268</v>
+      </c>
+      <c r="AW7" s="9">
+        <v>1</v>
+      </c>
+      <c r="AX7" s="9">
+        <v>0</v>
+      </c>
+      <c r="AY7" s="9">
+        <v>121.66670000000001</v>
+      </c>
+      <c r="AZ7" s="9">
+        <v>2.7855000000000002E-3</v>
+      </c>
+      <c r="BA7" t="s">
         <v>154</v>
       </c>
-      <c r="V7" s="32">
-        <v>3</v>
-      </c>
-      <c r="W7" s="32">
-        <v>0</v>
-      </c>
-      <c r="X7">
-        <v>90</v>
-      </c>
-      <c r="Y7">
-        <v>100</v>
-      </c>
-      <c r="Z7" s="9">
-        <v>1</v>
-      </c>
-      <c r="AA7" s="9">
-        <v>0</v>
-      </c>
-      <c r="AB7" s="9">
-        <v>182.5</v>
-      </c>
-      <c r="AC7" s="9">
-        <v>0.21634999999999999</v>
-      </c>
-      <c r="AD7" t="b">
-        <v>1</v>
-      </c>
-      <c r="AE7" s="30">
-        <v>1</v>
-      </c>
-      <c r="AF7" s="30">
-        <v>0</v>
-      </c>
-      <c r="AG7" s="30">
-        <v>182.5</v>
-      </c>
-      <c r="AH7" s="30">
-        <v>8.3141000000000007E-2</v>
-      </c>
-      <c r="AI7" s="7">
-        <v>1</v>
-      </c>
-      <c r="AJ7" s="7">
-        <v>0</v>
-      </c>
-      <c r="AK7" s="7">
-        <v>182.5</v>
-      </c>
-      <c r="AL7" s="7">
-        <v>0.47815999999999997</v>
-      </c>
-      <c r="AM7" s="54">
-        <v>1</v>
-      </c>
-      <c r="AN7" s="54">
-        <v>0</v>
-      </c>
-      <c r="AO7" s="54">
-        <v>121.66670000000001</v>
-      </c>
-      <c r="AP7" s="54">
-        <v>2.6738E-3</v>
-      </c>
-      <c r="AQ7" s="55">
-        <v>1</v>
-      </c>
-      <c r="AR7" s="55">
-        <v>0</v>
-      </c>
-      <c r="AS7" s="55">
-        <v>182.5</v>
-      </c>
-      <c r="AT7" s="55">
-        <v>0.11268</v>
-      </c>
-      <c r="AU7" s="10">
-        <v>1</v>
-      </c>
-      <c r="AV7" s="10">
-        <v>0</v>
-      </c>
-      <c r="AW7" s="10">
-        <v>121.66670000000001</v>
-      </c>
-      <c r="AX7" s="10">
-        <v>2.7855000000000002E-3</v>
-      </c>
-      <c r="AY7" t="s">
-        <v>155</v>
-      </c>
-      <c r="AZ7" t="s">
-        <v>193</v>
-      </c>
-      <c r="BA7" t="s">
-        <v>193</v>
-      </c>
       <c r="BB7" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="8" spans="1:54" x14ac:dyDescent="0.2">
+        <v>192</v>
+      </c>
+      <c r="BC7" t="s">
+        <v>192</v>
+      </c>
+      <c r="BD7" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="8" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B8" t="s">
-        <v>117</v>
-      </c>
-      <c r="C8" s="8">
+        <v>116</v>
+      </c>
+      <c r="C8" t="b">
+        <v>0</v>
+      </c>
+      <c r="D8" t="s">
+        <v>228</v>
+      </c>
+      <c r="E8" s="7">
         <v>45</v>
       </c>
-      <c r="D8" s="8">
+      <c r="F8" s="7">
         <v>365</v>
       </c>
-      <c r="E8" s="8">
+      <c r="G8" s="7">
         <v>0.02</v>
       </c>
-      <c r="F8" s="50" t="s">
+      <c r="H8" s="49">
+        <v>32</v>
+      </c>
+      <c r="I8" s="48" t="s">
         <v>29</v>
       </c>
-      <c r="G8" s="24" t="s">
-        <v>215</v>
-      </c>
-      <c r="H8" s="51">
-        <v>32</v>
-      </c>
-      <c r="I8" s="15" t="s">
+      <c r="J8" s="14" t="s">
         <v>88</v>
-      </c>
-      <c r="J8">
-        <v>0.35</v>
       </c>
       <c r="K8">
         <v>0.7</v>
       </c>
-      <c r="M8" t="s">
-        <v>218</v>
-      </c>
-      <c r="N8" s="51" t="s">
-        <v>156</v>
-      </c>
-      <c r="O8" s="15">
+      <c r="M8">
+        <v>0.35</v>
+      </c>
+      <c r="N8" t="s">
+        <v>216</v>
+      </c>
+      <c r="O8" s="49" t="s">
+        <v>155</v>
+      </c>
+      <c r="P8" s="22" t="s">
+        <v>213</v>
+      </c>
+      <c r="Q8" s="51" t="s">
+        <v>153</v>
+      </c>
+      <c r="R8" s="14">
         <v>0.9</v>
       </c>
-      <c r="P8" s="15">
+      <c r="S8" s="14">
         <v>3.5000000000000003E-2</v>
       </c>
-      <c r="Q8" s="52">
+      <c r="T8" s="50">
         <v>0.9</v>
       </c>
-      <c r="R8" s="52">
+      <c r="U8" s="50">
         <v>0.71</v>
       </c>
-      <c r="S8" s="52">
+      <c r="V8" s="50">
         <f t="shared" si="0"/>
         <v>504</v>
       </c>
-      <c r="T8" s="52">
+      <c r="W8" s="50">
         <f t="shared" si="1"/>
         <v>1008</v>
       </c>
-      <c r="U8" s="53" t="s">
+      <c r="X8" s="30">
+        <v>3</v>
+      </c>
+      <c r="Y8" s="30">
+        <v>0</v>
+      </c>
+      <c r="Z8">
+        <v>90</v>
+      </c>
+      <c r="AA8">
+        <v>100</v>
+      </c>
+      <c r="AB8" s="8">
+        <v>1</v>
+      </c>
+      <c r="AC8" s="8">
+        <v>0</v>
+      </c>
+      <c r="AD8" s="8">
+        <v>182.5</v>
+      </c>
+      <c r="AE8" s="8">
+        <v>0.21634999999999999</v>
+      </c>
+      <c r="AF8" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG8" s="28">
+        <v>1</v>
+      </c>
+      <c r="AH8" s="28">
+        <v>0</v>
+      </c>
+      <c r="AI8" s="28">
+        <v>182.5</v>
+      </c>
+      <c r="AJ8" s="28">
+        <v>8.3141000000000007E-2</v>
+      </c>
+      <c r="AK8" s="6">
+        <v>1</v>
+      </c>
+      <c r="AL8" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM8" s="6">
+        <v>182.5</v>
+      </c>
+      <c r="AN8" s="6">
+        <v>0.47815999999999997</v>
+      </c>
+      <c r="AO8" s="52">
+        <v>1</v>
+      </c>
+      <c r="AP8" s="52">
+        <v>0</v>
+      </c>
+      <c r="AQ8" s="52">
+        <v>121.66670000000001</v>
+      </c>
+      <c r="AR8" s="52">
+        <v>2.6738E-3</v>
+      </c>
+      <c r="AS8" s="53">
+        <v>1</v>
+      </c>
+      <c r="AT8" s="53">
+        <v>0</v>
+      </c>
+      <c r="AU8" s="53">
+        <v>182.5</v>
+      </c>
+      <c r="AV8" s="53">
+        <v>0.11268</v>
+      </c>
+      <c r="AW8" s="9">
+        <v>1</v>
+      </c>
+      <c r="AX8" s="9">
+        <v>0</v>
+      </c>
+      <c r="AY8" s="9">
+        <v>121.66670000000001</v>
+      </c>
+      <c r="AZ8" s="9">
+        <v>2.7855000000000002E-3</v>
+      </c>
+      <c r="BA8" t="s">
         <v>154</v>
       </c>
-      <c r="V8" s="32">
-        <v>3</v>
-      </c>
-      <c r="W8" s="32">
-        <v>0</v>
-      </c>
-      <c r="X8">
-        <v>90</v>
-      </c>
-      <c r="Y8">
-        <v>100</v>
-      </c>
-      <c r="Z8" s="9">
-        <v>1</v>
-      </c>
-      <c r="AA8" s="9">
-        <v>0</v>
-      </c>
-      <c r="AB8" s="9">
-        <v>182.5</v>
-      </c>
-      <c r="AC8" s="9">
-        <v>0.21634999999999999</v>
-      </c>
-      <c r="AD8" t="b">
-        <v>1</v>
-      </c>
-      <c r="AE8" s="30">
-        <v>1</v>
-      </c>
-      <c r="AF8" s="30">
-        <v>0</v>
-      </c>
-      <c r="AG8" s="30">
-        <v>182.5</v>
-      </c>
-      <c r="AH8" s="30">
-        <v>8.3141000000000007E-2</v>
-      </c>
-      <c r="AI8" s="7">
-        <v>1</v>
-      </c>
-      <c r="AJ8" s="7">
-        <v>0</v>
-      </c>
-      <c r="AK8" s="7">
-        <v>182.5</v>
-      </c>
-      <c r="AL8" s="7">
-        <v>0.47815999999999997</v>
-      </c>
-      <c r="AM8" s="54">
-        <v>1</v>
-      </c>
-      <c r="AN8" s="54">
-        <v>0</v>
-      </c>
-      <c r="AO8" s="54">
-        <v>121.66670000000001</v>
-      </c>
-      <c r="AP8" s="54">
-        <v>2.6738E-3</v>
-      </c>
-      <c r="AQ8" s="55">
-        <v>1</v>
-      </c>
-      <c r="AR8" s="55">
-        <v>0</v>
-      </c>
-      <c r="AS8" s="55">
-        <v>182.5</v>
-      </c>
-      <c r="AT8" s="55">
-        <v>0.11268</v>
-      </c>
-      <c r="AU8" s="10">
-        <v>1</v>
-      </c>
-      <c r="AV8" s="10">
-        <v>0</v>
-      </c>
-      <c r="AW8" s="10">
-        <v>121.66670000000001</v>
-      </c>
-      <c r="AX8" s="10">
-        <v>2.7855000000000002E-3</v>
-      </c>
-      <c r="AY8" t="s">
-        <v>155</v>
-      </c>
-      <c r="AZ8" t="s">
-        <v>193</v>
-      </c>
-      <c r="BA8" t="s">
-        <v>193</v>
-      </c>
       <c r="BB8" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="9" spans="1:54" x14ac:dyDescent="0.2">
+        <v>192</v>
+      </c>
+      <c r="BC8" t="s">
+        <v>192</v>
+      </c>
+      <c r="BD8" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="9" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B9" t="s">
-        <v>118</v>
-      </c>
-      <c r="C9" s="8">
+        <v>117</v>
+      </c>
+      <c r="C9" t="b">
+        <v>0</v>
+      </c>
+      <c r="D9" t="s">
+        <v>228</v>
+      </c>
+      <c r="E9" s="7">
         <v>45</v>
       </c>
-      <c r="D9" s="8">
+      <c r="F9" s="7">
         <v>365</v>
       </c>
-      <c r="E9" s="8">
+      <c r="G9" s="7">
         <v>0.02</v>
       </c>
-      <c r="F9" s="50" t="s">
+      <c r="H9" s="49">
+        <v>65</v>
+      </c>
+      <c r="I9" s="48" t="s">
         <v>29</v>
       </c>
-      <c r="G9" s="24" t="s">
-        <v>215</v>
-      </c>
-      <c r="H9" s="51">
-        <v>65</v>
-      </c>
-      <c r="I9" s="15" t="s">
+      <c r="J9" s="14" t="s">
         <v>88</v>
-      </c>
-      <c r="J9">
-        <v>0.35</v>
       </c>
       <c r="K9">
         <v>0.7</v>
       </c>
-      <c r="M9" t="s">
-        <v>218</v>
-      </c>
-      <c r="N9" s="51" t="s">
-        <v>156</v>
-      </c>
-      <c r="O9" s="15">
+      <c r="M9">
+        <v>0.35</v>
+      </c>
+      <c r="N9" t="s">
+        <v>216</v>
+      </c>
+      <c r="O9" s="49" t="s">
+        <v>155</v>
+      </c>
+      <c r="P9" s="22" t="s">
+        <v>213</v>
+      </c>
+      <c r="Q9" s="51" t="s">
+        <v>153</v>
+      </c>
+      <c r="R9" s="14">
         <v>0.9</v>
       </c>
-      <c r="P9" s="15">
+      <c r="S9" s="14">
         <v>3.5000000000000003E-2</v>
       </c>
-      <c r="Q9" s="52">
+      <c r="T9" s="50">
         <v>0.9</v>
       </c>
-      <c r="R9" s="52">
+      <c r="U9" s="50">
         <v>0.71</v>
       </c>
-      <c r="S9" s="52">
+      <c r="V9" s="50">
         <f t="shared" si="0"/>
         <v>504</v>
       </c>
-      <c r="T9" s="52">
+      <c r="W9" s="50">
         <f t="shared" si="1"/>
         <v>1008</v>
       </c>
-      <c r="U9" s="53" t="s">
+      <c r="X9" s="30">
+        <v>3</v>
+      </c>
+      <c r="Y9" s="30">
+        <v>0</v>
+      </c>
+      <c r="Z9">
+        <v>90</v>
+      </c>
+      <c r="AA9">
+        <v>100</v>
+      </c>
+      <c r="AB9" s="8">
+        <v>1</v>
+      </c>
+      <c r="AC9" s="8">
+        <v>0</v>
+      </c>
+      <c r="AD9" s="8">
+        <v>182.5</v>
+      </c>
+      <c r="AE9" s="8">
+        <v>0.21634999999999999</v>
+      </c>
+      <c r="AF9" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG9" s="28">
+        <v>1</v>
+      </c>
+      <c r="AH9" s="28">
+        <v>0</v>
+      </c>
+      <c r="AI9" s="28">
+        <v>182.5</v>
+      </c>
+      <c r="AJ9" s="28">
+        <v>8.3141000000000007E-2</v>
+      </c>
+      <c r="AK9" s="6">
+        <v>1</v>
+      </c>
+      <c r="AL9" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM9" s="6">
+        <v>182.5</v>
+      </c>
+      <c r="AN9" s="6">
+        <v>0.47815999999999997</v>
+      </c>
+      <c r="AO9" s="52">
+        <v>1</v>
+      </c>
+      <c r="AP9" s="52">
+        <v>0</v>
+      </c>
+      <c r="AQ9" s="52">
+        <v>121.66670000000001</v>
+      </c>
+      <c r="AR9" s="52">
+        <v>2.6738E-3</v>
+      </c>
+      <c r="AS9" s="53">
+        <v>1</v>
+      </c>
+      <c r="AT9" s="53">
+        <v>0</v>
+      </c>
+      <c r="AU9" s="53">
+        <v>182.5</v>
+      </c>
+      <c r="AV9" s="53">
+        <v>0.11268</v>
+      </c>
+      <c r="AW9" s="9">
+        <v>1</v>
+      </c>
+      <c r="AX9" s="9">
+        <v>0</v>
+      </c>
+      <c r="AY9" s="9">
+        <v>121.66670000000001</v>
+      </c>
+      <c r="AZ9" s="9">
+        <v>2.7855000000000002E-3</v>
+      </c>
+      <c r="BA9" t="s">
         <v>154</v>
       </c>
-      <c r="V9" s="32">
-        <v>3</v>
-      </c>
-      <c r="W9" s="32">
-        <v>0</v>
-      </c>
-      <c r="X9">
-        <v>90</v>
-      </c>
-      <c r="Y9">
-        <v>100</v>
-      </c>
-      <c r="Z9" s="9">
-        <v>1</v>
-      </c>
-      <c r="AA9" s="9">
-        <v>0</v>
-      </c>
-      <c r="AB9" s="9">
-        <v>182.5</v>
-      </c>
-      <c r="AC9" s="9">
-        <v>0.21634999999999999</v>
-      </c>
-      <c r="AD9" t="b">
-        <v>1</v>
-      </c>
-      <c r="AE9" s="30">
-        <v>1</v>
-      </c>
-      <c r="AF9" s="30">
-        <v>0</v>
-      </c>
-      <c r="AG9" s="30">
-        <v>182.5</v>
-      </c>
-      <c r="AH9" s="30">
-        <v>8.3141000000000007E-2</v>
-      </c>
-      <c r="AI9" s="7">
-        <v>1</v>
-      </c>
-      <c r="AJ9" s="7">
-        <v>0</v>
-      </c>
-      <c r="AK9" s="7">
-        <v>182.5</v>
-      </c>
-      <c r="AL9" s="7">
-        <v>0.47815999999999997</v>
-      </c>
-      <c r="AM9" s="54">
-        <v>1</v>
-      </c>
-      <c r="AN9" s="54">
-        <v>0</v>
-      </c>
-      <c r="AO9" s="54">
-        <v>121.66670000000001</v>
-      </c>
-      <c r="AP9" s="54">
-        <v>2.6738E-3</v>
-      </c>
-      <c r="AQ9" s="55">
-        <v>1</v>
-      </c>
-      <c r="AR9" s="55">
-        <v>0</v>
-      </c>
-      <c r="AS9" s="55">
-        <v>182.5</v>
-      </c>
-      <c r="AT9" s="55">
-        <v>0.11268</v>
-      </c>
-      <c r="AU9" s="10">
-        <v>1</v>
-      </c>
-      <c r="AV9" s="10">
-        <v>0</v>
-      </c>
-      <c r="AW9" s="10">
-        <v>121.66670000000001</v>
-      </c>
-      <c r="AX9" s="10">
-        <v>2.7855000000000002E-3</v>
-      </c>
-      <c r="AY9" t="s">
-        <v>155</v>
-      </c>
-      <c r="AZ9" t="s">
-        <v>193</v>
-      </c>
-      <c r="BA9" t="s">
-        <v>193</v>
-      </c>
       <c r="BB9" t="s">
-        <v>219</v>
+        <v>192</v>
+      </c>
+      <c r="BC9" t="s">
+        <v>192</v>
+      </c>
+      <c r="BD9" t="s">
+        <v>217</v>
       </c>
     </row>
   </sheetData>
@@ -5086,90 +5144,90 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A904CBC9-E240-4A6F-BB4B-8DAB1536C2C9}">
   <dimension ref="A1:S3"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="4" max="4" width="12.33203125" customWidth="1"/>
-    <col min="6" max="6" width="10.33203125" customWidth="1"/>
-    <col min="9" max="9" width="11.83203125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="11.33203125" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="11.33203125" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="47.1640625" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="13.5" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.28515625" customWidth="1"/>
+    <col min="6" max="6" width="10.28515625" customWidth="1"/>
+    <col min="9" max="9" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="47.140625" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="13.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" ht="80" x14ac:dyDescent="0.2">
-      <c r="A1" s="16" t="s">
+    <row r="1" spans="1:19" ht="75" x14ac:dyDescent="0.25">
+      <c r="A1" s="15" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="16" t="s">
+      <c r="B1" s="15" t="s">
         <v>8</v>
       </c>
-      <c r="C1" s="17" t="s">
+      <c r="C1" s="16" t="s">
         <v>9</v>
       </c>
-      <c r="D1" s="17" t="s">
+      <c r="D1" s="16" t="s">
         <v>68</v>
       </c>
-      <c r="E1" s="17" t="s">
+      <c r="E1" s="16" t="s">
         <v>10</v>
       </c>
-      <c r="F1" s="16" t="s">
+      <c r="F1" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="G1" s="16" t="s">
+      <c r="G1" s="15" t="s">
         <v>72</v>
       </c>
-      <c r="H1" s="16" t="s">
+      <c r="H1" s="15" t="s">
         <v>73</v>
       </c>
-      <c r="I1" s="16" t="s">
+      <c r="I1" s="15" t="s">
         <v>90</v>
       </c>
-      <c r="J1" s="16" t="s">
+      <c r="J1" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="K1" s="16" t="s">
+      <c r="K1" s="15" t="s">
         <v>74</v>
       </c>
-      <c r="L1" s="16" t="s">
+      <c r="L1" s="15" t="s">
         <v>75</v>
       </c>
-      <c r="M1" s="16" t="s">
+      <c r="M1" s="15" t="s">
         <v>91</v>
       </c>
-      <c r="N1" s="16" t="s">
+      <c r="N1" s="15" t="s">
         <v>70</v>
       </c>
-      <c r="O1" s="16" t="s">
+      <c r="O1" s="15" t="s">
         <v>71</v>
       </c>
-      <c r="P1" s="16" t="s">
+      <c r="P1" s="15" t="s">
         <v>92</v>
       </c>
-      <c r="Q1" s="16" t="s">
+      <c r="Q1" s="15" t="s">
         <v>7</v>
       </c>
-      <c r="R1" s="16" t="s">
-        <v>190</v>
-      </c>
-      <c r="S1" s="16" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="R1" s="15" t="s">
+        <v>189</v>
+      </c>
+      <c r="S1" s="15" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="2" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B2" t="s">
-        <v>109</v>
-      </c>
-      <c r="C2" s="8">
+        <v>108</v>
+      </c>
+      <c r="C2" s="7">
         <v>45</v>
       </c>
-      <c r="D2" s="8">
+      <c r="D2" s="7">
         <v>365</v>
       </c>
-      <c r="E2" s="8">
+      <c r="E2" s="7">
         <v>3.7499999999999999E-2</v>
       </c>
       <c r="F2">
@@ -5209,26 +5267,26 @@
         <v>66</v>
       </c>
       <c r="R2" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="S2" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="3" spans="1:19" x14ac:dyDescent="0.2">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B3" t="s">
-        <v>110</v>
-      </c>
-      <c r="C3" s="8">
+        <v>109</v>
+      </c>
+      <c r="C3" s="7">
         <v>45</v>
       </c>
-      <c r="D3" s="8">
+      <c r="D3" s="7">
         <v>365</v>
       </c>
-      <c r="E3" s="8">
+      <c r="E3" s="7">
         <v>3.7499999999999999E-2</v>
       </c>
       <c r="F3">
@@ -5268,10 +5326,10 @@
         <v>66</v>
       </c>
       <c r="R3" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="S3" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
   </sheetData>
@@ -5283,18 +5341,18 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{09131FE7-5CF0-4155-B869-9951A97BC4D6}">
   <dimension ref="A1:G130"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="20.83203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15.5" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="19.83203125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.83203125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="19.83203125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="16.33203125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="23.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="20.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="19.85546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="16.28515625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="23.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>7</v>
       </c>
@@ -5310,25 +5368,25 @@
       <c r="E1" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="F1" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="G1" s="5" t="s">
+      <c r="G1" s="4" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>67</v>
       </c>
       <c r="B2" t="s">
+        <v>99</v>
+      </c>
+      <c r="C2" t="s">
         <v>100</v>
       </c>
-      <c r="C2" t="s">
-        <v>101</v>
-      </c>
       <c r="D2" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E2" t="s">
         <v>33</v>
@@ -5336,20 +5394,20 @@
       <c r="F2" t="s">
         <v>62</v>
       </c>
-      <c r="G2" s="6"/>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="G2" s="5"/>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>67</v>
       </c>
       <c r="B3" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C3" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D3" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E3" t="s">
         <v>34</v>
@@ -5358,18 +5416,18 @@
         <v>62</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>67</v>
       </c>
       <c r="B4" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C4" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D4" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E4" t="s">
         <v>35</v>
@@ -5378,18 +5436,18 @@
         <v>62</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>67</v>
       </c>
       <c r="B5" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C5" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D5" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E5" t="s">
         <v>36</v>
@@ -5398,18 +5456,18 @@
         <v>62</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>67</v>
       </c>
       <c r="B6" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C6" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D6" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E6" t="s">
         <v>37</v>
@@ -5418,18 +5476,18 @@
         <v>62</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>67</v>
       </c>
       <c r="B7" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C7" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D7" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E7" t="s">
         <v>38</v>
@@ -5438,18 +5496,18 @@
         <v>62</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>67</v>
       </c>
       <c r="B8" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C8" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D8" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E8" t="s">
         <v>39</v>
@@ -5458,18 +5516,18 @@
         <v>62</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>67</v>
       </c>
       <c r="B9" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C9" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D9" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E9" t="s">
         <v>40</v>
@@ -5478,18 +5536,18 @@
         <v>62</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>67</v>
       </c>
       <c r="B10" t="s">
+        <v>99</v>
+      </c>
+      <c r="C10" t="s">
         <v>100</v>
       </c>
-      <c r="C10" t="s">
-        <v>101</v>
-      </c>
       <c r="D10" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E10" t="s">
         <v>33</v>
@@ -5498,18 +5556,18 @@
         <v>63</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>67</v>
       </c>
       <c r="B11" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C11" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D11" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E11" t="s">
         <v>34</v>
@@ -5518,18 +5576,18 @@
         <v>63</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>67</v>
       </c>
       <c r="B12" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C12" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D12" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E12" t="s">
         <v>35</v>
@@ -5538,18 +5596,18 @@
         <v>63</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>67</v>
       </c>
       <c r="B13" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C13" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D13" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E13" t="s">
         <v>36</v>
@@ -5558,18 +5616,18 @@
         <v>63</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>67</v>
       </c>
       <c r="B14" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C14" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D14" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E14" t="s">
         <v>37</v>
@@ -5578,18 +5636,18 @@
         <v>63</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>67</v>
       </c>
       <c r="B15" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C15" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D15" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E15" t="s">
         <v>38</v>
@@ -5598,18 +5656,18 @@
         <v>63</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>67</v>
       </c>
       <c r="B16" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C16" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D16" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E16" t="s">
         <v>39</v>
@@ -5618,18 +5676,18 @@
         <v>63</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>67</v>
       </c>
       <c r="B17" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C17" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D17" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E17" t="s">
         <v>40</v>
@@ -5638,18 +5696,18 @@
         <v>63</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>67</v>
       </c>
       <c r="B19" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C19" t="s">
         <v>33</v>
       </c>
       <c r="D19" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E19" t="s">
         <v>49</v>
@@ -5658,21 +5716,21 @@
         <v>62</v>
       </c>
       <c r="G19" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>67</v>
       </c>
       <c r="B20" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C20" t="s">
         <v>33</v>
       </c>
       <c r="D20" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E20" t="s">
         <v>49</v>
@@ -5684,64 +5742,64 @@
         <v>64</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>67</v>
       </c>
       <c r="B21" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C21" t="s">
         <v>33</v>
       </c>
       <c r="D21" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E21" t="s">
         <v>49</v>
       </c>
       <c r="F21" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="G21" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>67</v>
       </c>
       <c r="B22" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C22" t="s">
         <v>33</v>
       </c>
       <c r="D22" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E22" t="s">
         <v>49</v>
       </c>
       <c r="F22" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="G22" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>67</v>
       </c>
       <c r="B23" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C23" t="s">
         <v>34</v>
       </c>
       <c r="D23" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E23" t="s">
         <v>50</v>
@@ -5750,21 +5808,21 @@
         <v>62</v>
       </c>
       <c r="G23" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.2">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>67</v>
       </c>
       <c r="B24" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C24" t="s">
         <v>34</v>
       </c>
       <c r="D24" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E24" t="s">
         <v>50</v>
@@ -5776,64 +5834,64 @@
         <v>64</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>67</v>
       </c>
       <c r="B25" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C25" t="s">
         <v>34</v>
       </c>
       <c r="D25" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E25" t="s">
         <v>50</v>
       </c>
       <c r="F25" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="G25" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.2">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>67</v>
       </c>
       <c r="B26" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C26" t="s">
         <v>34</v>
       </c>
       <c r="D26" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E26" t="s">
         <v>50</v>
       </c>
       <c r="F26" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="G26" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.2">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>67</v>
       </c>
       <c r="B27" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C27" t="s">
         <v>35</v>
       </c>
       <c r="D27" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E27" t="s">
         <v>51</v>
@@ -5842,21 +5900,21 @@
         <v>62</v>
       </c>
       <c r="G27" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.2">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>67</v>
       </c>
       <c r="B28" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C28" t="s">
         <v>35</v>
       </c>
       <c r="D28" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E28" t="s">
         <v>51</v>
@@ -5868,64 +5926,64 @@
         <v>64</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>67</v>
       </c>
       <c r="B29" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C29" t="s">
         <v>35</v>
       </c>
       <c r="D29" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E29" t="s">
         <v>51</v>
       </c>
       <c r="F29" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="G29" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>67</v>
       </c>
       <c r="B30" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C30" t="s">
         <v>35</v>
       </c>
       <c r="D30" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E30" t="s">
         <v>51</v>
       </c>
       <c r="F30" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="G30" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>67</v>
       </c>
       <c r="B31" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C31" t="s">
         <v>36</v>
       </c>
       <c r="D31" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E31" t="s">
         <v>52</v>
@@ -5934,21 +5992,21 @@
         <v>62</v>
       </c>
       <c r="G31" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>67</v>
       </c>
       <c r="B32" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C32" t="s">
         <v>36</v>
       </c>
       <c r="D32" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E32" t="s">
         <v>52</v>
@@ -5960,64 +6018,64 @@
         <v>64</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>67</v>
       </c>
       <c r="B33" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C33" t="s">
         <v>36</v>
       </c>
       <c r="D33" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E33" t="s">
         <v>52</v>
       </c>
       <c r="F33" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="G33" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.2">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>67</v>
       </c>
       <c r="B34" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C34" t="s">
         <v>36</v>
       </c>
       <c r="D34" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E34" t="s">
         <v>52</v>
       </c>
       <c r="F34" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="G34" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.2">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>67</v>
       </c>
       <c r="B35" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C35" t="s">
         <v>37</v>
       </c>
       <c r="D35" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E35" t="s">
         <v>53</v>
@@ -6026,21 +6084,21 @@
         <v>62</v>
       </c>
       <c r="G35" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.2">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>67</v>
       </c>
       <c r="B36" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C36" t="s">
         <v>37</v>
       </c>
       <c r="D36" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E36" t="s">
         <v>53</v>
@@ -6052,64 +6110,64 @@
         <v>64</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>67</v>
       </c>
       <c r="B37" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C37" t="s">
         <v>37</v>
       </c>
       <c r="D37" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E37" t="s">
         <v>53</v>
       </c>
       <c r="F37" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="G37" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.2">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>67</v>
       </c>
       <c r="B38" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C38" t="s">
         <v>37</v>
       </c>
       <c r="D38" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E38" t="s">
         <v>53</v>
       </c>
       <c r="F38" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="G38" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.2">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>67</v>
       </c>
       <c r="B39" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C39" t="s">
         <v>38</v>
       </c>
       <c r="D39" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E39" t="s">
         <v>54</v>
@@ -6118,21 +6176,21 @@
         <v>62</v>
       </c>
       <c r="G39" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.2">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>67</v>
       </c>
       <c r="B40" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C40" t="s">
         <v>38</v>
       </c>
       <c r="D40" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E40" t="s">
         <v>54</v>
@@ -6144,64 +6202,64 @@
         <v>64</v>
       </c>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>67</v>
       </c>
       <c r="B41" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C41" t="s">
         <v>38</v>
       </c>
       <c r="D41" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E41" t="s">
         <v>54</v>
       </c>
       <c r="F41" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="G41" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.2">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>67</v>
       </c>
       <c r="B42" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C42" t="s">
         <v>38</v>
       </c>
       <c r="D42" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E42" t="s">
         <v>54</v>
       </c>
       <c r="F42" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="G42" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.2">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>67</v>
       </c>
       <c r="B43" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C43" t="s">
         <v>39</v>
       </c>
       <c r="D43" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E43" t="s">
         <v>55</v>
@@ -6210,21 +6268,21 @@
         <v>62</v>
       </c>
       <c r="G43" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.2">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>67</v>
       </c>
       <c r="B44" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C44" t="s">
         <v>39</v>
       </c>
       <c r="D44" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E44" t="s">
         <v>55</v>
@@ -6236,64 +6294,64 @@
         <v>64</v>
       </c>
     </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>67</v>
       </c>
       <c r="B45" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C45" t="s">
         <v>39</v>
       </c>
       <c r="D45" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E45" t="s">
         <v>55</v>
       </c>
       <c r="F45" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="G45" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.2">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>67</v>
       </c>
       <c r="B46" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C46" t="s">
         <v>39</v>
       </c>
       <c r="D46" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E46" t="s">
         <v>55</v>
       </c>
       <c r="F46" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="G46" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.2">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>67</v>
       </c>
       <c r="B47" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C47" t="s">
         <v>40</v>
       </c>
       <c r="D47" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E47" t="s">
         <v>56</v>
@@ -6302,21 +6360,21 @@
         <v>62</v>
       </c>
       <c r="G47" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.2">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>67</v>
       </c>
       <c r="B48" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C48" t="s">
         <v>40</v>
       </c>
       <c r="D48" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E48" t="s">
         <v>56</v>
@@ -6328,64 +6386,64 @@
         <v>64</v>
       </c>
     </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>67</v>
       </c>
       <c r="B49" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C49" t="s">
         <v>40</v>
       </c>
       <c r="D49" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E49" t="s">
         <v>56</v>
       </c>
       <c r="F49" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="G49" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.2">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>67</v>
       </c>
       <c r="B50" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C50" t="s">
         <v>40</v>
       </c>
       <c r="D50" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E50" t="s">
         <v>56</v>
       </c>
       <c r="F50" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="G50" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.2">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>67</v>
       </c>
       <c r="B52" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C52" t="s">
         <v>49</v>
       </c>
       <c r="D52" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E52" t="s">
         <v>27</v>
@@ -6397,18 +6455,18 @@
         <v>64</v>
       </c>
     </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>67</v>
       </c>
       <c r="B53" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C53" t="s">
         <v>50</v>
       </c>
       <c r="D53" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E53" t="s">
         <v>27</v>
@@ -6420,18 +6478,18 @@
         <v>64</v>
       </c>
     </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>67</v>
       </c>
       <c r="B54" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C54" t="s">
         <v>51</v>
       </c>
       <c r="D54" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E54" t="s">
         <v>27</v>
@@ -6443,18 +6501,18 @@
         <v>64</v>
       </c>
     </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>67</v>
       </c>
       <c r="B55" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C55" t="s">
         <v>52</v>
       </c>
       <c r="D55" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E55" t="s">
         <v>27</v>
@@ -6466,18 +6524,18 @@
         <v>64</v>
       </c>
     </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>67</v>
       </c>
       <c r="B56" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C56" t="s">
         <v>53</v>
       </c>
       <c r="D56" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E56" t="s">
         <v>27</v>
@@ -6489,18 +6547,18 @@
         <v>64</v>
       </c>
     </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>67</v>
       </c>
       <c r="B57" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C57" t="s">
         <v>54</v>
       </c>
       <c r="D57" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E57" t="s">
         <v>27</v>
@@ -6512,18 +6570,18 @@
         <v>64</v>
       </c>
     </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>67</v>
       </c>
       <c r="B58" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C58" t="s">
         <v>55</v>
       </c>
       <c r="D58" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E58" t="s">
         <v>27</v>
@@ -6535,18 +6593,18 @@
         <v>64</v>
       </c>
     </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>67</v>
       </c>
       <c r="B59" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C59" t="s">
         <v>56</v>
       </c>
       <c r="D59" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E59" t="s">
         <v>27</v>
@@ -6558,18 +6616,18 @@
         <v>64</v>
       </c>
     </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>67</v>
       </c>
       <c r="B61" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C61" t="s">
         <v>49</v>
       </c>
       <c r="D61" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E61" t="s">
         <v>28</v>
@@ -6578,90 +6636,90 @@
         <v>62</v>
       </c>
       <c r="G61" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.2">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="62" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>67</v>
       </c>
       <c r="B62" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C62" t="s">
         <v>49</v>
       </c>
       <c r="D62" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E62" t="s">
         <v>28</v>
       </c>
       <c r="F62" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="G62" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.2">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="63" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>67</v>
       </c>
       <c r="B63" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C63" t="s">
         <v>49</v>
       </c>
       <c r="D63" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E63" t="s">
         <v>28</v>
       </c>
       <c r="F63" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="G63" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.2">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="64" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>67</v>
       </c>
       <c r="B64" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C64" t="s">
         <v>49</v>
       </c>
       <c r="D64" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E64" t="s">
         <v>28</v>
       </c>
       <c r="F64" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="G64" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="65" spans="1:7" x14ac:dyDescent="0.2">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="65" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>67</v>
       </c>
       <c r="B65" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C65" t="s">
         <v>50</v>
       </c>
       <c r="D65" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E65" t="s">
         <v>28</v>
@@ -6670,90 +6728,90 @@
         <v>62</v>
       </c>
       <c r="G65" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="66" spans="1:7" x14ac:dyDescent="0.2">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="66" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>67</v>
       </c>
       <c r="B66" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C66" t="s">
         <v>50</v>
       </c>
       <c r="D66" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E66" t="s">
         <v>28</v>
       </c>
       <c r="F66" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="G66" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="67" spans="1:7" x14ac:dyDescent="0.2">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="67" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>67</v>
       </c>
       <c r="B67" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C67" t="s">
         <v>50</v>
       </c>
       <c r="D67" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E67" t="s">
         <v>28</v>
       </c>
       <c r="F67" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="G67" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="68" spans="1:7" x14ac:dyDescent="0.2">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="68" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>67</v>
       </c>
       <c r="B68" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C68" t="s">
         <v>50</v>
       </c>
       <c r="D68" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E68" t="s">
         <v>28</v>
       </c>
       <c r="F68" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="G68" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="69" spans="1:7" x14ac:dyDescent="0.2">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="69" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>67</v>
       </c>
       <c r="B69" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C69" t="s">
         <v>51</v>
       </c>
       <c r="D69" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E69" t="s">
         <v>28</v>
@@ -6762,90 +6820,90 @@
         <v>62</v>
       </c>
       <c r="G69" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="70" spans="1:7" x14ac:dyDescent="0.2">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="70" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>67</v>
       </c>
       <c r="B70" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C70" t="s">
         <v>51</v>
       </c>
       <c r="D70" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E70" t="s">
         <v>28</v>
       </c>
       <c r="F70" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="G70" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="71" spans="1:7" x14ac:dyDescent="0.2">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="71" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>67</v>
       </c>
       <c r="B71" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C71" t="s">
         <v>51</v>
       </c>
       <c r="D71" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E71" t="s">
         <v>28</v>
       </c>
       <c r="F71" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="G71" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="72" spans="1:7" x14ac:dyDescent="0.2">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="72" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>67</v>
       </c>
       <c r="B72" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C72" t="s">
         <v>51</v>
       </c>
       <c r="D72" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E72" t="s">
         <v>28</v>
       </c>
       <c r="F72" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="G72" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="73" spans="1:7" x14ac:dyDescent="0.2">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="73" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>67</v>
       </c>
       <c r="B73" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C73" t="s">
         <v>52</v>
       </c>
       <c r="D73" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E73" t="s">
         <v>28</v>
@@ -6854,90 +6912,90 @@
         <v>62</v>
       </c>
       <c r="G73" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="74" spans="1:7" x14ac:dyDescent="0.2">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="74" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>67</v>
       </c>
       <c r="B74" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C74" t="s">
         <v>52</v>
       </c>
       <c r="D74" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E74" t="s">
         <v>28</v>
       </c>
       <c r="F74" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="G74" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="75" spans="1:7" x14ac:dyDescent="0.2">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="75" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>67</v>
       </c>
       <c r="B75" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C75" t="s">
         <v>52</v>
       </c>
       <c r="D75" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E75" t="s">
         <v>28</v>
       </c>
       <c r="F75" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="G75" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="76" spans="1:7" x14ac:dyDescent="0.2">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="76" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>67</v>
       </c>
       <c r="B76" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C76" t="s">
         <v>52</v>
       </c>
       <c r="D76" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E76" t="s">
         <v>28</v>
       </c>
       <c r="F76" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="G76" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="77" spans="1:7" x14ac:dyDescent="0.2">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="77" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>67</v>
       </c>
       <c r="B77" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C77" t="s">
         <v>53</v>
       </c>
       <c r="D77" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E77" t="s">
         <v>28</v>
@@ -6946,90 +7004,90 @@
         <v>62</v>
       </c>
       <c r="G77" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="78" spans="1:7" x14ac:dyDescent="0.2">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="78" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>67</v>
       </c>
       <c r="B78" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C78" t="s">
         <v>53</v>
       </c>
       <c r="D78" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E78" t="s">
         <v>28</v>
       </c>
       <c r="F78" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="G78" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="79" spans="1:7" x14ac:dyDescent="0.2">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="79" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>67</v>
       </c>
       <c r="B79" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C79" t="s">
         <v>53</v>
       </c>
       <c r="D79" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E79" t="s">
         <v>28</v>
       </c>
       <c r="F79" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="G79" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="80" spans="1:7" x14ac:dyDescent="0.2">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="80" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>67</v>
       </c>
       <c r="B80" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C80" t="s">
         <v>53</v>
       </c>
       <c r="D80" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E80" t="s">
         <v>28</v>
       </c>
       <c r="F80" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="G80" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="81" spans="1:7" x14ac:dyDescent="0.2">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="81" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>67</v>
       </c>
       <c r="B81" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C81" t="s">
         <v>54</v>
       </c>
       <c r="D81" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E81" t="s">
         <v>28</v>
@@ -7038,90 +7096,90 @@
         <v>62</v>
       </c>
       <c r="G81" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="82" spans="1:7" x14ac:dyDescent="0.2">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="82" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>67</v>
       </c>
       <c r="B82" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C82" t="s">
         <v>54</v>
       </c>
       <c r="D82" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E82" t="s">
         <v>28</v>
       </c>
       <c r="F82" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="G82" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="83" spans="1:7" x14ac:dyDescent="0.2">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="83" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>67</v>
       </c>
       <c r="B83" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C83" t="s">
         <v>54</v>
       </c>
       <c r="D83" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E83" t="s">
         <v>28</v>
       </c>
       <c r="F83" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="G83" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="84" spans="1:7" x14ac:dyDescent="0.2">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="84" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>67</v>
       </c>
       <c r="B84" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C84" t="s">
         <v>54</v>
       </c>
       <c r="D84" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E84" t="s">
         <v>28</v>
       </c>
       <c r="F84" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="G84" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="85" spans="1:7" x14ac:dyDescent="0.2">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="85" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>67</v>
       </c>
       <c r="B85" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C85" t="s">
         <v>55</v>
       </c>
       <c r="D85" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E85" t="s">
         <v>28</v>
@@ -7130,90 +7188,90 @@
         <v>62</v>
       </c>
       <c r="G85" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="86" spans="1:7" x14ac:dyDescent="0.2">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="86" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>67</v>
       </c>
       <c r="B86" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C86" t="s">
         <v>55</v>
       </c>
       <c r="D86" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E86" t="s">
         <v>28</v>
       </c>
       <c r="F86" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="G86" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="87" spans="1:7" x14ac:dyDescent="0.2">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="87" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>67</v>
       </c>
       <c r="B87" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C87" t="s">
         <v>55</v>
       </c>
       <c r="D87" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E87" t="s">
         <v>28</v>
       </c>
       <c r="F87" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="G87" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="88" spans="1:7" x14ac:dyDescent="0.2">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="88" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>67</v>
       </c>
       <c r="B88" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C88" t="s">
         <v>55</v>
       </c>
       <c r="D88" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E88" t="s">
         <v>28</v>
       </c>
       <c r="F88" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="G88" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="89" spans="1:7" x14ac:dyDescent="0.2">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="89" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>67</v>
       </c>
       <c r="B89" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C89" t="s">
         <v>56</v>
       </c>
       <c r="D89" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E89" t="s">
         <v>28</v>
@@ -7222,881 +7280,881 @@
         <v>62</v>
       </c>
       <c r="G89" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="90" spans="1:7" x14ac:dyDescent="0.2">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="90" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>67</v>
       </c>
       <c r="B90" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C90" t="s">
         <v>56</v>
       </c>
       <c r="D90" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E90" t="s">
         <v>28</v>
       </c>
       <c r="F90" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="G90" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="91" spans="1:7" x14ac:dyDescent="0.2">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="91" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>67</v>
       </c>
       <c r="B91" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C91" t="s">
         <v>56</v>
       </c>
       <c r="D91" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E91" t="s">
         <v>28</v>
       </c>
       <c r="F91" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="G91" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="92" spans="1:7" x14ac:dyDescent="0.2">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="92" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>67</v>
       </c>
       <c r="B92" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C92" t="s">
         <v>56</v>
       </c>
       <c r="D92" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E92" t="s">
         <v>28</v>
       </c>
       <c r="F92" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="G92" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="94" spans="1:7" x14ac:dyDescent="0.2">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="94" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>67</v>
       </c>
       <c r="B94" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C94" t="s">
         <v>49</v>
       </c>
       <c r="D94" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E94" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="F94" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="G94" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="95" spans="1:7" x14ac:dyDescent="0.2">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="95" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>67</v>
       </c>
       <c r="B95" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C95" t="s">
         <v>49</v>
       </c>
       <c r="D95" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E95" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="F95" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="G95" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="96" spans="1:7" x14ac:dyDescent="0.2">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="96" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>67</v>
       </c>
       <c r="B96" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C96" t="s">
         <v>49</v>
       </c>
       <c r="D96" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E96" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="F96" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="G96" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="97" spans="1:7" x14ac:dyDescent="0.2">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="97" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>67</v>
       </c>
       <c r="B97" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C97" t="s">
         <v>50</v>
       </c>
       <c r="D97" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E97" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="F97" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="G97" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="98" spans="1:7" x14ac:dyDescent="0.2">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="98" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>67</v>
       </c>
       <c r="B98" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C98" t="s">
         <v>50</v>
       </c>
       <c r="D98" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E98" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="F98" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="G98" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="99" spans="1:7" x14ac:dyDescent="0.2">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="99" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>67</v>
       </c>
       <c r="B99" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C99" t="s">
         <v>50</v>
       </c>
       <c r="D99" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E99" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="F99" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="G99" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="100" spans="1:7" x14ac:dyDescent="0.2">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="100" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>67</v>
       </c>
       <c r="B100" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C100" t="s">
         <v>51</v>
       </c>
       <c r="D100" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E100" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F100" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="G100" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="101" spans="1:7" x14ac:dyDescent="0.2">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="101" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
         <v>67</v>
       </c>
       <c r="B101" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C101" t="s">
         <v>51</v>
       </c>
       <c r="D101" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E101" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F101" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="G101" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="102" spans="1:7" x14ac:dyDescent="0.2">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="102" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
         <v>67</v>
       </c>
       <c r="B102" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C102" t="s">
         <v>51</v>
       </c>
       <c r="D102" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E102" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F102" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="G102" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="103" spans="1:7" x14ac:dyDescent="0.2">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="103" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
         <v>67</v>
       </c>
       <c r="B103" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C103" t="s">
         <v>52</v>
       </c>
       <c r="D103" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E103" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="F103" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="G103" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="104" spans="1:7" x14ac:dyDescent="0.2">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="104" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
         <v>67</v>
       </c>
       <c r="B104" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C104" t="s">
         <v>52</v>
       </c>
       <c r="D104" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E104" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="F104" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="G104" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="105" spans="1:7" x14ac:dyDescent="0.2">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="105" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
         <v>67</v>
       </c>
       <c r="B105" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C105" t="s">
         <v>52</v>
       </c>
       <c r="D105" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E105" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="F105" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="G105" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="106" spans="1:7" x14ac:dyDescent="0.2">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="106" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
         <v>67</v>
       </c>
       <c r="B106" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C106" t="s">
         <v>53</v>
       </c>
       <c r="D106" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E106" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="F106" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="G106" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="107" spans="1:7" x14ac:dyDescent="0.2">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="107" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
         <v>67</v>
       </c>
       <c r="B107" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C107" t="s">
         <v>53</v>
       </c>
       <c r="D107" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E107" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="F107" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="G107" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="108" spans="1:7" x14ac:dyDescent="0.2">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="108" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
         <v>67</v>
       </c>
       <c r="B108" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C108" t="s">
         <v>53</v>
       </c>
       <c r="D108" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E108" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="F108" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="G108" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="109" spans="1:7" x14ac:dyDescent="0.2">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="109" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
         <v>67</v>
       </c>
       <c r="B109" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C109" t="s">
         <v>54</v>
       </c>
       <c r="D109" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E109" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="F109" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="G109" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="110" spans="1:7" x14ac:dyDescent="0.2">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="110" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
         <v>67</v>
       </c>
       <c r="B110" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C110" t="s">
         <v>54</v>
       </c>
       <c r="D110" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E110" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="F110" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="G110" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="111" spans="1:7" x14ac:dyDescent="0.2">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="111" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
         <v>67</v>
       </c>
       <c r="B111" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C111" t="s">
         <v>54</v>
       </c>
       <c r="D111" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E111" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="F111" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="G111" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="112" spans="1:7" x14ac:dyDescent="0.2">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="112" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
         <v>67</v>
       </c>
       <c r="B112" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C112" t="s">
         <v>55</v>
       </c>
       <c r="D112" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E112" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="F112" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="G112" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="113" spans="1:7" x14ac:dyDescent="0.2">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="113" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
         <v>67</v>
       </c>
       <c r="B113" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C113" t="s">
         <v>55</v>
       </c>
       <c r="D113" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E113" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="F113" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="G113" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="114" spans="1:7" x14ac:dyDescent="0.2">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="114" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
         <v>67</v>
       </c>
       <c r="B114" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C114" t="s">
         <v>55</v>
       </c>
       <c r="D114" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E114" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="F114" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="G114" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="115" spans="1:7" x14ac:dyDescent="0.2">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="115" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
         <v>67</v>
       </c>
       <c r="B115" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C115" t="s">
         <v>56</v>
       </c>
       <c r="D115" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E115" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="F115" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="G115" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="116" spans="1:7" x14ac:dyDescent="0.2">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="116" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
         <v>67</v>
       </c>
       <c r="B116" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C116" t="s">
         <v>56</v>
       </c>
       <c r="D116" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E116" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="F116" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="G116" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="117" spans="1:7" x14ac:dyDescent="0.2">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="117" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
         <v>67</v>
       </c>
       <c r="B117" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C117" t="s">
         <v>56</v>
       </c>
       <c r="D117" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E117" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="F117" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="G117" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="119" spans="1:7" x14ac:dyDescent="0.2">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="119" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
         <v>67</v>
       </c>
       <c r="B119" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C119" t="s">
+        <v>110</v>
+      </c>
+      <c r="D119" t="s">
+        <v>99</v>
+      </c>
+      <c r="E119" t="s">
+        <v>108</v>
+      </c>
+      <c r="F119" t="s">
+        <v>94</v>
+      </c>
+      <c r="G119" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="120" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A120" t="s">
+        <v>67</v>
+      </c>
+      <c r="B120" t="s">
+        <v>99</v>
+      </c>
+      <c r="C120" t="s">
         <v>111</v>
       </c>
-      <c r="D119" t="s">
-        <v>100</v>
-      </c>
-      <c r="E119" t="s">
-        <v>109</v>
-      </c>
-      <c r="F119" t="s">
-        <v>95</v>
-      </c>
-      <c r="G119" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="120" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A120" t="s">
-        <v>67</v>
-      </c>
-      <c r="B120" t="s">
-        <v>100</v>
-      </c>
-      <c r="C120" t="s">
+      <c r="D120" t="s">
+        <v>99</v>
+      </c>
+      <c r="E120" t="s">
+        <v>108</v>
+      </c>
+      <c r="F120" t="s">
+        <v>94</v>
+      </c>
+      <c r="G120" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="121" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A121" t="s">
+        <v>67</v>
+      </c>
+      <c r="B121" t="s">
+        <v>99</v>
+      </c>
+      <c r="C121" t="s">
         <v>112</v>
       </c>
-      <c r="D120" t="s">
-        <v>100</v>
-      </c>
-      <c r="E120" t="s">
-        <v>109</v>
-      </c>
-      <c r="F120" t="s">
-        <v>95</v>
-      </c>
-      <c r="G120" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="121" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A121" t="s">
-        <v>67</v>
-      </c>
-      <c r="B121" t="s">
-        <v>100</v>
-      </c>
-      <c r="C121" t="s">
+      <c r="D121" t="s">
+        <v>99</v>
+      </c>
+      <c r="E121" t="s">
+        <v>108</v>
+      </c>
+      <c r="F121" t="s">
+        <v>94</v>
+      </c>
+      <c r="G121" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="122" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A122" t="s">
+        <v>67</v>
+      </c>
+      <c r="B122" t="s">
+        <v>99</v>
+      </c>
+      <c r="C122" t="s">
         <v>113</v>
       </c>
-      <c r="D121" t="s">
-        <v>100</v>
-      </c>
-      <c r="E121" t="s">
-        <v>109</v>
-      </c>
-      <c r="F121" t="s">
-        <v>95</v>
-      </c>
-      <c r="G121" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="122" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A122" t="s">
-        <v>67</v>
-      </c>
-      <c r="B122" t="s">
-        <v>100</v>
-      </c>
-      <c r="C122" t="s">
+      <c r="D122" t="s">
+        <v>99</v>
+      </c>
+      <c r="E122" t="s">
+        <v>108</v>
+      </c>
+      <c r="F122" t="s">
+        <v>94</v>
+      </c>
+      <c r="G122" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="123" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A123" t="s">
+        <v>67</v>
+      </c>
+      <c r="B123" t="s">
+        <v>99</v>
+      </c>
+      <c r="C123" t="s">
         <v>114</v>
       </c>
-      <c r="D122" t="s">
-        <v>100</v>
-      </c>
-      <c r="E122" t="s">
-        <v>109</v>
-      </c>
-      <c r="F122" t="s">
-        <v>95</v>
-      </c>
-      <c r="G122" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="123" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A123" t="s">
-        <v>67</v>
-      </c>
-      <c r="B123" t="s">
-        <v>100</v>
-      </c>
-      <c r="C123" t="s">
+      <c r="D123" t="s">
+        <v>99</v>
+      </c>
+      <c r="E123" t="s">
+        <v>108</v>
+      </c>
+      <c r="F123" t="s">
+        <v>94</v>
+      </c>
+      <c r="G123" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="124" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A124" t="s">
+        <v>67</v>
+      </c>
+      <c r="B124" t="s">
+        <v>99</v>
+      </c>
+      <c r="C124" t="s">
         <v>115</v>
       </c>
-      <c r="D123" t="s">
-        <v>100</v>
-      </c>
-      <c r="E123" t="s">
-        <v>109</v>
-      </c>
-      <c r="F123" t="s">
-        <v>95</v>
-      </c>
-      <c r="G123" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="124" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A124" t="s">
-        <v>67</v>
-      </c>
-      <c r="B124" t="s">
-        <v>100</v>
-      </c>
-      <c r="C124" t="s">
+      <c r="D124" t="s">
+        <v>99</v>
+      </c>
+      <c r="E124" t="s">
+        <v>108</v>
+      </c>
+      <c r="F124" t="s">
+        <v>94</v>
+      </c>
+      <c r="G124" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="125" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A125" t="s">
+        <v>67</v>
+      </c>
+      <c r="B125" t="s">
+        <v>99</v>
+      </c>
+      <c r="C125" t="s">
         <v>116</v>
       </c>
-      <c r="D124" t="s">
-        <v>100</v>
-      </c>
-      <c r="E124" t="s">
-        <v>109</v>
-      </c>
-      <c r="F124" t="s">
-        <v>95</v>
-      </c>
-      <c r="G124" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="125" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A125" t="s">
-        <v>67</v>
-      </c>
-      <c r="B125" t="s">
-        <v>100</v>
-      </c>
-      <c r="C125" t="s">
+      <c r="D125" t="s">
+        <v>99</v>
+      </c>
+      <c r="E125" t="s">
+        <v>108</v>
+      </c>
+      <c r="F125" t="s">
+        <v>94</v>
+      </c>
+      <c r="G125" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="126" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A126" t="s">
+        <v>67</v>
+      </c>
+      <c r="B126" t="s">
+        <v>99</v>
+      </c>
+      <c r="C126" t="s">
         <v>117</v>
       </c>
-      <c r="D125" t="s">
-        <v>100</v>
-      </c>
-      <c r="E125" t="s">
-        <v>109</v>
-      </c>
-      <c r="F125" t="s">
-        <v>95</v>
-      </c>
-      <c r="G125" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="126" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A126" t="s">
-        <v>67</v>
-      </c>
-      <c r="B126" t="s">
-        <v>100</v>
-      </c>
-      <c r="C126" t="s">
-        <v>118</v>
-      </c>
       <c r="D126" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E126" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="F126" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="G126" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="128" spans="1:7" x14ac:dyDescent="0.2">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="128" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
         <v>67</v>
       </c>
       <c r="B128" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C128" t="s">
         <v>28</v>
       </c>
       <c r="D128" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E128" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F128" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="G128" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="129" spans="1:7" x14ac:dyDescent="0.2">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="129" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
         <v>67</v>
       </c>
       <c r="B129" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C129" t="s">
         <v>28</v>
       </c>
       <c r="D129" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E129" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F129" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="G129" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="130" spans="1:7" x14ac:dyDescent="0.2">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="130" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
         <v>67</v>
       </c>
       <c r="B130" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C130" t="s">
         <v>27</v>
       </c>
       <c r="D130" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E130" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F130" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="G130" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
   </sheetData>

--- a/input/Studies/C3/C3_Prototypical_Sites/P3_2stages_VRU.xlsx
+++ b/input/Studies/C3/C3_Prototypical_Sites/P3_2stages_VRU.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28429"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\METEC\MAES2\input\Studies\C3\C3_Prototypical_Sites\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05C12776-A8CD-4C41-8DF5-D8BFFD2CC108}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6406C75A-3480-4A5C-9ADE-3B2B663C3973}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="645" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="925" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Global Simulation Parameters" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1375" uniqueCount="229">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1370" uniqueCount="230">
   <si>
     <t>Simulation Start Date</t>
   </si>
@@ -323,6 +323,9 @@
     <t>Operating Destruction Efficiency</t>
   </si>
   <si>
+    <t>Activity / Emission Factor Name</t>
+  </si>
+  <si>
     <t>Factor Tag</t>
   </si>
   <si>
@@ -653,6 +656,9 @@
     <t>Leak Gas Composition</t>
   </si>
   <si>
+    <t>Output Directory Template</t>
+  </si>
+  <si>
     <t>Facility Type</t>
   </si>
   <si>
@@ -719,16 +725,13 @@
     <t>Max Downstream Equipment Capacity [scfh]</t>
   </si>
   <si>
+    <t>Tank Controlled [True, False]</t>
+  </si>
+  <si>
     <t>Crankcase Emissions Flag [TRUE, FALSE]</t>
   </si>
   <si>
     <t>CCEE Ratio Distribution</t>
-  </si>
-  <si>
-    <t>Actuator Type [Gas, Air, Electric, Gas Mechanistic]</t>
-  </si>
-  <si>
-    <t>Common/CrankcaseDistributions/crankcaseTest.csv</t>
   </si>
 </sst>
 </file>
@@ -790,7 +793,7 @@
       <name val="Calibri"/>
     </font>
   </fonts>
-  <fills count="16">
+  <fills count="17">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -879,6 +882,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="6">
     <border>
@@ -959,10 +968,13 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="6" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="62">
+  <cellXfs count="65">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -997,6 +1009,9 @@
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1107,14 +1122,15 @@
     <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="16" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="16" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -1420,7 +1436,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B4"/>
+  <dimension ref="A1:B6"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="33.42578125" bestFit="1" customWidth="1"/>
@@ -1453,10 +1469,20 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>203</v>
-      </c>
-      <c r="B4" t="s">
         <v>204</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>205</v>
+      </c>
+      <c r="B6" t="s">
+        <v>206</v>
       </c>
     </row>
   </sheetData>
@@ -1491,26 +1517,26 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B3" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B4" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B5" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
@@ -1562,26 +1588,26 @@
     <col min="5" max="5" width="20" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" s="11" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="10" t="s">
+    <row r="1" spans="1:5" s="12" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="11" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="17" t="s">
+      <c r="B1" s="19" t="s">
         <v>5</v>
       </c>
-      <c r="C1" s="10" t="s">
+      <c r="C1" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="D1" s="10" t="s">
-        <v>202</v>
-      </c>
-      <c r="E1" s="10" t="s">
+      <c r="D1" s="11" t="s">
+        <v>203</v>
+      </c>
+      <c r="E1" s="11" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B2">
         <v>40.319454999999998</v>
@@ -1590,7 +1616,7 @@
         <v>-104.912887</v>
       </c>
       <c r="D2" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="E2" t="s">
         <v>65</v>
@@ -1611,74 +1637,74 @@
     <col min="18" max="18" width="63.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" s="18" customFormat="1" ht="90" x14ac:dyDescent="0.25">
-      <c r="A1" s="18" t="s">
+    <row r="1" spans="1:19" s="20" customFormat="1" ht="90" x14ac:dyDescent="0.25">
+      <c r="A1" s="20" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="18" t="s">
+      <c r="B1" s="20" t="s">
         <v>7</v>
       </c>
-      <c r="C1" s="18" t="s">
+      <c r="C1" s="20" t="s">
         <v>8</v>
       </c>
-      <c r="D1" s="18" t="s">
+      <c r="D1" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="E1" s="18" t="s">
+      <c r="E1" s="20" t="s">
         <v>6</v>
       </c>
-      <c r="F1" s="19" t="s">
+      <c r="F1" s="21" t="s">
         <v>68</v>
       </c>
-      <c r="G1" s="19" t="s">
+      <c r="G1" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="H1" s="19" t="s">
+      <c r="H1" s="21" t="s">
         <v>10</v>
       </c>
-      <c r="I1" s="18" t="s">
-        <v>119</v>
-      </c>
-      <c r="J1" s="18" t="s">
+      <c r="I1" s="20" t="s">
         <v>120</v>
       </c>
-      <c r="K1" s="18" t="s">
+      <c r="J1" s="20" t="s">
         <v>121</v>
       </c>
-      <c r="L1" s="18" t="s">
+      <c r="K1" s="20" t="s">
         <v>122</v>
       </c>
-      <c r="M1" s="18" t="s">
+      <c r="L1" s="20" t="s">
         <v>123</v>
       </c>
-      <c r="N1" s="18" t="s">
+      <c r="M1" s="20" t="s">
         <v>124</v>
       </c>
-      <c r="O1" s="18" t="s">
+      <c r="N1" s="20" t="s">
+        <v>125</v>
+      </c>
+      <c r="O1" s="20" t="s">
         <v>86</v>
       </c>
-      <c r="P1" s="18" t="s">
+      <c r="P1" s="20" t="s">
         <v>57</v>
       </c>
-      <c r="Q1" s="18" t="s">
-        <v>189</v>
-      </c>
-      <c r="R1" s="18" t="s">
+      <c r="Q1" s="20" t="s">
+        <v>190</v>
+      </c>
+      <c r="R1" s="20" t="s">
         <v>87</v>
       </c>
-      <c r="S1" s="18" t="s">
-        <v>93</v>
+      <c r="S1" s="20" t="s">
+        <v>94</v>
       </c>
     </row>
     <row r="2" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B2" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C2" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D2">
         <v>0</v>
@@ -1686,13 +1712,13 @@
       <c r="E2">
         <v>0</v>
       </c>
-      <c r="F2" s="20">
+      <c r="F2" s="22">
         <v>365</v>
       </c>
-      <c r="G2" s="20">
+      <c r="G2" s="22">
         <v>48</v>
       </c>
-      <c r="H2" s="20">
+      <c r="H2" s="22">
         <v>5.0000000000000001E-3</v>
       </c>
       <c r="I2">
@@ -1720,24 +1746,24 @@
         <v>58</v>
       </c>
       <c r="Q2" t="s">
+        <v>163</v>
+      </c>
+      <c r="R2" t="s">
         <v>162</v>
       </c>
-      <c r="R2" t="s">
-        <v>161</v>
-      </c>
       <c r="S2" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="3" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B3" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C3" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D3">
         <v>0</v>
@@ -1745,13 +1771,13 @@
       <c r="E3">
         <v>0</v>
       </c>
-      <c r="F3" s="20">
+      <c r="F3" s="22">
         <v>365</v>
       </c>
-      <c r="G3" s="20">
+      <c r="G3" s="22">
         <v>48</v>
       </c>
-      <c r="H3" s="20">
+      <c r="H3" s="22">
         <v>5.0000000000000001E-3</v>
       </c>
       <c r="I3">
@@ -1779,24 +1805,24 @@
         <v>58</v>
       </c>
       <c r="Q3" t="s">
+        <v>163</v>
+      </c>
+      <c r="R3" t="s">
         <v>162</v>
       </c>
-      <c r="R3" t="s">
-        <v>161</v>
-      </c>
       <c r="S3" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B4" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C4" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D4">
         <v>0</v>
@@ -1804,13 +1830,13 @@
       <c r="E4">
         <v>0</v>
       </c>
-      <c r="F4" s="20">
+      <c r="F4" s="22">
         <v>365</v>
       </c>
-      <c r="G4" s="20">
+      <c r="G4" s="22">
         <v>48</v>
       </c>
-      <c r="H4" s="20">
+      <c r="H4" s="22">
         <v>5.0000000000000001E-3</v>
       </c>
       <c r="I4">
@@ -1838,24 +1864,24 @@
         <v>58</v>
       </c>
       <c r="Q4" t="s">
+        <v>163</v>
+      </c>
+      <c r="R4" t="s">
         <v>162</v>
       </c>
-      <c r="R4" t="s">
-        <v>161</v>
-      </c>
       <c r="S4" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="5" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B5" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C5" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D5">
         <v>0</v>
@@ -1863,13 +1889,13 @@
       <c r="E5">
         <v>0</v>
       </c>
-      <c r="F5" s="20">
+      <c r="F5" s="22">
         <v>365</v>
       </c>
-      <c r="G5" s="20">
+      <c r="G5" s="22">
         <v>48</v>
       </c>
-      <c r="H5" s="20">
+      <c r="H5" s="22">
         <v>5.0000000000000001E-3</v>
       </c>
       <c r="I5">
@@ -1897,24 +1923,24 @@
         <v>58</v>
       </c>
       <c r="Q5" t="s">
+        <v>163</v>
+      </c>
+      <c r="R5" t="s">
         <v>162</v>
       </c>
-      <c r="R5" t="s">
-        <v>161</v>
-      </c>
       <c r="S5" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="6" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B6" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C6" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D6">
         <v>0</v>
@@ -1922,13 +1948,13 @@
       <c r="E6">
         <v>0</v>
       </c>
-      <c r="F6" s="20">
+      <c r="F6" s="22">
         <v>365</v>
       </c>
-      <c r="G6" s="20">
+      <c r="G6" s="22">
         <v>48</v>
       </c>
-      <c r="H6" s="20">
+      <c r="H6" s="22">
         <v>5.0000000000000001E-3</v>
       </c>
       <c r="I6">
@@ -1956,24 +1982,24 @@
         <v>58</v>
       </c>
       <c r="Q6" t="s">
+        <v>163</v>
+      </c>
+      <c r="R6" t="s">
         <v>162</v>
       </c>
-      <c r="R6" t="s">
-        <v>161</v>
-      </c>
       <c r="S6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="7" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B7" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C7" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="D7">
         <v>0</v>
@@ -1981,13 +2007,13 @@
       <c r="E7">
         <v>0</v>
       </c>
-      <c r="F7" s="20">
+      <c r="F7" s="22">
         <v>365</v>
       </c>
-      <c r="G7" s="20">
+      <c r="G7" s="22">
         <v>48</v>
       </c>
-      <c r="H7" s="20">
+      <c r="H7" s="22">
         <v>5.0000000000000001E-3</v>
       </c>
       <c r="I7">
@@ -2015,24 +2041,24 @@
         <v>58</v>
       </c>
       <c r="Q7" t="s">
+        <v>163</v>
+      </c>
+      <c r="R7" t="s">
         <v>162</v>
       </c>
-      <c r="R7" t="s">
-        <v>161</v>
-      </c>
       <c r="S7" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="8" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B8" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C8" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D8">
         <v>0</v>
@@ -2040,13 +2066,13 @@
       <c r="E8">
         <v>0</v>
       </c>
-      <c r="F8" s="20">
+      <c r="F8" s="22">
         <v>365</v>
       </c>
-      <c r="G8" s="20">
+      <c r="G8" s="22">
         <v>48</v>
       </c>
-      <c r="H8" s="20">
+      <c r="H8" s="22">
         <v>5.0000000000000001E-3</v>
       </c>
       <c r="I8">
@@ -2074,24 +2100,24 @@
         <v>58</v>
       </c>
       <c r="Q8" t="s">
+        <v>163</v>
+      </c>
+      <c r="R8" t="s">
         <v>162</v>
       </c>
-      <c r="R8" t="s">
-        <v>161</v>
-      </c>
       <c r="S8" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="9" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B9" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C9" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D9">
         <v>0</v>
@@ -2099,13 +2125,13 @@
       <c r="E9">
         <v>0</v>
       </c>
-      <c r="F9" s="20">
+      <c r="F9" s="22">
         <v>365</v>
       </c>
-      <c r="G9" s="20">
+      <c r="G9" s="22">
         <v>48</v>
       </c>
-      <c r="H9" s="20">
+      <c r="H9" s="22">
         <v>5.0000000000000001E-3</v>
       </c>
       <c r="I9">
@@ -2133,13 +2159,13 @@
         <v>58</v>
       </c>
       <c r="Q9" t="s">
+        <v>163</v>
+      </c>
+      <c r="R9" t="s">
         <v>162</v>
       </c>
-      <c r="R9" t="s">
-        <v>161</v>
-      </c>
       <c r="S9" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
   </sheetData>
@@ -2153,461 +2179,461 @@
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="5" width="15.7109375" customWidth="1"/>
-    <col min="6" max="13" width="15.7109375" style="3" customWidth="1"/>
+    <col min="6" max="13" width="15.7109375" style="4" customWidth="1"/>
     <col min="14" max="14" width="24.42578125" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="47.140625" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="15.7109375" customWidth="1"/>
     <col min="17" max="17" width="18.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" s="2" customFormat="1" ht="60" x14ac:dyDescent="0.25">
-      <c r="A1" s="15" t="s">
+    <row r="1" spans="1:16" s="3" customFormat="1" ht="60" x14ac:dyDescent="0.25">
+      <c r="A1" s="16" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="15" t="s">
+      <c r="B1" s="16" t="s">
         <v>8</v>
       </c>
-      <c r="C1" s="16" t="s">
+      <c r="C1" s="17" t="s">
         <v>68</v>
       </c>
-      <c r="D1" s="16" t="s">
+      <c r="D1" s="17" t="s">
         <v>9</v>
       </c>
-      <c r="E1" s="16" t="s">
+      <c r="E1" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="F1" s="15" t="s">
+      <c r="F1" s="16" t="s">
         <v>86</v>
       </c>
-      <c r="G1" s="21" t="s">
-        <v>126</v>
-      </c>
-      <c r="H1" s="21" t="s">
+      <c r="G1" s="23" t="s">
         <v>127</v>
       </c>
-      <c r="I1" s="21" t="s">
+      <c r="H1" s="23" t="s">
         <v>128</v>
       </c>
-      <c r="J1" s="21" t="s">
+      <c r="I1" s="23" t="s">
         <v>129</v>
       </c>
-      <c r="K1" s="21" t="s">
+      <c r="J1" s="23" t="s">
         <v>130</v>
       </c>
-      <c r="L1" s="15" t="s">
+      <c r="K1" s="23" t="s">
+        <v>131</v>
+      </c>
+      <c r="L1" s="16" t="s">
         <v>32</v>
       </c>
-      <c r="M1" s="15" t="s">
+      <c r="M1" s="16" t="s">
         <v>59</v>
       </c>
-      <c r="N1" s="15" t="s">
+      <c r="N1" s="16" t="s">
         <v>7</v>
       </c>
-      <c r="O1" s="15" t="s">
-        <v>189</v>
-      </c>
-      <c r="P1" s="15" t="s">
-        <v>93</v>
+      <c r="O1" s="16" t="s">
+        <v>190</v>
+      </c>
+      <c r="P1" s="16" t="s">
+        <v>94</v>
       </c>
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B2" t="s">
         <v>33</v>
       </c>
-      <c r="C2" s="7">
+      <c r="C2" s="8">
         <v>365</v>
       </c>
-      <c r="D2" s="7">
+      <c r="D2" s="8">
         <v>62</v>
       </c>
-      <c r="E2" s="7">
+      <c r="E2" s="8">
         <v>5.9867000000000002E-3</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="F2" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="G2" s="22">
-        <v>1</v>
-      </c>
-      <c r="H2" s="22">
+      <c r="G2" s="24">
+        <v>1</v>
+      </c>
+      <c r="H2" s="24">
         <v>0.01</v>
       </c>
-      <c r="I2" s="22">
-        <v>1</v>
-      </c>
-      <c r="J2" s="22">
+      <c r="I2" s="24">
+        <v>1</v>
+      </c>
+      <c r="J2" s="24">
         <v>20</v>
       </c>
-      <c r="K2" s="22" t="s">
-        <v>205</v>
-      </c>
-      <c r="L2" s="3">
+      <c r="K2" s="24" t="s">
+        <v>207</v>
+      </c>
+      <c r="L2" s="4">
         <v>0.75</v>
       </c>
-      <c r="M2" s="3" t="s">
+      <c r="M2" s="4" t="s">
         <v>60</v>
       </c>
       <c r="N2" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="O2" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="P2" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B3" t="s">
         <v>34</v>
       </c>
-      <c r="C3" s="7">
+      <c r="C3" s="8">
         <v>365</v>
       </c>
-      <c r="D3" s="7">
+      <c r="D3" s="8">
         <v>62</v>
       </c>
-      <c r="E3" s="7">
+      <c r="E3" s="8">
         <v>5.9867000000000002E-3</v>
       </c>
-      <c r="F3" s="3" t="s">
+      <c r="F3" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="G3" s="22">
-        <v>1</v>
-      </c>
-      <c r="H3" s="22">
+      <c r="G3" s="24">
+        <v>1</v>
+      </c>
+      <c r="H3" s="24">
         <v>0.01</v>
       </c>
-      <c r="I3" s="22">
-        <v>1</v>
-      </c>
-      <c r="J3" s="22">
+      <c r="I3" s="24">
+        <v>1</v>
+      </c>
+      <c r="J3" s="24">
         <v>20</v>
       </c>
-      <c r="K3" s="22" t="s">
-        <v>205</v>
-      </c>
-      <c r="L3" s="3">
+      <c r="K3" s="24" t="s">
+        <v>207</v>
+      </c>
+      <c r="L3" s="4">
         <v>0.75</v>
       </c>
-      <c r="M3" s="3" t="s">
+      <c r="M3" s="4" t="s">
         <v>60</v>
       </c>
       <c r="N3" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="O3" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="P3" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="4" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B4" t="s">
         <v>35</v>
       </c>
-      <c r="C4" s="7">
+      <c r="C4" s="8">
         <v>365</v>
       </c>
-      <c r="D4" s="7">
+      <c r="D4" s="8">
         <v>62</v>
       </c>
-      <c r="E4" s="7">
+      <c r="E4" s="8">
         <v>5.9867000000000002E-3</v>
       </c>
-      <c r="F4" s="3" t="s">
+      <c r="F4" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="G4" s="22">
-        <v>1</v>
-      </c>
-      <c r="H4" s="22">
+      <c r="G4" s="24">
+        <v>1</v>
+      </c>
+      <c r="H4" s="24">
         <v>0.01</v>
       </c>
-      <c r="I4" s="22">
-        <v>1</v>
-      </c>
-      <c r="J4" s="22">
+      <c r="I4" s="24">
+        <v>1</v>
+      </c>
+      <c r="J4" s="24">
         <v>20</v>
       </c>
-      <c r="K4" s="22" t="s">
-        <v>205</v>
-      </c>
-      <c r="L4" s="3">
+      <c r="K4" s="24" t="s">
+        <v>207</v>
+      </c>
+      <c r="L4" s="4">
         <v>0.75</v>
       </c>
-      <c r="M4" s="3" t="s">
+      <c r="M4" s="4" t="s">
         <v>60</v>
       </c>
       <c r="N4" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="O4" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="P4" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B5" t="s">
         <v>36</v>
       </c>
-      <c r="C5" s="7">
+      <c r="C5" s="8">
         <v>365</v>
       </c>
-      <c r="D5" s="7">
+      <c r="D5" s="8">
         <v>62</v>
       </c>
-      <c r="E5" s="7">
+      <c r="E5" s="8">
         <v>5.9867000000000002E-3</v>
       </c>
-      <c r="F5" s="3" t="s">
+      <c r="F5" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="G5" s="22">
-        <v>1</v>
-      </c>
-      <c r="H5" s="22">
+      <c r="G5" s="24">
+        <v>1</v>
+      </c>
+      <c r="H5" s="24">
         <v>0.01</v>
       </c>
-      <c r="I5" s="22">
-        <v>1</v>
-      </c>
-      <c r="J5" s="22">
+      <c r="I5" s="24">
+        <v>1</v>
+      </c>
+      <c r="J5" s="24">
         <v>20</v>
       </c>
-      <c r="K5" s="22" t="s">
-        <v>205</v>
-      </c>
-      <c r="L5" s="3">
+      <c r="K5" s="24" t="s">
+        <v>207</v>
+      </c>
+      <c r="L5" s="4">
         <v>0.75</v>
       </c>
-      <c r="M5" s="3" t="s">
+      <c r="M5" s="4" t="s">
         <v>60</v>
       </c>
       <c r="N5" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="O5" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="P5" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B6" t="s">
         <v>37</v>
       </c>
-      <c r="C6" s="7">
+      <c r="C6" s="8">
         <v>365</v>
       </c>
-      <c r="D6" s="7">
+      <c r="D6" s="8">
         <v>62</v>
       </c>
-      <c r="E6" s="7">
+      <c r="E6" s="8">
         <v>5.9867000000000002E-3</v>
       </c>
-      <c r="F6" s="3" t="s">
+      <c r="F6" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="G6" s="22">
-        <v>1</v>
-      </c>
-      <c r="H6" s="22">
+      <c r="G6" s="24">
+        <v>1</v>
+      </c>
+      <c r="H6" s="24">
         <v>0.01</v>
       </c>
-      <c r="I6" s="22">
-        <v>1</v>
-      </c>
-      <c r="J6" s="22">
+      <c r="I6" s="24">
+        <v>1</v>
+      </c>
+      <c r="J6" s="24">
         <v>20</v>
       </c>
-      <c r="K6" s="22" t="s">
-        <v>205</v>
-      </c>
-      <c r="L6" s="3">
+      <c r="K6" s="24" t="s">
+        <v>207</v>
+      </c>
+      <c r="L6" s="4">
         <v>0.75</v>
       </c>
-      <c r="M6" s="3" t="s">
+      <c r="M6" s="4" t="s">
         <v>60</v>
       </c>
       <c r="N6" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="O6" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="P6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B7" t="s">
         <v>38</v>
       </c>
-      <c r="C7" s="7">
+      <c r="C7" s="8">
         <v>365</v>
       </c>
-      <c r="D7" s="7">
+      <c r="D7" s="8">
         <v>62</v>
       </c>
-      <c r="E7" s="7">
+      <c r="E7" s="8">
         <v>5.9867000000000002E-3</v>
       </c>
-      <c r="F7" s="3" t="s">
+      <c r="F7" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="G7" s="22">
-        <v>1</v>
-      </c>
-      <c r="H7" s="22">
+      <c r="G7" s="24">
+        <v>1</v>
+      </c>
+      <c r="H7" s="24">
         <v>0.01</v>
       </c>
-      <c r="I7" s="22">
-        <v>1</v>
-      </c>
-      <c r="J7" s="22">
+      <c r="I7" s="24">
+        <v>1</v>
+      </c>
+      <c r="J7" s="24">
         <v>20</v>
       </c>
-      <c r="K7" s="22" t="s">
-        <v>205</v>
-      </c>
-      <c r="L7" s="3">
+      <c r="K7" s="24" t="s">
+        <v>207</v>
+      </c>
+      <c r="L7" s="4">
         <v>0.75</v>
       </c>
-      <c r="M7" s="3" t="s">
+      <c r="M7" s="4" t="s">
         <v>60</v>
       </c>
       <c r="N7" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="O7" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="P7" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="8" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B8" t="s">
         <v>39</v>
       </c>
-      <c r="C8" s="7">
+      <c r="C8" s="8">
         <v>365</v>
       </c>
-      <c r="D8" s="7">
+      <c r="D8" s="8">
         <v>62</v>
       </c>
-      <c r="E8" s="7">
+      <c r="E8" s="8">
         <v>5.9867000000000002E-3</v>
       </c>
-      <c r="F8" s="3" t="s">
+      <c r="F8" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="G8" s="22">
-        <v>1</v>
-      </c>
-      <c r="H8" s="22">
+      <c r="G8" s="24">
+        <v>1</v>
+      </c>
+      <c r="H8" s="24">
         <v>0.01</v>
       </c>
-      <c r="I8" s="22">
-        <v>1</v>
-      </c>
-      <c r="J8" s="22">
+      <c r="I8" s="24">
+        <v>1</v>
+      </c>
+      <c r="J8" s="24">
         <v>20</v>
       </c>
-      <c r="K8" s="22" t="s">
-        <v>205</v>
-      </c>
-      <c r="L8" s="3">
+      <c r="K8" s="24" t="s">
+        <v>207</v>
+      </c>
+      <c r="L8" s="4">
         <v>0.75</v>
       </c>
-      <c r="M8" s="3" t="s">
+      <c r="M8" s="4" t="s">
         <v>60</v>
       </c>
       <c r="N8" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="O8" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="P8" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="9" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B9" t="s">
         <v>40</v>
       </c>
-      <c r="C9" s="7">
+      <c r="C9" s="8">
         <v>365</v>
       </c>
-      <c r="D9" s="7">
+      <c r="D9" s="8">
         <v>62</v>
       </c>
-      <c r="E9" s="7">
+      <c r="E9" s="8">
         <v>5.9867000000000002E-3</v>
       </c>
-      <c r="F9" s="3" t="s">
+      <c r="F9" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="G9" s="22">
-        <v>1</v>
-      </c>
-      <c r="H9" s="22">
+      <c r="G9" s="24">
+        <v>1</v>
+      </c>
+      <c r="H9" s="24">
         <v>0.01</v>
       </c>
-      <c r="I9" s="22">
-        <v>1</v>
-      </c>
-      <c r="J9" s="22">
+      <c r="I9" s="24">
+        <v>1</v>
+      </c>
+      <c r="J9" s="24">
         <v>20</v>
       </c>
-      <c r="K9" s="22" t="s">
-        <v>205</v>
-      </c>
-      <c r="L9" s="3">
+      <c r="K9" s="24" t="s">
+        <v>207</v>
+      </c>
+      <c r="L9" s="4">
         <v>0.75</v>
       </c>
-      <c r="M9" s="3" t="s">
+      <c r="M9" s="4" t="s">
         <v>60</v>
       </c>
       <c r="N9" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="O9" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="P9" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="10" spans="1:16" x14ac:dyDescent="0.25">
@@ -2622,402 +2648,402 @@
     </row>
     <row r="11" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B11" t="s">
         <v>49</v>
       </c>
-      <c r="C11" s="7">
+      <c r="C11" s="8">
         <v>365</v>
       </c>
-      <c r="D11" s="7">
+      <c r="D11" s="8">
         <v>62</v>
       </c>
-      <c r="E11" s="7">
+      <c r="E11" s="8">
         <v>5.9867000000000002E-3</v>
       </c>
-      <c r="F11" s="3" t="s">
+      <c r="F11" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="G11" s="22">
-        <v>1</v>
-      </c>
-      <c r="H11" s="22">
+      <c r="G11" s="24">
+        <v>1</v>
+      </c>
+      <c r="H11" s="24">
         <v>0.01</v>
       </c>
-      <c r="I11" s="22">
-        <v>1</v>
-      </c>
-      <c r="J11" s="22">
+      <c r="I11" s="24">
+        <v>1</v>
+      </c>
+      <c r="J11" s="24">
         <v>20</v>
       </c>
-      <c r="K11" s="22" t="s">
-        <v>205</v>
-      </c>
-      <c r="L11" s="3">
-        <v>1</v>
-      </c>
-      <c r="M11" s="3" t="s">
+      <c r="K11" s="24" t="s">
+        <v>207</v>
+      </c>
+      <c r="L11" s="4">
+        <v>1</v>
+      </c>
+      <c r="M11" s="4" t="s">
         <v>61</v>
       </c>
       <c r="N11" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="O11" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="P11" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="12" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B12" t="s">
         <v>50</v>
       </c>
-      <c r="C12" s="7">
+      <c r="C12" s="8">
         <v>365</v>
       </c>
-      <c r="D12" s="7">
+      <c r="D12" s="8">
         <v>62</v>
       </c>
-      <c r="E12" s="7">
+      <c r="E12" s="8">
         <v>5.9867000000000002E-3</v>
       </c>
-      <c r="F12" s="3" t="s">
+      <c r="F12" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="G12" s="22">
-        <v>1</v>
-      </c>
-      <c r="H12" s="22">
+      <c r="G12" s="24">
+        <v>1</v>
+      </c>
+      <c r="H12" s="24">
         <v>0.01</v>
       </c>
-      <c r="I12" s="22">
-        <v>1</v>
-      </c>
-      <c r="J12" s="22">
+      <c r="I12" s="24">
+        <v>1</v>
+      </c>
+      <c r="J12" s="24">
         <v>20</v>
       </c>
-      <c r="K12" s="22" t="s">
-        <v>205</v>
-      </c>
-      <c r="L12" s="3">
-        <v>1</v>
-      </c>
-      <c r="M12" s="3" t="s">
+      <c r="K12" s="24" t="s">
+        <v>207</v>
+      </c>
+      <c r="L12" s="4">
+        <v>1</v>
+      </c>
+      <c r="M12" s="4" t="s">
         <v>61</v>
       </c>
       <c r="N12" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="O12" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="P12" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="13" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B13" t="s">
         <v>51</v>
       </c>
-      <c r="C13" s="7">
+      <c r="C13" s="8">
         <v>365</v>
       </c>
-      <c r="D13" s="7">
+      <c r="D13" s="8">
         <v>62</v>
       </c>
-      <c r="E13" s="7">
+      <c r="E13" s="8">
         <v>5.9867000000000002E-3</v>
       </c>
-      <c r="F13" s="3" t="s">
+      <c r="F13" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="G13" s="22">
-        <v>1</v>
-      </c>
-      <c r="H13" s="22">
+      <c r="G13" s="24">
+        <v>1</v>
+      </c>
+      <c r="H13" s="24">
         <v>0.01</v>
       </c>
-      <c r="I13" s="22">
-        <v>1</v>
-      </c>
-      <c r="J13" s="22">
+      <c r="I13" s="24">
+        <v>1</v>
+      </c>
+      <c r="J13" s="24">
         <v>20</v>
       </c>
-      <c r="K13" s="22" t="s">
-        <v>205</v>
-      </c>
-      <c r="L13" s="3">
-        <v>1</v>
-      </c>
-      <c r="M13" s="3" t="s">
+      <c r="K13" s="24" t="s">
+        <v>207</v>
+      </c>
+      <c r="L13" s="4">
+        <v>1</v>
+      </c>
+      <c r="M13" s="4" t="s">
         <v>61</v>
       </c>
       <c r="N13" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="O13" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="P13" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="14" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B14" t="s">
         <v>52</v>
       </c>
-      <c r="C14" s="7">
+      <c r="C14" s="8">
         <v>365</v>
       </c>
-      <c r="D14" s="7">
+      <c r="D14" s="8">
         <v>62</v>
       </c>
-      <c r="E14" s="7">
+      <c r="E14" s="8">
         <v>5.9867000000000002E-3</v>
       </c>
-      <c r="F14" s="3" t="s">
+      <c r="F14" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="G14" s="22">
-        <v>1</v>
-      </c>
-      <c r="H14" s="22">
+      <c r="G14" s="24">
+        <v>1</v>
+      </c>
+      <c r="H14" s="24">
         <v>0.01</v>
       </c>
-      <c r="I14" s="22">
-        <v>1</v>
-      </c>
-      <c r="J14" s="22">
+      <c r="I14" s="24">
+        <v>1</v>
+      </c>
+      <c r="J14" s="24">
         <v>20</v>
       </c>
-      <c r="K14" s="22" t="s">
-        <v>205</v>
-      </c>
-      <c r="L14" s="3">
-        <v>1</v>
-      </c>
-      <c r="M14" s="3" t="s">
+      <c r="K14" s="24" t="s">
+        <v>207</v>
+      </c>
+      <c r="L14" s="4">
+        <v>1</v>
+      </c>
+      <c r="M14" s="4" t="s">
         <v>61</v>
       </c>
       <c r="N14" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="O14" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="P14" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="15" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B15" t="s">
         <v>53</v>
       </c>
-      <c r="C15" s="7">
+      <c r="C15" s="8">
         <v>365</v>
       </c>
-      <c r="D15" s="7">
+      <c r="D15" s="8">
         <v>62</v>
       </c>
-      <c r="E15" s="7">
+      <c r="E15" s="8">
         <v>5.9867000000000002E-3</v>
       </c>
-      <c r="F15" s="3" t="s">
+      <c r="F15" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="G15" s="22">
-        <v>1</v>
-      </c>
-      <c r="H15" s="22">
+      <c r="G15" s="24">
+        <v>1</v>
+      </c>
+      <c r="H15" s="24">
         <v>0.01</v>
       </c>
-      <c r="I15" s="22">
-        <v>1</v>
-      </c>
-      <c r="J15" s="22">
+      <c r="I15" s="24">
+        <v>1</v>
+      </c>
+      <c r="J15" s="24">
         <v>20</v>
       </c>
-      <c r="K15" s="22" t="s">
-        <v>205</v>
-      </c>
-      <c r="L15" s="3">
-        <v>1</v>
-      </c>
-      <c r="M15" s="3" t="s">
+      <c r="K15" s="24" t="s">
+        <v>207</v>
+      </c>
+      <c r="L15" s="4">
+        <v>1</v>
+      </c>
+      <c r="M15" s="4" t="s">
         <v>61</v>
       </c>
       <c r="N15" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="O15" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="P15" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="16" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B16" t="s">
         <v>54</v>
       </c>
-      <c r="C16" s="7">
+      <c r="C16" s="8">
         <v>365</v>
       </c>
-      <c r="D16" s="7">
+      <c r="D16" s="8">
         <v>62</v>
       </c>
-      <c r="E16" s="7">
+      <c r="E16" s="8">
         <v>5.9867000000000002E-3</v>
       </c>
-      <c r="F16" s="3" t="s">
+      <c r="F16" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="G16" s="22">
-        <v>1</v>
-      </c>
-      <c r="H16" s="22">
+      <c r="G16" s="24">
+        <v>1</v>
+      </c>
+      <c r="H16" s="24">
         <v>0.01</v>
       </c>
-      <c r="I16" s="22">
-        <v>1</v>
-      </c>
-      <c r="J16" s="22">
+      <c r="I16" s="24">
+        <v>1</v>
+      </c>
+      <c r="J16" s="24">
         <v>20</v>
       </c>
-      <c r="K16" s="22" t="s">
-        <v>205</v>
-      </c>
-      <c r="L16" s="3">
-        <v>1</v>
-      </c>
-      <c r="M16" s="3" t="s">
+      <c r="K16" s="24" t="s">
+        <v>207</v>
+      </c>
+      <c r="L16" s="4">
+        <v>1</v>
+      </c>
+      <c r="M16" s="4" t="s">
         <v>61</v>
       </c>
       <c r="N16" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="O16" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="P16" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="17" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B17" t="s">
         <v>55</v>
       </c>
-      <c r="C17" s="7">
+      <c r="C17" s="8">
         <v>365</v>
       </c>
-      <c r="D17" s="7">
+      <c r="D17" s="8">
         <v>62</v>
       </c>
-      <c r="E17" s="7">
+      <c r="E17" s="8">
         <v>5.9867000000000002E-3</v>
       </c>
-      <c r="F17" s="3" t="s">
+      <c r="F17" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="G17" s="22">
-        <v>1</v>
-      </c>
-      <c r="H17" s="22">
+      <c r="G17" s="24">
+        <v>1</v>
+      </c>
+      <c r="H17" s="24">
         <v>0.01</v>
       </c>
-      <c r="I17" s="22">
-        <v>1</v>
-      </c>
-      <c r="J17" s="22">
+      <c r="I17" s="24">
+        <v>1</v>
+      </c>
+      <c r="J17" s="24">
         <v>20</v>
       </c>
-      <c r="K17" s="22" t="s">
-        <v>205</v>
-      </c>
-      <c r="L17" s="3">
-        <v>1</v>
-      </c>
-      <c r="M17" s="3" t="s">
+      <c r="K17" s="24" t="s">
+        <v>207</v>
+      </c>
+      <c r="L17" s="4">
+        <v>1</v>
+      </c>
+      <c r="M17" s="4" t="s">
         <v>61</v>
       </c>
       <c r="N17" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="O17" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="P17" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="18" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B18" t="s">
         <v>56</v>
       </c>
-      <c r="C18" s="7">
+      <c r="C18" s="8">
         <v>365</v>
       </c>
-      <c r="D18" s="7">
+      <c r="D18" s="8">
         <v>62</v>
       </c>
-      <c r="E18" s="7">
+      <c r="E18" s="8">
         <v>5.9867000000000002E-3</v>
       </c>
-      <c r="F18" s="3" t="s">
+      <c r="F18" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="G18" s="22">
-        <v>1</v>
-      </c>
-      <c r="H18" s="22">
+      <c r="G18" s="24">
+        <v>1</v>
+      </c>
+      <c r="H18" s="24">
         <v>0.01</v>
       </c>
-      <c r="I18" s="22">
-        <v>1</v>
-      </c>
-      <c r="J18" s="22">
+      <c r="I18" s="24">
+        <v>1</v>
+      </c>
+      <c r="J18" s="24">
         <v>20</v>
       </c>
-      <c r="K18" s="22" t="s">
-        <v>205</v>
-      </c>
-      <c r="L18" s="3">
-        <v>1</v>
-      </c>
-      <c r="M18" s="3" t="s">
+      <c r="K18" s="24" t="s">
+        <v>207</v>
+      </c>
+      <c r="L18" s="4">
+        <v>1</v>
+      </c>
+      <c r="M18" s="4" t="s">
         <v>61</v>
       </c>
       <c r="N18" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="O18" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="P18" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="19" spans="1:16" x14ac:dyDescent="0.25">
@@ -3042,7 +3068,7 @@
     <col min="1" max="1" width="9" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="16" bestFit="1" customWidth="1"/>
     <col min="3" max="5" width="12" customWidth="1"/>
-    <col min="6" max="6" width="8.42578125" style="3" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="8.42578125" style="4" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="14.85546875" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="19.85546875" bestFit="1" customWidth="1"/>
     <col min="9" max="10" width="13.85546875" customWidth="1"/>
@@ -3056,134 +3082,134 @@
     <col min="21" max="21" width="9.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" s="11" customFormat="1" ht="75" x14ac:dyDescent="0.25">
-      <c r="A1" s="10" t="s">
+    <row r="1" spans="1:21" s="12" customFormat="1" ht="75" x14ac:dyDescent="0.25">
+      <c r="A1" s="11" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="10" t="s">
+      <c r="B1" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="C1" s="12" t="s">
+      <c r="C1" s="13" t="s">
         <v>68</v>
       </c>
-      <c r="D1" s="12" t="s">
+      <c r="D1" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="E1" s="12" t="s">
+      <c r="E1" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="F1" s="10" t="s">
+      <c r="F1" s="11" t="s">
         <v>86</v>
       </c>
-      <c r="G1" s="10" t="s">
+      <c r="G1" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="H1" s="10" t="s">
-        <v>189</v>
-      </c>
-      <c r="I1" s="10" t="s">
-        <v>168</v>
-      </c>
-      <c r="J1" s="55" t="s">
+      <c r="H1" s="11" t="s">
+        <v>190</v>
+      </c>
+      <c r="I1" s="11" t="s">
         <v>169</v>
       </c>
-      <c r="K1" s="56" t="s">
+      <c r="J1" s="57" t="s">
         <v>170</v>
       </c>
-      <c r="L1" s="56" t="s">
+      <c r="K1" s="58" t="s">
         <v>171</v>
       </c>
-      <c r="M1" s="25" t="s">
+      <c r="L1" s="58" t="s">
         <v>172</v>
       </c>
-      <c r="N1" s="10" t="s">
+      <c r="M1" s="27" t="s">
         <v>173</v>
       </c>
-      <c r="O1" s="57" t="s">
+      <c r="N1" s="11" t="s">
         <v>174</v>
       </c>
-      <c r="P1" s="57" t="s">
+      <c r="O1" s="59" t="s">
         <v>175</v>
       </c>
-      <c r="Q1" s="40" t="s">
+      <c r="P1" s="59" t="s">
         <v>176</v>
       </c>
-      <c r="R1" s="58" t="s">
+      <c r="Q1" s="42" t="s">
         <v>177</v>
       </c>
-      <c r="S1" s="58" t="s">
+      <c r="R1" s="60" t="s">
         <v>178</v>
       </c>
-      <c r="T1" s="36" t="s">
+      <c r="S1" s="60" t="s">
         <v>179</v>
       </c>
-      <c r="U1" s="10" t="s">
-        <v>93</v>
+      <c r="T1" s="38" t="s">
+        <v>180</v>
+      </c>
+      <c r="U1" s="11" t="s">
+        <v>94</v>
       </c>
     </row>
     <row r="2" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B2" t="s">
-        <v>96</v>
-      </c>
-      <c r="C2" s="6">
+        <v>97</v>
+      </c>
+      <c r="C2" s="7">
         <v>365</v>
       </c>
-      <c r="D2" s="6">
+      <c r="D2" s="7">
         <v>60</v>
       </c>
-      <c r="E2" s="6">
+      <c r="E2" s="7">
         <v>3.7499999999999999E-2</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="F2" s="4" t="s">
         <v>29</v>
       </c>
       <c r="G2" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="H2" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="I2" t="b">
         <v>0</v>
       </c>
-      <c r="J2" s="28">
-        <v>0</v>
-      </c>
-      <c r="K2" s="28">
-        <v>0</v>
-      </c>
-      <c r="L2" s="28">
-        <v>0</v>
-      </c>
-      <c r="M2" s="28">
+      <c r="J2" s="30">
+        <v>0</v>
+      </c>
+      <c r="K2" s="30">
+        <v>0</v>
+      </c>
+      <c r="L2" s="30">
+        <v>0</v>
+      </c>
+      <c r="M2" s="30">
         <v>0.1</v>
       </c>
       <c r="N2" t="b">
         <v>0</v>
       </c>
-      <c r="O2" s="6">
-        <v>0</v>
-      </c>
-      <c r="P2" s="6">
-        <v>0</v>
-      </c>
-      <c r="Q2" s="6">
+      <c r="O2" s="7">
+        <v>0</v>
+      </c>
+      <c r="P2" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q2" s="7">
         <v>0.1</v>
       </c>
-      <c r="R2" s="8">
-        <v>0</v>
-      </c>
-      <c r="S2" s="8">
-        <v>0</v>
-      </c>
-      <c r="T2" s="8">
+      <c r="R2" s="9">
+        <v>0</v>
+      </c>
+      <c r="S2" s="9">
+        <v>0</v>
+      </c>
+      <c r="T2" s="9">
         <v>0.1</v>
       </c>
       <c r="U2" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
     <row r="7" spans="1:21" x14ac:dyDescent="0.25">
@@ -3224,7 +3250,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
-  <dimension ref="A1:AF3"/>
+  <dimension ref="A1:AG3"/>
   <sheetFormatPr defaultColWidth="66.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.42578125" bestFit="1" customWidth="1"/>
@@ -3254,111 +3280,115 @@
     <col min="28" max="28" width="18.42578125" bestFit="1" customWidth="1"/>
     <col min="29" max="29" width="12.28515625" bestFit="1" customWidth="1"/>
     <col min="30" max="30" width="12.140625" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="63.7109375" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="12.140625" customWidth="1"/>
+    <col min="32" max="32" width="63.7109375" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:32" s="11" customFormat="1" ht="59.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="10" t="s">
+    <row r="1" spans="1:33" s="12" customFormat="1" ht="59.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="11" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="10" t="s">
+      <c r="B1" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="C1" s="10" t="s">
+      <c r="C1" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="D1" s="10" t="s">
+      <c r="D1" s="11" t="s">
         <v>86</v>
       </c>
-      <c r="E1" s="10" t="s">
-        <v>163</v>
-      </c>
-      <c r="F1" s="23" t="s">
+      <c r="E1" s="11" t="s">
         <v>164</v>
       </c>
-      <c r="G1" s="13" t="s">
+      <c r="F1" s="25" t="s">
+        <v>165</v>
+      </c>
+      <c r="G1" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="H1" s="12" t="s">
+      <c r="H1" s="13" t="s">
         <v>68</v>
       </c>
-      <c r="I1" s="12" t="s">
+      <c r="I1" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="J1" s="24" t="s">
-        <v>97</v>
-      </c>
-      <c r="K1" s="24" t="s">
+      <c r="J1" s="26" t="s">
         <v>98</v>
       </c>
-      <c r="L1" s="24" t="s">
-        <v>206</v>
-      </c>
-      <c r="M1" s="25" t="s">
+      <c r="K1" s="26" t="s">
+        <v>99</v>
+      </c>
+      <c r="L1" s="26" t="s">
+        <v>208</v>
+      </c>
+      <c r="M1" s="27" t="s">
         <v>76</v>
       </c>
-      <c r="N1" s="25" t="s">
+      <c r="N1" s="27" t="s">
         <v>77</v>
       </c>
-      <c r="O1" s="25" t="s">
+      <c r="O1" s="27" t="s">
         <v>17</v>
       </c>
-      <c r="P1" s="26" t="s">
+      <c r="P1" s="28" t="s">
         <v>78</v>
       </c>
-      <c r="Q1" s="26" t="s">
+      <c r="Q1" s="28" t="s">
         <v>79</v>
       </c>
-      <c r="R1" s="26" t="s">
+      <c r="R1" s="28" t="s">
         <v>18</v>
       </c>
-      <c r="S1" s="25" t="s">
-        <v>207</v>
-      </c>
-      <c r="T1" s="25" t="s">
-        <v>208</v>
-      </c>
-      <c r="U1" s="25" t="s">
+      <c r="S1" s="27" t="s">
         <v>209</v>
       </c>
-      <c r="V1" s="26" t="s">
+      <c r="T1" s="27" t="s">
         <v>210</v>
       </c>
-      <c r="W1" s="26" t="s">
+      <c r="U1" s="27" t="s">
         <v>211</v>
       </c>
-      <c r="X1" s="26" t="s">
+      <c r="V1" s="28" t="s">
         <v>212</v>
       </c>
-      <c r="Y1" s="27" t="s">
-        <v>219</v>
-      </c>
-      <c r="Z1" s="27" t="s">
-        <v>220</v>
-      </c>
-      <c r="AA1" s="27" t="s">
+      <c r="W1" s="28" t="s">
+        <v>213</v>
+      </c>
+      <c r="X1" s="28" t="s">
+        <v>214</v>
+      </c>
+      <c r="Y1" s="29" t="s">
         <v>221</v>
       </c>
-      <c r="AB1" s="27" t="s">
+      <c r="Z1" s="29" t="s">
         <v>222</v>
       </c>
-      <c r="AC1" s="27" t="s">
+      <c r="AA1" s="29" t="s">
         <v>223</v>
       </c>
-      <c r="AD1" s="27" t="s">
+      <c r="AB1" s="29" t="s">
         <v>224</v>
       </c>
-      <c r="AE1" s="10" t="s">
-        <v>189</v>
-      </c>
-      <c r="AF1" s="10" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="2" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="AC1" s="29" t="s">
+        <v>225</v>
+      </c>
+      <c r="AD1" s="29" t="s">
+        <v>226</v>
+      </c>
+      <c r="AE1" s="61" t="s">
+        <v>227</v>
+      </c>
+      <c r="AF1" s="11" t="s">
+        <v>190</v>
+      </c>
+      <c r="AG1" s="11" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="2" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B2" t="s">
         <v>69</v>
@@ -3366,7 +3396,7 @@
       <c r="C2" t="s">
         <v>27</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="D2" s="4" t="s">
         <v>29</v>
       </c>
       <c r="E2" t="s">
@@ -3375,13 +3405,13 @@
       <c r="F2" t="s">
         <v>63</v>
       </c>
-      <c r="G2" s="7">
+      <c r="G2" s="8">
         <v>50</v>
       </c>
-      <c r="H2" s="7">
+      <c r="H2" s="8">
         <v>365</v>
       </c>
-      <c r="I2" s="7">
+      <c r="I2" s="8">
         <v>4.3276E-3</v>
       </c>
       <c r="J2">
@@ -3393,70 +3423,73 @@
       <c r="L2" t="b">
         <v>1</v>
       </c>
-      <c r="M2" s="28">
-        <v>0</v>
-      </c>
-      <c r="N2" s="28">
+      <c r="M2" s="30">
+        <v>0</v>
+      </c>
+      <c r="N2" s="30">
         <v>365</v>
       </c>
-      <c r="O2" s="28">
+      <c r="O2" s="30">
         <v>0.34166999999999997</v>
       </c>
-      <c r="P2" s="29">
-        <v>0</v>
-      </c>
-      <c r="Q2" s="29">
+      <c r="P2" s="31">
+        <v>0</v>
+      </c>
+      <c r="Q2" s="31">
         <v>365</v>
       </c>
-      <c r="R2" s="29">
+      <c r="R2" s="31">
         <v>0.14960999999999999</v>
       </c>
-      <c r="S2" s="28">
+      <c r="S2" s="30">
         <v>3</v>
       </c>
-      <c r="T2" s="28">
+      <c r="T2" s="30">
         <v>7</v>
       </c>
-      <c r="U2" s="28">
+      <c r="U2" s="30">
         <v>0.34166999999999997</v>
       </c>
-      <c r="V2" s="29">
+      <c r="V2" s="31">
         <v>7</v>
       </c>
-      <c r="W2" s="29">
+      <c r="W2" s="31">
         <v>7</v>
       </c>
-      <c r="X2" s="29">
+      <c r="X2" s="31">
         <v>0.14960999999999999</v>
       </c>
-      <c r="Y2" s="30">
-        <v>1</v>
-      </c>
-      <c r="Z2" s="30">
+      <c r="Y2" s="32">
+        <v>1</v>
+      </c>
+      <c r="Z2" s="32">
         <v>2</v>
       </c>
-      <c r="AA2" s="30">
+      <c r="AA2" s="32">
         <v>0.5</v>
       </c>
-      <c r="AB2" s="54">
+      <c r="AB2" s="56">
         <v>3000</v>
       </c>
-      <c r="AC2" s="54">
+      <c r="AC2" s="56">
         <v>10000</v>
       </c>
-      <c r="AD2" s="54">
+      <c r="AD2" s="56">
         <v>5000</v>
       </c>
-      <c r="AE2" t="s">
-        <v>193</v>
+      <c r="AE2" s="62" t="b">
+        <v>1</v>
       </c>
       <c r="AF2" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="3" spans="1:32" x14ac:dyDescent="0.25">
+        <v>194</v>
+      </c>
+      <c r="AG2" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="3" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B3" t="s">
         <v>69</v>
@@ -3464,7 +3497,7 @@
       <c r="C3" t="s">
         <v>28</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="D3" s="4" t="s">
         <v>29</v>
       </c>
       <c r="E3" t="s">
@@ -3473,13 +3506,13 @@
       <c r="F3" t="s">
         <v>62</v>
       </c>
-      <c r="G3" s="7">
+      <c r="G3" s="8">
         <v>50</v>
       </c>
-      <c r="H3" s="7">
+      <c r="H3" s="8">
         <v>365</v>
       </c>
-      <c r="I3" s="7">
+      <c r="I3" s="8">
         <v>4.3276E-3</v>
       </c>
       <c r="J3">
@@ -3491,65 +3524,68 @@
       <c r="L3" t="b">
         <v>1</v>
       </c>
-      <c r="M3" s="28">
-        <v>0</v>
-      </c>
-      <c r="N3" s="28">
+      <c r="M3" s="30">
+        <v>0</v>
+      </c>
+      <c r="N3" s="30">
         <v>365</v>
       </c>
-      <c r="O3" s="28">
+      <c r="O3" s="30">
         <v>0.34166999999999997</v>
       </c>
-      <c r="P3" s="29">
-        <v>0</v>
-      </c>
-      <c r="Q3" s="29">
+      <c r="P3" s="31">
+        <v>0</v>
+      </c>
+      <c r="Q3" s="31">
         <v>365</v>
       </c>
-      <c r="R3" s="29">
+      <c r="R3" s="31">
         <v>0.14960999999999999</v>
       </c>
-      <c r="S3" s="28">
+      <c r="S3" s="30">
         <v>3</v>
       </c>
-      <c r="T3" s="28">
+      <c r="T3" s="30">
         <v>7</v>
       </c>
-      <c r="U3" s="28">
+      <c r="U3" s="30">
         <v>0.34166999999999997</v>
       </c>
-      <c r="V3" s="29">
+      <c r="V3" s="31">
         <v>7</v>
       </c>
-      <c r="W3" s="29">
+      <c r="W3" s="31">
         <v>7</v>
       </c>
-      <c r="X3" s="29">
+      <c r="X3" s="31">
         <v>0.14960999999999999</v>
       </c>
-      <c r="Y3" s="30">
-        <v>1</v>
-      </c>
-      <c r="Z3" s="30">
+      <c r="Y3" s="32">
+        <v>1</v>
+      </c>
+      <c r="Z3" s="32">
         <v>2</v>
       </c>
-      <c r="AA3" s="30">
+      <c r="AA3" s="32">
         <v>0.5</v>
       </c>
-      <c r="AB3" s="54">
+      <c r="AB3" s="56">
         <v>3000</v>
       </c>
-      <c r="AC3" s="54">
+      <c r="AC3" s="56">
         <v>10000</v>
       </c>
-      <c r="AD3" s="54">
+      <c r="AD3" s="56">
         <v>5000</v>
       </c>
-      <c r="AE3" t="s">
-        <v>194</v>
+      <c r="AE3" s="62" t="b">
+        <v>1</v>
       </c>
       <c r="AF3" t="s">
-        <v>200</v>
+        <v>195</v>
+      </c>
+      <c r="AG3" t="s">
+        <v>201</v>
       </c>
     </row>
   </sheetData>
@@ -3565,296 +3601,298 @@
   <cols>
     <col min="1" max="1" width="8.7109375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="7.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.7109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="11.42578125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.7109375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.28515625" customWidth="1"/>
-    <col min="8" max="8" width="11.42578125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.42578125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="9.42578125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="11.42578125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="11.42578125" customWidth="1"/>
-    <col min="13" max="13" width="14.28515625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="16.42578125" style="3" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="8.28515625" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="11.140625" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="9.85546875" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="10.42578125" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="11.28515625" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="11.42578125" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="10.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="21.7109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="11.42578125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.7109375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="12.28515625" customWidth="1"/>
+    <col min="10" max="10" width="11.42578125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="11.42578125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="11.42578125" customWidth="1"/>
+    <col min="15" max="15" width="14.28515625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="16.42578125" style="4" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="8.28515625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="11.140625" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="11.28515625" bestFit="1" customWidth="1"/>
     <col min="22" max="22" width="11.42578125" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="13.140625" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.28515625" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.42578125" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="10.7109375" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="10.42578125" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="10.85546875" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="12.42578125" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="15" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="11" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="15.7109375" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="11.42578125" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="10" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="10.28515625" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="9.42578125" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="15" customWidth="1"/>
-    <col min="40" max="41" width="13.85546875" bestFit="1" customWidth="1"/>
-    <col min="42" max="42" width="10" bestFit="1" customWidth="1"/>
-    <col min="43" max="43" width="11.7109375" bestFit="1" customWidth="1"/>
-    <col min="44" max="45" width="10.7109375" bestFit="1" customWidth="1"/>
-    <col min="46" max="46" width="9.7109375" bestFit="1" customWidth="1"/>
-    <col min="47" max="47" width="17.42578125" bestFit="1" customWidth="1"/>
-    <col min="48" max="49" width="15" bestFit="1" customWidth="1"/>
-    <col min="50" max="50" width="14" bestFit="1" customWidth="1"/>
-    <col min="51" max="51" width="16" bestFit="1" customWidth="1"/>
-    <col min="52" max="53" width="47.140625" bestFit="1" customWidth="1"/>
-    <col min="54" max="54" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="10.28515625" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="11.42578125" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.28515625" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.42578125" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="15" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="11" bestFit="1" customWidth="1"/>
+    <col min="35" max="36" width="15.7109375" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="11.42578125" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="10" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="10.28515625" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="15" customWidth="1"/>
+    <col min="42" max="43" width="13.85546875" bestFit="1" customWidth="1"/>
+    <col min="44" max="44" width="10" bestFit="1" customWidth="1"/>
+    <col min="45" max="45" width="11.7109375" bestFit="1" customWidth="1"/>
+    <col min="46" max="47" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="48" max="48" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="49" max="49" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="50" max="51" width="15" bestFit="1" customWidth="1"/>
+    <col min="52" max="52" width="14" bestFit="1" customWidth="1"/>
+    <col min="53" max="53" width="16" bestFit="1" customWidth="1"/>
+    <col min="54" max="55" width="47.140625" bestFit="1" customWidth="1"/>
+    <col min="56" max="56" width="9.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:56" s="61" customFormat="1" ht="120" x14ac:dyDescent="0.25">
-      <c r="A1" s="10" t="s">
+    <row r="1" spans="1:56" s="18" customFormat="1" ht="63" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="16" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="10" t="s">
+      <c r="B1" s="16" t="s">
         <v>8</v>
       </c>
-      <c r="C1" s="59" t="s">
-        <v>225</v>
-      </c>
-      <c r="D1" s="60" t="s">
-        <v>226</v>
-      </c>
-      <c r="E1" s="12" t="s">
+      <c r="C1" s="63" t="s">
+        <v>228</v>
+      </c>
+      <c r="D1" s="64" t="s">
+        <v>229</v>
+      </c>
+      <c r="E1" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1" s="17" t="s">
         <v>68</v>
       </c>
-      <c r="F1" s="12" t="s">
-        <v>9</v>
-      </c>
-      <c r="G1" s="12" t="s">
+      <c r="G1" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="H1" s="10" t="s">
+      <c r="H1" s="23" t="s">
+        <v>86</v>
+      </c>
+      <c r="I1" s="33" t="s">
+        <v>166</v>
+      </c>
+      <c r="J1" s="34" t="s">
+        <v>189</v>
+      </c>
+      <c r="K1" s="34" t="s">
+        <v>167</v>
+      </c>
+      <c r="L1" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="M1" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="N1" s="40" t="s">
+        <v>217</v>
+      </c>
+      <c r="O1" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="P1" s="35" t="s">
+        <v>132</v>
+      </c>
+      <c r="Q1" s="34" t="s">
+        <v>11</v>
+      </c>
+      <c r="R1" s="34" t="s">
+        <v>12</v>
+      </c>
+      <c r="S1" s="36" t="s">
+        <v>133</v>
+      </c>
+      <c r="T1" s="36" t="s">
+        <v>134</v>
+      </c>
+      <c r="U1" s="36" t="s">
+        <v>187</v>
+      </c>
+      <c r="V1" s="36" t="s">
         <v>188</v>
       </c>
-      <c r="I1" s="21" t="s">
-        <v>227</v>
-      </c>
-      <c r="J1" s="32" t="s">
-        <v>166</v>
-      </c>
-      <c r="K1" s="38" t="s">
-        <v>214</v>
-      </c>
-      <c r="L1" s="38" t="s">
-        <v>215</v>
-      </c>
-      <c r="M1" s="10" t="s">
-        <v>184</v>
-      </c>
-      <c r="N1" s="10" t="s">
-        <v>185</v>
-      </c>
-      <c r="O1" s="33" t="s">
-        <v>131</v>
-      </c>
-      <c r="P1" s="31" t="s">
-        <v>165</v>
-      </c>
-      <c r="Q1" s="35" t="s">
-        <v>134</v>
-      </c>
-      <c r="R1" s="32" t="s">
-        <v>11</v>
-      </c>
-      <c r="S1" s="32" t="s">
-        <v>12</v>
-      </c>
-      <c r="T1" s="34" t="s">
-        <v>132</v>
-      </c>
-      <c r="U1" s="34" t="s">
-        <v>133</v>
-      </c>
-      <c r="V1" s="34" t="s">
-        <v>186</v>
-      </c>
-      <c r="W1" s="34" t="s">
-        <v>187</v>
-      </c>
-      <c r="X1" s="27" t="s">
+      <c r="W1" s="37" t="s">
         <v>135</v>
       </c>
-      <c r="Y1" s="27" t="s">
+      <c r="X1" s="29" t="s">
         <v>136</v>
       </c>
-      <c r="Z1" s="10" t="s">
+      <c r="Y1" s="29" t="s">
         <v>137</v>
       </c>
-      <c r="AA1" s="10" t="s">
+      <c r="Z1" s="11" t="s">
         <v>138</v>
       </c>
-      <c r="AB1" s="36" t="s">
+      <c r="AA1" s="11" t="s">
         <v>139</v>
       </c>
-      <c r="AC1" s="37" t="s">
+      <c r="AB1" s="38" t="s">
         <v>140</v>
       </c>
-      <c r="AD1" s="37" t="s">
+      <c r="AC1" s="39" t="s">
         <v>141</v>
       </c>
-      <c r="AE1" s="37" t="s">
+      <c r="AD1" s="39" t="s">
+        <v>142</v>
+      </c>
+      <c r="AE1" s="39" t="s">
         <v>13</v>
       </c>
-      <c r="AF1" s="10" t="s">
-        <v>167</v>
-      </c>
-      <c r="AG1" s="39" t="s">
-        <v>142</v>
-      </c>
-      <c r="AH1" s="25" t="s">
+      <c r="AF1" s="11" t="s">
+        <v>168</v>
+      </c>
+      <c r="AG1" s="41" t="s">
+        <v>143</v>
+      </c>
+      <c r="AH1" s="27" t="s">
         <v>80</v>
       </c>
-      <c r="AI1" s="25" t="s">
+      <c r="AI1" s="27" t="s">
         <v>81</v>
       </c>
-      <c r="AJ1" s="39" t="s">
+      <c r="AJ1" s="41" t="s">
         <v>14</v>
       </c>
-      <c r="AK1" s="40" t="s">
-        <v>143</v>
-      </c>
-      <c r="AL1" s="41" t="s">
+      <c r="AK1" s="42" t="s">
+        <v>144</v>
+      </c>
+      <c r="AL1" s="43" t="s">
         <v>82</v>
       </c>
-      <c r="AM1" s="40" t="s">
+      <c r="AM1" s="42" t="s">
         <v>83</v>
       </c>
-      <c r="AN1" s="41" t="s">
+      <c r="AN1" s="43" t="s">
         <v>30</v>
       </c>
-      <c r="AO1" s="42" t="s">
-        <v>144</v>
-      </c>
-      <c r="AP1" s="43" t="s">
+      <c r="AO1" s="44" t="s">
+        <v>145</v>
+      </c>
+      <c r="AP1" s="45" t="s">
         <v>84</v>
       </c>
-      <c r="AQ1" s="43" t="s">
+      <c r="AQ1" s="45" t="s">
         <v>85</v>
       </c>
-      <c r="AR1" s="43" t="s">
+      <c r="AR1" s="45" t="s">
         <v>31</v>
       </c>
-      <c r="AS1" s="44" t="s">
-        <v>145</v>
-      </c>
-      <c r="AT1" s="44" t="s">
+      <c r="AS1" s="46" t="s">
         <v>146</v>
       </c>
-      <c r="AU1" s="44" t="s">
+      <c r="AT1" s="46" t="s">
         <v>147</v>
       </c>
-      <c r="AV1" s="44" t="s">
+      <c r="AU1" s="46" t="s">
         <v>148</v>
       </c>
-      <c r="AW1" s="45" t="s">
+      <c r="AV1" s="46" t="s">
         <v>149</v>
       </c>
-      <c r="AX1" s="46" t="s">
+      <c r="AW1" s="47" t="s">
         <v>150</v>
       </c>
-      <c r="AY1" s="46" t="s">
+      <c r="AX1" s="48" t="s">
         <v>151</v>
       </c>
-      <c r="AZ1" s="46" t="s">
+      <c r="AY1" s="48" t="s">
         <v>152</v>
       </c>
-      <c r="BA1" s="10" t="s">
+      <c r="AZ1" s="48" t="s">
+        <v>153</v>
+      </c>
+      <c r="BA1" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="BB1" s="38" t="s">
-        <v>189</v>
-      </c>
-      <c r="BC1" s="47" t="s">
+      <c r="BB1" s="40" t="s">
+        <v>190</v>
+      </c>
+      <c r="BC1" s="49" t="s">
         <v>89</v>
       </c>
-      <c r="BD1" s="10" t="s">
-        <v>93</v>
+      <c r="BD1" s="11" t="s">
+        <v>94</v>
       </c>
     </row>
     <row r="2" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B2" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C2" t="b">
         <v>0</v>
       </c>
-      <c r="D2" t="s">
-        <v>228</v>
-      </c>
-      <c r="E2" s="7">
+      <c r="D2">
+        <v>1.4E-2</v>
+      </c>
+      <c r="E2" s="8">
         <v>45</v>
       </c>
-      <c r="F2" s="7">
+      <c r="F2" s="8">
         <v>365</v>
       </c>
-      <c r="G2" s="7">
+      <c r="G2" s="8">
         <v>0.02</v>
       </c>
-      <c r="H2" s="49">
+      <c r="H2" s="50" t="s">
+        <v>29</v>
+      </c>
+      <c r="I2" s="24" t="s">
+        <v>215</v>
+      </c>
+      <c r="J2" s="51">
         <v>32</v>
       </c>
-      <c r="I2" s="48" t="s">
-        <v>29</v>
-      </c>
-      <c r="J2" s="14" t="s">
+      <c r="K2" s="15" t="s">
         <v>88</v>
       </c>
-      <c r="K2">
+      <c r="L2">
+        <v>0.35</v>
+      </c>
+      <c r="M2">
         <v>0.7</v>
       </c>
-      <c r="M2">
-        <v>0.35</v>
-      </c>
-      <c r="N2" t="s">
-        <v>216</v>
-      </c>
-      <c r="O2" s="49" t="s">
-        <v>155</v>
-      </c>
-      <c r="P2" s="22" t="s">
-        <v>213</v>
-      </c>
-      <c r="Q2" s="51" t="s">
-        <v>153</v>
-      </c>
-      <c r="R2" s="14">
+      <c r="O2" t="s">
+        <v>218</v>
+      </c>
+      <c r="P2" s="51" t="s">
+        <v>156</v>
+      </c>
+      <c r="Q2" s="15">
         <v>0.9</v>
       </c>
-      <c r="S2" s="14">
+      <c r="R2" s="15">
         <v>3.5000000000000003E-2</v>
       </c>
-      <c r="T2" s="50">
+      <c r="S2" s="52">
         <v>0.9</v>
       </c>
-      <c r="U2" s="50">
+      <c r="T2" s="52">
         <v>0.71</v>
       </c>
-      <c r="V2" s="50">
+      <c r="U2" s="52">
         <f>24*21</f>
         <v>504</v>
       </c>
-      <c r="W2" s="50">
+      <c r="V2" s="52">
         <f>24*7*6</f>
         <v>1008</v>
       </c>
-      <c r="X2" s="30">
+      <c r="W2" s="53" t="s">
+        <v>154</v>
+      </c>
+      <c r="X2" s="32">
         <v>3</v>
       </c>
-      <c r="Y2" s="30">
+      <c r="Y2" s="32">
         <v>0</v>
       </c>
       <c r="Z2">
@@ -3863,167 +3901,167 @@
       <c r="AA2">
         <v>100</v>
       </c>
-      <c r="AB2" s="8">
-        <v>1</v>
-      </c>
-      <c r="AC2" s="8">
-        <v>0</v>
-      </c>
-      <c r="AD2" s="8">
+      <c r="AB2" s="9">
+        <v>1</v>
+      </c>
+      <c r="AC2" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD2" s="9">
         <v>182.5</v>
       </c>
-      <c r="AE2" s="8">
+      <c r="AE2" s="9">
         <v>0.21634999999999999</v>
       </c>
       <c r="AF2" t="b">
         <v>1</v>
       </c>
-      <c r="AG2" s="28">
-        <v>1</v>
-      </c>
-      <c r="AH2" s="28">
-        <v>0</v>
-      </c>
-      <c r="AI2" s="28">
+      <c r="AG2" s="30">
+        <v>1</v>
+      </c>
+      <c r="AH2" s="30">
+        <v>0</v>
+      </c>
+      <c r="AI2" s="30">
         <v>182.5</v>
       </c>
-      <c r="AJ2" s="28">
+      <c r="AJ2" s="30">
         <v>8.3141000000000007E-2</v>
       </c>
-      <c r="AK2" s="6">
-        <v>1</v>
-      </c>
-      <c r="AL2" s="6">
-        <v>0</v>
-      </c>
-      <c r="AM2" s="6">
+      <c r="AK2" s="7">
+        <v>1</v>
+      </c>
+      <c r="AL2" s="7">
+        <v>0</v>
+      </c>
+      <c r="AM2" s="7">
         <v>182.5</v>
       </c>
-      <c r="AN2" s="6">
+      <c r="AN2" s="7">
         <v>0.47815999999999997</v>
       </c>
-      <c r="AO2" s="52">
-        <v>1</v>
-      </c>
-      <c r="AP2" s="52">
-        <v>0</v>
-      </c>
-      <c r="AQ2" s="52">
+      <c r="AO2" s="54">
+        <v>1</v>
+      </c>
+      <c r="AP2" s="54">
+        <v>0</v>
+      </c>
+      <c r="AQ2" s="54">
         <v>121.66670000000001</v>
       </c>
-      <c r="AR2" s="52">
+      <c r="AR2" s="54">
         <v>2.6738E-3</v>
       </c>
-      <c r="AS2" s="53">
-        <v>1</v>
-      </c>
-      <c r="AT2" s="53">
-        <v>0</v>
-      </c>
-      <c r="AU2" s="53">
+      <c r="AS2" s="55">
+        <v>1</v>
+      </c>
+      <c r="AT2" s="55">
+        <v>0</v>
+      </c>
+      <c r="AU2" s="55">
         <v>182.5</v>
       </c>
-      <c r="AV2" s="53">
+      <c r="AV2" s="55">
         <v>0.11268</v>
       </c>
-      <c r="AW2" s="9">
-        <v>1</v>
-      </c>
-      <c r="AX2" s="9">
-        <v>0</v>
-      </c>
-      <c r="AY2" s="9">
+      <c r="AW2" s="10">
+        <v>1</v>
+      </c>
+      <c r="AX2" s="10">
+        <v>0</v>
+      </c>
+      <c r="AY2" s="10">
         <v>121.66670000000001</v>
       </c>
-      <c r="AZ2" s="9">
+      <c r="AZ2" s="10">
         <v>2.7855000000000002E-3</v>
       </c>
       <c r="BA2" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="BB2" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="BC2" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="BD2" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
     </row>
     <row r="3" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B3" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C3" t="b">
         <v>0</v>
       </c>
-      <c r="D3" t="s">
-        <v>228</v>
-      </c>
-      <c r="E3" s="7">
+      <c r="D3">
+        <v>1.4E-2</v>
+      </c>
+      <c r="E3" s="8">
         <v>45</v>
       </c>
-      <c r="F3" s="7">
+      <c r="F3" s="8">
         <v>365</v>
       </c>
-      <c r="G3" s="7">
+      <c r="G3" s="8">
         <v>0.02</v>
       </c>
-      <c r="H3" s="49">
+      <c r="H3" s="50" t="s">
+        <v>29</v>
+      </c>
+      <c r="I3" s="24" t="s">
+        <v>215</v>
+      </c>
+      <c r="J3" s="51">
         <v>32</v>
       </c>
-      <c r="I3" s="48" t="s">
-        <v>29</v>
-      </c>
-      <c r="J3" s="14" t="s">
+      <c r="K3" s="15" t="s">
         <v>88</v>
       </c>
-      <c r="K3">
+      <c r="L3">
+        <v>0.35</v>
+      </c>
+      <c r="M3">
         <v>0.7</v>
       </c>
-      <c r="M3">
-        <v>0.35</v>
-      </c>
-      <c r="N3" t="s">
-        <v>216</v>
-      </c>
-      <c r="O3" s="49" t="s">
-        <v>155</v>
-      </c>
-      <c r="P3" s="22" t="s">
-        <v>213</v>
-      </c>
-      <c r="Q3" s="51" t="s">
-        <v>153</v>
-      </c>
-      <c r="R3" s="14">
+      <c r="O3" t="s">
+        <v>218</v>
+      </c>
+      <c r="P3" s="51" t="s">
+        <v>156</v>
+      </c>
+      <c r="Q3" s="15">
         <v>0.9</v>
       </c>
-      <c r="S3" s="14">
+      <c r="R3" s="15">
         <v>3.5000000000000003E-2</v>
       </c>
-      <c r="T3" s="50">
+      <c r="S3" s="52">
         <v>0.9</v>
       </c>
-      <c r="U3" s="50">
+      <c r="T3" s="52">
         <v>0.71</v>
       </c>
-      <c r="V3" s="50">
+      <c r="U3" s="52">
         <f>24*21</f>
         <v>504</v>
       </c>
-      <c r="W3" s="50">
+      <c r="V3" s="52">
         <f>24*7*6</f>
         <v>1008</v>
       </c>
-      <c r="X3" s="30">
+      <c r="W3" s="53" t="s">
+        <v>154</v>
+      </c>
+      <c r="X3" s="32">
         <v>3</v>
       </c>
-      <c r="Y3" s="30">
+      <c r="Y3" s="32">
         <v>0</v>
       </c>
       <c r="Z3">
@@ -4032,167 +4070,167 @@
       <c r="AA3">
         <v>100</v>
       </c>
-      <c r="AB3" s="8">
-        <v>1</v>
-      </c>
-      <c r="AC3" s="8">
-        <v>0</v>
-      </c>
-      <c r="AD3" s="8">
+      <c r="AB3" s="9">
+        <v>1</v>
+      </c>
+      <c r="AC3" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD3" s="9">
         <v>182.5</v>
       </c>
-      <c r="AE3" s="8">
+      <c r="AE3" s="9">
         <v>0.21634999999999999</v>
       </c>
       <c r="AF3" t="b">
         <v>1</v>
       </c>
-      <c r="AG3" s="28">
-        <v>1</v>
-      </c>
-      <c r="AH3" s="28">
-        <v>0</v>
-      </c>
-      <c r="AI3" s="28">
+      <c r="AG3" s="30">
+        <v>1</v>
+      </c>
+      <c r="AH3" s="30">
+        <v>0</v>
+      </c>
+      <c r="AI3" s="30">
         <v>182.5</v>
       </c>
-      <c r="AJ3" s="28">
+      <c r="AJ3" s="30">
         <v>8.3141000000000007E-2</v>
       </c>
-      <c r="AK3" s="6">
-        <v>1</v>
-      </c>
-      <c r="AL3" s="6">
-        <v>0</v>
-      </c>
-      <c r="AM3" s="6">
+      <c r="AK3" s="7">
+        <v>1</v>
+      </c>
+      <c r="AL3" s="7">
+        <v>0</v>
+      </c>
+      <c r="AM3" s="7">
         <v>182.5</v>
       </c>
-      <c r="AN3" s="6">
+      <c r="AN3" s="7">
         <v>0.47815999999999997</v>
       </c>
-      <c r="AO3" s="52">
-        <v>1</v>
-      </c>
-      <c r="AP3" s="52">
-        <v>0</v>
-      </c>
-      <c r="AQ3" s="52">
+      <c r="AO3" s="54">
+        <v>1</v>
+      </c>
+      <c r="AP3" s="54">
+        <v>0</v>
+      </c>
+      <c r="AQ3" s="54">
         <v>121.66670000000001</v>
       </c>
-      <c r="AR3" s="52">
+      <c r="AR3" s="54">
         <v>2.6738E-3</v>
       </c>
-      <c r="AS3" s="53">
-        <v>1</v>
-      </c>
-      <c r="AT3" s="53">
-        <v>0</v>
-      </c>
-      <c r="AU3" s="53">
+      <c r="AS3" s="55">
+        <v>1</v>
+      </c>
+      <c r="AT3" s="55">
+        <v>0</v>
+      </c>
+      <c r="AU3" s="55">
         <v>182.5</v>
       </c>
-      <c r="AV3" s="53">
+      <c r="AV3" s="55">
         <v>0.11268</v>
       </c>
-      <c r="AW3" s="9">
-        <v>1</v>
-      </c>
-      <c r="AX3" s="9">
-        <v>0</v>
-      </c>
-      <c r="AY3" s="9">
+      <c r="AW3" s="10">
+        <v>1</v>
+      </c>
+      <c r="AX3" s="10">
+        <v>0</v>
+      </c>
+      <c r="AY3" s="10">
         <v>121.66670000000001</v>
       </c>
-      <c r="AZ3" s="9">
+      <c r="AZ3" s="10">
         <v>2.7855000000000002E-3</v>
       </c>
       <c r="BA3" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="BB3" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="BC3" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="BD3" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
     </row>
     <row r="4" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B4" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C4" t="b">
         <v>0</v>
       </c>
-      <c r="D4" t="s">
-        <v>228</v>
-      </c>
-      <c r="E4" s="7">
+      <c r="D4">
+        <v>1.4E-2</v>
+      </c>
+      <c r="E4" s="8">
         <v>45</v>
       </c>
-      <c r="F4" s="7">
+      <c r="F4" s="8">
         <v>365</v>
       </c>
-      <c r="G4" s="7">
+      <c r="G4" s="8">
         <v>0.02</v>
       </c>
-      <c r="H4" s="49">
+      <c r="H4" s="50" t="s">
+        <v>29</v>
+      </c>
+      <c r="I4" s="24" t="s">
+        <v>215</v>
+      </c>
+      <c r="J4" s="51">
         <v>32</v>
       </c>
-      <c r="I4" s="48" t="s">
-        <v>29</v>
-      </c>
-      <c r="J4" s="14" t="s">
+      <c r="K4" s="15" t="s">
         <v>88</v>
       </c>
-      <c r="K4">
+      <c r="L4">
+        <v>0.35</v>
+      </c>
+      <c r="M4">
         <v>0.7</v>
       </c>
-      <c r="M4">
-        <v>0.35</v>
-      </c>
-      <c r="N4" t="s">
-        <v>216</v>
-      </c>
-      <c r="O4" s="49" t="s">
-        <v>155</v>
-      </c>
-      <c r="P4" s="22" t="s">
-        <v>213</v>
-      </c>
-      <c r="Q4" s="51" t="s">
-        <v>153</v>
-      </c>
-      <c r="R4" s="14">
+      <c r="O4" t="s">
+        <v>218</v>
+      </c>
+      <c r="P4" s="51" t="s">
+        <v>156</v>
+      </c>
+      <c r="Q4" s="15">
         <v>0.9</v>
       </c>
-      <c r="S4" s="14">
+      <c r="R4" s="15">
         <v>3.5000000000000003E-2</v>
       </c>
-      <c r="T4" s="50">
+      <c r="S4" s="52">
         <v>0.9</v>
       </c>
-      <c r="U4" s="50">
+      <c r="T4" s="52">
         <v>0.71</v>
       </c>
-      <c r="V4" s="50">
-        <f t="shared" ref="V4:V9" si="0">24*21</f>
+      <c r="U4" s="52">
+        <f t="shared" ref="U4:U9" si="0">24*21</f>
         <v>504</v>
       </c>
-      <c r="W4" s="50">
-        <f t="shared" ref="W4:W9" si="1">24*7*6</f>
+      <c r="V4" s="52">
+        <f t="shared" ref="V4:V9" si="1">24*7*6</f>
         <v>1008</v>
       </c>
-      <c r="X4" s="30">
+      <c r="W4" s="53" t="s">
+        <v>154</v>
+      </c>
+      <c r="X4" s="32">
         <v>3</v>
       </c>
-      <c r="Y4" s="30">
+      <c r="Y4" s="32">
         <v>0</v>
       </c>
       <c r="Z4">
@@ -4201,167 +4239,167 @@
       <c r="AA4">
         <v>100</v>
       </c>
-      <c r="AB4" s="8">
-        <v>1</v>
-      </c>
-      <c r="AC4" s="8">
-        <v>0</v>
-      </c>
-      <c r="AD4" s="8">
+      <c r="AB4" s="9">
+        <v>1</v>
+      </c>
+      <c r="AC4" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD4" s="9">
         <v>182.5</v>
       </c>
-      <c r="AE4" s="8">
+      <c r="AE4" s="9">
         <v>0.21634999999999999</v>
       </c>
       <c r="AF4" t="b">
         <v>1</v>
       </c>
-      <c r="AG4" s="28">
-        <v>1</v>
-      </c>
-      <c r="AH4" s="28">
-        <v>0</v>
-      </c>
-      <c r="AI4" s="28">
+      <c r="AG4" s="30">
+        <v>1</v>
+      </c>
+      <c r="AH4" s="30">
+        <v>0</v>
+      </c>
+      <c r="AI4" s="30">
         <v>182.5</v>
       </c>
-      <c r="AJ4" s="28">
+      <c r="AJ4" s="30">
         <v>8.3141000000000007E-2</v>
       </c>
-      <c r="AK4" s="6">
-        <v>1</v>
-      </c>
-      <c r="AL4" s="6">
-        <v>0</v>
-      </c>
-      <c r="AM4" s="6">
+      <c r="AK4" s="7">
+        <v>1</v>
+      </c>
+      <c r="AL4" s="7">
+        <v>0</v>
+      </c>
+      <c r="AM4" s="7">
         <v>182.5</v>
       </c>
-      <c r="AN4" s="6">
+      <c r="AN4" s="7">
         <v>0.47815999999999997</v>
       </c>
-      <c r="AO4" s="52">
-        <v>1</v>
-      </c>
-      <c r="AP4" s="52">
-        <v>0</v>
-      </c>
-      <c r="AQ4" s="52">
+      <c r="AO4" s="54">
+        <v>1</v>
+      </c>
+      <c r="AP4" s="54">
+        <v>0</v>
+      </c>
+      <c r="AQ4" s="54">
         <v>121.66670000000001</v>
       </c>
-      <c r="AR4" s="52">
+      <c r="AR4" s="54">
         <v>2.6738E-3</v>
       </c>
-      <c r="AS4" s="53">
-        <v>1</v>
-      </c>
-      <c r="AT4" s="53">
-        <v>0</v>
-      </c>
-      <c r="AU4" s="53">
+      <c r="AS4" s="55">
+        <v>1</v>
+      </c>
+      <c r="AT4" s="55">
+        <v>0</v>
+      </c>
+      <c r="AU4" s="55">
         <v>182.5</v>
       </c>
-      <c r="AV4" s="53">
+      <c r="AV4" s="55">
         <v>0.11268</v>
       </c>
-      <c r="AW4" s="9">
-        <v>1</v>
-      </c>
-      <c r="AX4" s="9">
-        <v>0</v>
-      </c>
-      <c r="AY4" s="9">
+      <c r="AW4" s="10">
+        <v>1</v>
+      </c>
+      <c r="AX4" s="10">
+        <v>0</v>
+      </c>
+      <c r="AY4" s="10">
         <v>121.66670000000001</v>
       </c>
-      <c r="AZ4" s="9">
+      <c r="AZ4" s="10">
         <v>2.7855000000000002E-3</v>
       </c>
       <c r="BA4" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="BB4" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="BC4" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="BD4" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
     </row>
     <row r="5" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B5" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C5" t="b">
         <v>0</v>
       </c>
-      <c r="D5" t="s">
-        <v>228</v>
-      </c>
-      <c r="E5" s="7">
+      <c r="D5">
+        <v>1.4E-2</v>
+      </c>
+      <c r="E5" s="8">
         <v>45</v>
       </c>
-      <c r="F5" s="7">
+      <c r="F5" s="8">
         <v>365</v>
       </c>
-      <c r="G5" s="7">
+      <c r="G5" s="8">
         <v>0.02</v>
       </c>
-      <c r="H5" s="49">
+      <c r="H5" s="50" t="s">
+        <v>29</v>
+      </c>
+      <c r="I5" s="24" t="s">
+        <v>215</v>
+      </c>
+      <c r="J5" s="51">
         <v>32</v>
       </c>
-      <c r="I5" s="48" t="s">
-        <v>29</v>
-      </c>
-      <c r="J5" s="14" t="s">
+      <c r="K5" s="15" t="s">
         <v>88</v>
       </c>
-      <c r="K5">
+      <c r="L5">
+        <v>0.35</v>
+      </c>
+      <c r="M5">
         <v>0.7</v>
       </c>
-      <c r="M5">
-        <v>0.35</v>
-      </c>
-      <c r="N5" t="s">
-        <v>216</v>
-      </c>
-      <c r="O5" s="49" t="s">
-        <v>155</v>
-      </c>
-      <c r="P5" s="22" t="s">
-        <v>213</v>
-      </c>
-      <c r="Q5" s="51" t="s">
-        <v>153</v>
-      </c>
-      <c r="R5" s="14">
+      <c r="O5" t="s">
+        <v>218</v>
+      </c>
+      <c r="P5" s="51" t="s">
+        <v>156</v>
+      </c>
+      <c r="Q5" s="15">
         <v>0.9</v>
       </c>
-      <c r="S5" s="14">
+      <c r="R5" s="15">
         <v>3.5000000000000003E-2</v>
       </c>
-      <c r="T5" s="50">
+      <c r="S5" s="52">
         <v>0.9</v>
       </c>
-      <c r="U5" s="50">
+      <c r="T5" s="52">
         <v>0.71</v>
       </c>
-      <c r="V5" s="50">
+      <c r="U5" s="52">
         <f t="shared" si="0"/>
         <v>504</v>
       </c>
-      <c r="W5" s="50">
+      <c r="V5" s="52">
         <f t="shared" si="1"/>
         <v>1008</v>
       </c>
-      <c r="X5" s="30">
+      <c r="W5" s="53" t="s">
+        <v>154</v>
+      </c>
+      <c r="X5" s="32">
         <v>3</v>
       </c>
-      <c r="Y5" s="30">
+      <c r="Y5" s="32">
         <v>0</v>
       </c>
       <c r="Z5">
@@ -4370,167 +4408,167 @@
       <c r="AA5">
         <v>100</v>
       </c>
-      <c r="AB5" s="8">
-        <v>1</v>
-      </c>
-      <c r="AC5" s="8">
-        <v>0</v>
-      </c>
-      <c r="AD5" s="8">
+      <c r="AB5" s="9">
+        <v>1</v>
+      </c>
+      <c r="AC5" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD5" s="9">
         <v>182.5</v>
       </c>
-      <c r="AE5" s="8">
+      <c r="AE5" s="9">
         <v>0.21634999999999999</v>
       </c>
       <c r="AF5" t="b">
         <v>1</v>
       </c>
-      <c r="AG5" s="28">
-        <v>1</v>
-      </c>
-      <c r="AH5" s="28">
-        <v>0</v>
-      </c>
-      <c r="AI5" s="28">
+      <c r="AG5" s="30">
+        <v>1</v>
+      </c>
+      <c r="AH5" s="30">
+        <v>0</v>
+      </c>
+      <c r="AI5" s="30">
         <v>182.5</v>
       </c>
-      <c r="AJ5" s="28">
+      <c r="AJ5" s="30">
         <v>8.3141000000000007E-2</v>
       </c>
-      <c r="AK5" s="6">
-        <v>1</v>
-      </c>
-      <c r="AL5" s="6">
-        <v>0</v>
-      </c>
-      <c r="AM5" s="6">
+      <c r="AK5" s="7">
+        <v>1</v>
+      </c>
+      <c r="AL5" s="7">
+        <v>0</v>
+      </c>
+      <c r="AM5" s="7">
         <v>182.5</v>
       </c>
-      <c r="AN5" s="6">
+      <c r="AN5" s="7">
         <v>0.47815999999999997</v>
       </c>
-      <c r="AO5" s="52">
-        <v>1</v>
-      </c>
-      <c r="AP5" s="52">
-        <v>0</v>
-      </c>
-      <c r="AQ5" s="52">
+      <c r="AO5" s="54">
+        <v>1</v>
+      </c>
+      <c r="AP5" s="54">
+        <v>0</v>
+      </c>
+      <c r="AQ5" s="54">
         <v>121.66670000000001</v>
       </c>
-      <c r="AR5" s="52">
+      <c r="AR5" s="54">
         <v>2.6738E-3</v>
       </c>
-      <c r="AS5" s="53">
-        <v>1</v>
-      </c>
-      <c r="AT5" s="53">
-        <v>0</v>
-      </c>
-      <c r="AU5" s="53">
+      <c r="AS5" s="55">
+        <v>1</v>
+      </c>
+      <c r="AT5" s="55">
+        <v>0</v>
+      </c>
+      <c r="AU5" s="55">
         <v>182.5</v>
       </c>
-      <c r="AV5" s="53">
+      <c r="AV5" s="55">
         <v>0.11268</v>
       </c>
-      <c r="AW5" s="9">
-        <v>1</v>
-      </c>
-      <c r="AX5" s="9">
-        <v>0</v>
-      </c>
-      <c r="AY5" s="9">
+      <c r="AW5" s="10">
+        <v>1</v>
+      </c>
+      <c r="AX5" s="10">
+        <v>0</v>
+      </c>
+      <c r="AY5" s="10">
         <v>121.66670000000001</v>
       </c>
-      <c r="AZ5" s="9">
+      <c r="AZ5" s="10">
         <v>2.7855000000000002E-3</v>
       </c>
       <c r="BA5" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="BB5" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="BC5" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="BD5" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
     </row>
     <row r="6" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B6" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C6" t="b">
         <v>0</v>
       </c>
-      <c r="D6" t="s">
-        <v>228</v>
-      </c>
-      <c r="E6" s="7">
+      <c r="D6">
+        <v>1.4E-2</v>
+      </c>
+      <c r="E6" s="8">
         <v>45</v>
       </c>
-      <c r="F6" s="7">
+      <c r="F6" s="8">
         <v>365</v>
       </c>
-      <c r="G6" s="7">
+      <c r="G6" s="8">
         <v>0.02</v>
       </c>
-      <c r="H6" s="49">
+      <c r="H6" s="50" t="s">
+        <v>29</v>
+      </c>
+      <c r="I6" s="24" t="s">
+        <v>215</v>
+      </c>
+      <c r="J6" s="51">
         <v>32</v>
       </c>
-      <c r="I6" s="48" t="s">
-        <v>29</v>
-      </c>
-      <c r="J6" s="14" t="s">
+      <c r="K6" s="15" t="s">
         <v>88</v>
       </c>
-      <c r="K6">
+      <c r="L6">
+        <v>0.35</v>
+      </c>
+      <c r="M6">
         <v>0.7</v>
       </c>
-      <c r="M6">
-        <v>0.35</v>
-      </c>
-      <c r="N6" t="s">
-        <v>216</v>
-      </c>
-      <c r="O6" s="49" t="s">
-        <v>155</v>
-      </c>
-      <c r="P6" s="22" t="s">
-        <v>213</v>
-      </c>
-      <c r="Q6" s="51" t="s">
-        <v>153</v>
-      </c>
-      <c r="R6" s="14">
+      <c r="O6" t="s">
+        <v>218</v>
+      </c>
+      <c r="P6" s="51" t="s">
+        <v>156</v>
+      </c>
+      <c r="Q6" s="15">
         <v>0.9</v>
       </c>
-      <c r="S6" s="14">
+      <c r="R6" s="15">
         <v>3.5000000000000003E-2</v>
       </c>
-      <c r="T6" s="50">
+      <c r="S6" s="52">
         <v>0.9</v>
       </c>
-      <c r="U6" s="50">
+      <c r="T6" s="52">
         <v>0.71</v>
       </c>
-      <c r="V6" s="50">
+      <c r="U6" s="52">
         <f t="shared" si="0"/>
         <v>504</v>
       </c>
-      <c r="W6" s="50">
+      <c r="V6" s="52">
         <f t="shared" si="1"/>
         <v>1008</v>
       </c>
-      <c r="X6" s="30">
+      <c r="W6" s="53" t="s">
+        <v>154</v>
+      </c>
+      <c r="X6" s="32">
         <v>3</v>
       </c>
-      <c r="Y6" s="30">
+      <c r="Y6" s="32">
         <v>0</v>
       </c>
       <c r="Z6">
@@ -4539,167 +4577,167 @@
       <c r="AA6">
         <v>100</v>
       </c>
-      <c r="AB6" s="8">
-        <v>1</v>
-      </c>
-      <c r="AC6" s="8">
-        <v>0</v>
-      </c>
-      <c r="AD6" s="8">
+      <c r="AB6" s="9">
+        <v>1</v>
+      </c>
+      <c r="AC6" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD6" s="9">
         <v>182.5</v>
       </c>
-      <c r="AE6" s="8">
+      <c r="AE6" s="9">
         <v>0.21634999999999999</v>
       </c>
       <c r="AF6" t="b">
         <v>1</v>
       </c>
-      <c r="AG6" s="28">
-        <v>1</v>
-      </c>
-      <c r="AH6" s="28">
-        <v>0</v>
-      </c>
-      <c r="AI6" s="28">
+      <c r="AG6" s="30">
+        <v>1</v>
+      </c>
+      <c r="AH6" s="30">
+        <v>0</v>
+      </c>
+      <c r="AI6" s="30">
         <v>182.5</v>
       </c>
-      <c r="AJ6" s="28">
+      <c r="AJ6" s="30">
         <v>8.3141000000000007E-2</v>
       </c>
-      <c r="AK6" s="6">
-        <v>1</v>
-      </c>
-      <c r="AL6" s="6">
-        <v>0</v>
-      </c>
-      <c r="AM6" s="6">
+      <c r="AK6" s="7">
+        <v>1</v>
+      </c>
+      <c r="AL6" s="7">
+        <v>0</v>
+      </c>
+      <c r="AM6" s="7">
         <v>182.5</v>
       </c>
-      <c r="AN6" s="6">
+      <c r="AN6" s="7">
         <v>0.47815999999999997</v>
       </c>
-      <c r="AO6" s="52">
-        <v>1</v>
-      </c>
-      <c r="AP6" s="52">
-        <v>0</v>
-      </c>
-      <c r="AQ6" s="52">
+      <c r="AO6" s="54">
+        <v>1</v>
+      </c>
+      <c r="AP6" s="54">
+        <v>0</v>
+      </c>
+      <c r="AQ6" s="54">
         <v>121.66670000000001</v>
       </c>
-      <c r="AR6" s="52">
+      <c r="AR6" s="54">
         <v>2.6738E-3</v>
       </c>
-      <c r="AS6" s="53">
-        <v>1</v>
-      </c>
-      <c r="AT6" s="53">
-        <v>0</v>
-      </c>
-      <c r="AU6" s="53">
+      <c r="AS6" s="55">
+        <v>1</v>
+      </c>
+      <c r="AT6" s="55">
+        <v>0</v>
+      </c>
+      <c r="AU6" s="55">
         <v>182.5</v>
       </c>
-      <c r="AV6" s="53">
+      <c r="AV6" s="55">
         <v>0.11268</v>
       </c>
-      <c r="AW6" s="9">
-        <v>1</v>
-      </c>
-      <c r="AX6" s="9">
-        <v>0</v>
-      </c>
-      <c r="AY6" s="9">
+      <c r="AW6" s="10">
+        <v>1</v>
+      </c>
+      <c r="AX6" s="10">
+        <v>0</v>
+      </c>
+      <c r="AY6" s="10">
         <v>121.66670000000001</v>
       </c>
-      <c r="AZ6" s="9">
+      <c r="AZ6" s="10">
         <v>2.7855000000000002E-3</v>
       </c>
       <c r="BA6" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="BB6" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="BC6" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="BD6" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
     </row>
     <row r="7" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B7" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C7" t="b">
         <v>0</v>
       </c>
-      <c r="D7" t="s">
-        <v>228</v>
-      </c>
-      <c r="E7" s="7">
+      <c r="D7">
+        <v>1.4E-2</v>
+      </c>
+      <c r="E7" s="8">
         <v>45</v>
       </c>
-      <c r="F7" s="7">
+      <c r="F7" s="8">
         <v>365</v>
       </c>
-      <c r="G7" s="7">
+      <c r="G7" s="8">
         <v>0.02</v>
       </c>
-      <c r="H7" s="49">
+      <c r="H7" s="50" t="s">
+        <v>29</v>
+      </c>
+      <c r="I7" s="24" t="s">
+        <v>215</v>
+      </c>
+      <c r="J7" s="51">
         <v>32</v>
       </c>
-      <c r="I7" s="48" t="s">
-        <v>29</v>
-      </c>
-      <c r="J7" s="14" t="s">
+      <c r="K7" s="15" t="s">
         <v>88</v>
       </c>
-      <c r="K7">
+      <c r="L7">
+        <v>0.35</v>
+      </c>
+      <c r="M7">
         <v>0.7</v>
       </c>
-      <c r="M7">
-        <v>0.35</v>
-      </c>
-      <c r="N7" t="s">
-        <v>216</v>
-      </c>
-      <c r="O7" s="49" t="s">
-        <v>155</v>
-      </c>
-      <c r="P7" s="22" t="s">
-        <v>213</v>
-      </c>
-      <c r="Q7" s="51" t="s">
-        <v>153</v>
-      </c>
-      <c r="R7" s="14">
+      <c r="O7" t="s">
+        <v>218</v>
+      </c>
+      <c r="P7" s="51" t="s">
+        <v>156</v>
+      </c>
+      <c r="Q7" s="15">
         <v>0.9</v>
       </c>
-      <c r="S7" s="14">
+      <c r="R7" s="15">
         <v>3.5000000000000003E-2</v>
       </c>
-      <c r="T7" s="50">
+      <c r="S7" s="52">
         <v>0.9</v>
       </c>
-      <c r="U7" s="50">
+      <c r="T7" s="52">
         <v>0.71</v>
       </c>
-      <c r="V7" s="50">
+      <c r="U7" s="52">
         <f t="shared" si="0"/>
         <v>504</v>
       </c>
-      <c r="W7" s="50">
+      <c r="V7" s="52">
         <f t="shared" si="1"/>
         <v>1008</v>
       </c>
-      <c r="X7" s="30">
+      <c r="W7" s="53" t="s">
+        <v>154</v>
+      </c>
+      <c r="X7" s="32">
         <v>3</v>
       </c>
-      <c r="Y7" s="30">
+      <c r="Y7" s="32">
         <v>0</v>
       </c>
       <c r="Z7">
@@ -4708,167 +4746,167 @@
       <c r="AA7">
         <v>100</v>
       </c>
-      <c r="AB7" s="8">
-        <v>1</v>
-      </c>
-      <c r="AC7" s="8">
-        <v>0</v>
-      </c>
-      <c r="AD7" s="8">
+      <c r="AB7" s="9">
+        <v>1</v>
+      </c>
+      <c r="AC7" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD7" s="9">
         <v>182.5</v>
       </c>
-      <c r="AE7" s="8">
+      <c r="AE7" s="9">
         <v>0.21634999999999999</v>
       </c>
       <c r="AF7" t="b">
         <v>1</v>
       </c>
-      <c r="AG7" s="28">
-        <v>1</v>
-      </c>
-      <c r="AH7" s="28">
-        <v>0</v>
-      </c>
-      <c r="AI7" s="28">
+      <c r="AG7" s="30">
+        <v>1</v>
+      </c>
+      <c r="AH7" s="30">
+        <v>0</v>
+      </c>
+      <c r="AI7" s="30">
         <v>182.5</v>
       </c>
-      <c r="AJ7" s="28">
+      <c r="AJ7" s="30">
         <v>8.3141000000000007E-2</v>
       </c>
-      <c r="AK7" s="6">
-        <v>1</v>
-      </c>
-      <c r="AL7" s="6">
-        <v>0</v>
-      </c>
-      <c r="AM7" s="6">
+      <c r="AK7" s="7">
+        <v>1</v>
+      </c>
+      <c r="AL7" s="7">
+        <v>0</v>
+      </c>
+      <c r="AM7" s="7">
         <v>182.5</v>
       </c>
-      <c r="AN7" s="6">
+      <c r="AN7" s="7">
         <v>0.47815999999999997</v>
       </c>
-      <c r="AO7" s="52">
-        <v>1</v>
-      </c>
-      <c r="AP7" s="52">
-        <v>0</v>
-      </c>
-      <c r="AQ7" s="52">
+      <c r="AO7" s="54">
+        <v>1</v>
+      </c>
+      <c r="AP7" s="54">
+        <v>0</v>
+      </c>
+      <c r="AQ7" s="54">
         <v>121.66670000000001</v>
       </c>
-      <c r="AR7" s="52">
+      <c r="AR7" s="54">
         <v>2.6738E-3</v>
       </c>
-      <c r="AS7" s="53">
-        <v>1</v>
-      </c>
-      <c r="AT7" s="53">
-        <v>0</v>
-      </c>
-      <c r="AU7" s="53">
+      <c r="AS7" s="55">
+        <v>1</v>
+      </c>
+      <c r="AT7" s="55">
+        <v>0</v>
+      </c>
+      <c r="AU7" s="55">
         <v>182.5</v>
       </c>
-      <c r="AV7" s="53">
+      <c r="AV7" s="55">
         <v>0.11268</v>
       </c>
-      <c r="AW7" s="9">
-        <v>1</v>
-      </c>
-      <c r="AX7" s="9">
-        <v>0</v>
-      </c>
-      <c r="AY7" s="9">
+      <c r="AW7" s="10">
+        <v>1</v>
+      </c>
+      <c r="AX7" s="10">
+        <v>0</v>
+      </c>
+      <c r="AY7" s="10">
         <v>121.66670000000001</v>
       </c>
-      <c r="AZ7" s="9">
+      <c r="AZ7" s="10">
         <v>2.7855000000000002E-3</v>
       </c>
       <c r="BA7" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="BB7" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="BC7" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="BD7" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
     </row>
     <row r="8" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B8" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C8" t="b">
         <v>0</v>
       </c>
-      <c r="D8" t="s">
-        <v>228</v>
-      </c>
-      <c r="E8" s="7">
+      <c r="D8">
+        <v>1.4E-2</v>
+      </c>
+      <c r="E8" s="8">
         <v>45</v>
       </c>
-      <c r="F8" s="7">
+      <c r="F8" s="8">
         <v>365</v>
       </c>
-      <c r="G8" s="7">
+      <c r="G8" s="8">
         <v>0.02</v>
       </c>
-      <c r="H8" s="49">
+      <c r="H8" s="50" t="s">
+        <v>29</v>
+      </c>
+      <c r="I8" s="24" t="s">
+        <v>215</v>
+      </c>
+      <c r="J8" s="51">
         <v>32</v>
       </c>
-      <c r="I8" s="48" t="s">
-        <v>29</v>
-      </c>
-      <c r="J8" s="14" t="s">
+      <c r="K8" s="15" t="s">
         <v>88</v>
       </c>
-      <c r="K8">
+      <c r="L8">
+        <v>0.35</v>
+      </c>
+      <c r="M8">
         <v>0.7</v>
       </c>
-      <c r="M8">
-        <v>0.35</v>
-      </c>
-      <c r="N8" t="s">
-        <v>216</v>
-      </c>
-      <c r="O8" s="49" t="s">
-        <v>155</v>
-      </c>
-      <c r="P8" s="22" t="s">
-        <v>213</v>
-      </c>
-      <c r="Q8" s="51" t="s">
-        <v>153</v>
-      </c>
-      <c r="R8" s="14">
+      <c r="O8" t="s">
+        <v>218</v>
+      </c>
+      <c r="P8" s="51" t="s">
+        <v>156</v>
+      </c>
+      <c r="Q8" s="15">
         <v>0.9</v>
       </c>
-      <c r="S8" s="14">
+      <c r="R8" s="15">
         <v>3.5000000000000003E-2</v>
       </c>
-      <c r="T8" s="50">
+      <c r="S8" s="52">
         <v>0.9</v>
       </c>
-      <c r="U8" s="50">
+      <c r="T8" s="52">
         <v>0.71</v>
       </c>
-      <c r="V8" s="50">
+      <c r="U8" s="52">
         <f t="shared" si="0"/>
         <v>504</v>
       </c>
-      <c r="W8" s="50">
+      <c r="V8" s="52">
         <f t="shared" si="1"/>
         <v>1008</v>
       </c>
-      <c r="X8" s="30">
+      <c r="W8" s="53" t="s">
+        <v>154</v>
+      </c>
+      <c r="X8" s="32">
         <v>3</v>
       </c>
-      <c r="Y8" s="30">
+      <c r="Y8" s="32">
         <v>0</v>
       </c>
       <c r="Z8">
@@ -4877,167 +4915,167 @@
       <c r="AA8">
         <v>100</v>
       </c>
-      <c r="AB8" s="8">
-        <v>1</v>
-      </c>
-      <c r="AC8" s="8">
-        <v>0</v>
-      </c>
-      <c r="AD8" s="8">
+      <c r="AB8" s="9">
+        <v>1</v>
+      </c>
+      <c r="AC8" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD8" s="9">
         <v>182.5</v>
       </c>
-      <c r="AE8" s="8">
+      <c r="AE8" s="9">
         <v>0.21634999999999999</v>
       </c>
       <c r="AF8" t="b">
         <v>1</v>
       </c>
-      <c r="AG8" s="28">
-        <v>1</v>
-      </c>
-      <c r="AH8" s="28">
-        <v>0</v>
-      </c>
-      <c r="AI8" s="28">
+      <c r="AG8" s="30">
+        <v>1</v>
+      </c>
+      <c r="AH8" s="30">
+        <v>0</v>
+      </c>
+      <c r="AI8" s="30">
         <v>182.5</v>
       </c>
-      <c r="AJ8" s="28">
+      <c r="AJ8" s="30">
         <v>8.3141000000000007E-2</v>
       </c>
-      <c r="AK8" s="6">
-        <v>1</v>
-      </c>
-      <c r="AL8" s="6">
-        <v>0</v>
-      </c>
-      <c r="AM8" s="6">
+      <c r="AK8" s="7">
+        <v>1</v>
+      </c>
+      <c r="AL8" s="7">
+        <v>0</v>
+      </c>
+      <c r="AM8" s="7">
         <v>182.5</v>
       </c>
-      <c r="AN8" s="6">
+      <c r="AN8" s="7">
         <v>0.47815999999999997</v>
       </c>
-      <c r="AO8" s="52">
-        <v>1</v>
-      </c>
-      <c r="AP8" s="52">
-        <v>0</v>
-      </c>
-      <c r="AQ8" s="52">
+      <c r="AO8" s="54">
+        <v>1</v>
+      </c>
+      <c r="AP8" s="54">
+        <v>0</v>
+      </c>
+      <c r="AQ8" s="54">
         <v>121.66670000000001</v>
       </c>
-      <c r="AR8" s="52">
+      <c r="AR8" s="54">
         <v>2.6738E-3</v>
       </c>
-      <c r="AS8" s="53">
-        <v>1</v>
-      </c>
-      <c r="AT8" s="53">
-        <v>0</v>
-      </c>
-      <c r="AU8" s="53">
+      <c r="AS8" s="55">
+        <v>1</v>
+      </c>
+      <c r="AT8" s="55">
+        <v>0</v>
+      </c>
+      <c r="AU8" s="55">
         <v>182.5</v>
       </c>
-      <c r="AV8" s="53">
+      <c r="AV8" s="55">
         <v>0.11268</v>
       </c>
-      <c r="AW8" s="9">
-        <v>1</v>
-      </c>
-      <c r="AX8" s="9">
-        <v>0</v>
-      </c>
-      <c r="AY8" s="9">
+      <c r="AW8" s="10">
+        <v>1</v>
+      </c>
+      <c r="AX8" s="10">
+        <v>0</v>
+      </c>
+      <c r="AY8" s="10">
         <v>121.66670000000001</v>
       </c>
-      <c r="AZ8" s="9">
+      <c r="AZ8" s="10">
         <v>2.7855000000000002E-3</v>
       </c>
       <c r="BA8" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="BB8" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="BC8" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="BD8" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
     </row>
     <row r="9" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B9" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C9" t="b">
         <v>0</v>
       </c>
-      <c r="D9" t="s">
-        <v>228</v>
-      </c>
-      <c r="E9" s="7">
+      <c r="D9">
+        <v>1.4E-2</v>
+      </c>
+      <c r="E9" s="8">
         <v>45</v>
       </c>
-      <c r="F9" s="7">
+      <c r="F9" s="8">
         <v>365</v>
       </c>
-      <c r="G9" s="7">
+      <c r="G9" s="8">
         <v>0.02</v>
       </c>
-      <c r="H9" s="49">
+      <c r="H9" s="50" t="s">
+        <v>29</v>
+      </c>
+      <c r="I9" s="24" t="s">
+        <v>215</v>
+      </c>
+      <c r="J9" s="51">
         <v>65</v>
       </c>
-      <c r="I9" s="48" t="s">
-        <v>29</v>
-      </c>
-      <c r="J9" s="14" t="s">
+      <c r="K9" s="15" t="s">
         <v>88</v>
       </c>
-      <c r="K9">
+      <c r="L9">
+        <v>0.35</v>
+      </c>
+      <c r="M9">
         <v>0.7</v>
       </c>
-      <c r="M9">
-        <v>0.35</v>
-      </c>
-      <c r="N9" t="s">
-        <v>216</v>
-      </c>
-      <c r="O9" s="49" t="s">
-        <v>155</v>
-      </c>
-      <c r="P9" s="22" t="s">
-        <v>213</v>
-      </c>
-      <c r="Q9" s="51" t="s">
-        <v>153</v>
-      </c>
-      <c r="R9" s="14">
+      <c r="O9" t="s">
+        <v>218</v>
+      </c>
+      <c r="P9" s="51" t="s">
+        <v>156</v>
+      </c>
+      <c r="Q9" s="15">
         <v>0.9</v>
       </c>
-      <c r="S9" s="14">
+      <c r="R9" s="15">
         <v>3.5000000000000003E-2</v>
       </c>
-      <c r="T9" s="50">
+      <c r="S9" s="52">
         <v>0.9</v>
       </c>
-      <c r="U9" s="50">
+      <c r="T9" s="52">
         <v>0.71</v>
       </c>
-      <c r="V9" s="50">
+      <c r="U9" s="52">
         <f t="shared" si="0"/>
         <v>504</v>
       </c>
-      <c r="W9" s="50">
+      <c r="V9" s="52">
         <f t="shared" si="1"/>
         <v>1008</v>
       </c>
-      <c r="X9" s="30">
+      <c r="W9" s="53" t="s">
+        <v>154</v>
+      </c>
+      <c r="X9" s="32">
         <v>3</v>
       </c>
-      <c r="Y9" s="30">
+      <c r="Y9" s="32">
         <v>0</v>
       </c>
       <c r="Z9">
@@ -5046,92 +5084,92 @@
       <c r="AA9">
         <v>100</v>
       </c>
-      <c r="AB9" s="8">
-        <v>1</v>
-      </c>
-      <c r="AC9" s="8">
-        <v>0</v>
-      </c>
-      <c r="AD9" s="8">
+      <c r="AB9" s="9">
+        <v>1</v>
+      </c>
+      <c r="AC9" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD9" s="9">
         <v>182.5</v>
       </c>
-      <c r="AE9" s="8">
+      <c r="AE9" s="9">
         <v>0.21634999999999999</v>
       </c>
       <c r="AF9" t="b">
         <v>1</v>
       </c>
-      <c r="AG9" s="28">
-        <v>1</v>
-      </c>
-      <c r="AH9" s="28">
-        <v>0</v>
-      </c>
-      <c r="AI9" s="28">
+      <c r="AG9" s="30">
+        <v>1</v>
+      </c>
+      <c r="AH9" s="30">
+        <v>0</v>
+      </c>
+      <c r="AI9" s="30">
         <v>182.5</v>
       </c>
-      <c r="AJ9" s="28">
+      <c r="AJ9" s="30">
         <v>8.3141000000000007E-2</v>
       </c>
-      <c r="AK9" s="6">
-        <v>1</v>
-      </c>
-      <c r="AL9" s="6">
-        <v>0</v>
-      </c>
-      <c r="AM9" s="6">
+      <c r="AK9" s="7">
+        <v>1</v>
+      </c>
+      <c r="AL9" s="7">
+        <v>0</v>
+      </c>
+      <c r="AM9" s="7">
         <v>182.5</v>
       </c>
-      <c r="AN9" s="6">
+      <c r="AN9" s="7">
         <v>0.47815999999999997</v>
       </c>
-      <c r="AO9" s="52">
-        <v>1</v>
-      </c>
-      <c r="AP9" s="52">
-        <v>0</v>
-      </c>
-      <c r="AQ9" s="52">
+      <c r="AO9" s="54">
+        <v>1</v>
+      </c>
+      <c r="AP9" s="54">
+        <v>0</v>
+      </c>
+      <c r="AQ9" s="54">
         <v>121.66670000000001</v>
       </c>
-      <c r="AR9" s="52">
+      <c r="AR9" s="54">
         <v>2.6738E-3</v>
       </c>
-      <c r="AS9" s="53">
-        <v>1</v>
-      </c>
-      <c r="AT9" s="53">
-        <v>0</v>
-      </c>
-      <c r="AU9" s="53">
+      <c r="AS9" s="55">
+        <v>1</v>
+      </c>
+      <c r="AT9" s="55">
+        <v>0</v>
+      </c>
+      <c r="AU9" s="55">
         <v>182.5</v>
       </c>
-      <c r="AV9" s="53">
+      <c r="AV9" s="55">
         <v>0.11268</v>
       </c>
-      <c r="AW9" s="9">
-        <v>1</v>
-      </c>
-      <c r="AX9" s="9">
-        <v>0</v>
-      </c>
-      <c r="AY9" s="9">
+      <c r="AW9" s="10">
+        <v>1</v>
+      </c>
+      <c r="AX9" s="10">
+        <v>0</v>
+      </c>
+      <c r="AY9" s="10">
         <v>121.66670000000001</v>
       </c>
-      <c r="AZ9" s="9">
+      <c r="AZ9" s="10">
         <v>2.7855000000000002E-3</v>
       </c>
       <c r="BA9" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="BB9" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="BC9" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="BD9" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
     </row>
   </sheetData>
@@ -5156,78 +5194,78 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:19" ht="75" x14ac:dyDescent="0.25">
-      <c r="A1" s="15" t="s">
+      <c r="A1" s="16" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="15" t="s">
+      <c r="B1" s="16" t="s">
         <v>8</v>
       </c>
-      <c r="C1" s="16" t="s">
+      <c r="C1" s="17" t="s">
         <v>9</v>
       </c>
-      <c r="D1" s="16" t="s">
+      <c r="D1" s="17" t="s">
         <v>68</v>
       </c>
-      <c r="E1" s="16" t="s">
+      <c r="E1" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="F1" s="15" t="s">
+      <c r="F1" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="G1" s="15" t="s">
+      <c r="G1" s="16" t="s">
         <v>72</v>
       </c>
-      <c r="H1" s="15" t="s">
+      <c r="H1" s="16" t="s">
         <v>73</v>
       </c>
-      <c r="I1" s="15" t="s">
+      <c r="I1" s="16" t="s">
         <v>90</v>
       </c>
-      <c r="J1" s="15" t="s">
+      <c r="J1" s="16" t="s">
         <v>16</v>
       </c>
-      <c r="K1" s="15" t="s">
+      <c r="K1" s="16" t="s">
         <v>74</v>
       </c>
-      <c r="L1" s="15" t="s">
+      <c r="L1" s="16" t="s">
         <v>75</v>
       </c>
-      <c r="M1" s="15" t="s">
+      <c r="M1" s="16" t="s">
         <v>91</v>
       </c>
-      <c r="N1" s="15" t="s">
+      <c r="N1" s="16" t="s">
         <v>70</v>
       </c>
-      <c r="O1" s="15" t="s">
+      <c r="O1" s="16" t="s">
         <v>71</v>
       </c>
-      <c r="P1" s="15" t="s">
+      <c r="P1" s="16" t="s">
         <v>92</v>
       </c>
-      <c r="Q1" s="15" t="s">
+      <c r="Q1" s="16" t="s">
         <v>7</v>
       </c>
-      <c r="R1" s="15" t="s">
-        <v>189</v>
-      </c>
-      <c r="S1" s="15" t="s">
-        <v>93</v>
+      <c r="R1" s="16" t="s">
+        <v>190</v>
+      </c>
+      <c r="S1" s="16" t="s">
+        <v>94</v>
       </c>
     </row>
     <row r="2" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B2" t="s">
-        <v>108</v>
-      </c>
-      <c r="C2" s="7">
+        <v>109</v>
+      </c>
+      <c r="C2" s="8">
         <v>45</v>
       </c>
-      <c r="D2" s="7">
+      <c r="D2" s="8">
         <v>365</v>
       </c>
-      <c r="E2" s="7">
+      <c r="E2" s="8">
         <v>3.7499999999999999E-2</v>
       </c>
       <c r="F2">
@@ -5267,26 +5305,26 @@
         <v>66</v>
       </c>
       <c r="R2" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="S2" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="3" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B3" t="s">
-        <v>109</v>
-      </c>
-      <c r="C3" s="7">
+        <v>110</v>
+      </c>
+      <c r="C3" s="8">
         <v>45</v>
       </c>
-      <c r="D3" s="7">
+      <c r="D3" s="8">
         <v>365</v>
       </c>
-      <c r="E3" s="7">
+      <c r="E3" s="8">
         <v>3.7499999999999999E-2</v>
       </c>
       <c r="F3">
@@ -5326,10 +5364,10 @@
         <v>66</v>
       </c>
       <c r="R3" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="S3" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
   </sheetData>
@@ -5368,10 +5406,10 @@
       <c r="E1" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="F1" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="G1" s="5" t="s">
         <v>48</v>
       </c>
     </row>
@@ -5380,13 +5418,13 @@
         <v>67</v>
       </c>
       <c r="B2" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C2" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D2" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E2" t="s">
         <v>33</v>
@@ -5394,20 +5432,20 @@
       <c r="F2" t="s">
         <v>62</v>
       </c>
-      <c r="G2" s="5"/>
+      <c r="G2" s="6"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>67</v>
       </c>
       <c r="B3" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C3" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D3" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E3" t="s">
         <v>34</v>
@@ -5421,13 +5459,13 @@
         <v>67</v>
       </c>
       <c r="B4" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C4" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D4" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E4" t="s">
         <v>35</v>
@@ -5441,13 +5479,13 @@
         <v>67</v>
       </c>
       <c r="B5" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C5" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D5" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E5" t="s">
         <v>36</v>
@@ -5461,13 +5499,13 @@
         <v>67</v>
       </c>
       <c r="B6" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C6" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D6" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E6" t="s">
         <v>37</v>
@@ -5481,13 +5519,13 @@
         <v>67</v>
       </c>
       <c r="B7" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C7" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="D7" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E7" t="s">
         <v>38</v>
@@ -5501,13 +5539,13 @@
         <v>67</v>
       </c>
       <c r="B8" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C8" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D8" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E8" t="s">
         <v>39</v>
@@ -5521,13 +5559,13 @@
         <v>67</v>
       </c>
       <c r="B9" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C9" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D9" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E9" t="s">
         <v>40</v>
@@ -5541,13 +5579,13 @@
         <v>67</v>
       </c>
       <c r="B10" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C10" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D10" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E10" t="s">
         <v>33</v>
@@ -5561,13 +5599,13 @@
         <v>67</v>
       </c>
       <c r="B11" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C11" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D11" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E11" t="s">
         <v>34</v>
@@ -5581,13 +5619,13 @@
         <v>67</v>
       </c>
       <c r="B12" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C12" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D12" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E12" t="s">
         <v>35</v>
@@ -5601,13 +5639,13 @@
         <v>67</v>
       </c>
       <c r="B13" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C13" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D13" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E13" t="s">
         <v>36</v>
@@ -5621,13 +5659,13 @@
         <v>67</v>
       </c>
       <c r="B14" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C14" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D14" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E14" t="s">
         <v>37</v>
@@ -5641,13 +5679,13 @@
         <v>67</v>
       </c>
       <c r="B15" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C15" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="D15" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E15" t="s">
         <v>38</v>
@@ -5661,13 +5699,13 @@
         <v>67</v>
       </c>
       <c r="B16" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C16" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D16" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E16" t="s">
         <v>39</v>
@@ -5681,13 +5719,13 @@
         <v>67</v>
       </c>
       <c r="B17" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C17" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D17" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E17" t="s">
         <v>40</v>
@@ -5701,13 +5739,13 @@
         <v>67</v>
       </c>
       <c r="B19" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C19" t="s">
         <v>33</v>
       </c>
       <c r="D19" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E19" t="s">
         <v>49</v>
@@ -5716,7 +5754,7 @@
         <v>62</v>
       </c>
       <c r="G19" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
@@ -5724,13 +5762,13 @@
         <v>67</v>
       </c>
       <c r="B20" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C20" t="s">
         <v>33</v>
       </c>
       <c r="D20" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E20" t="s">
         <v>49</v>
@@ -5747,22 +5785,22 @@
         <v>67</v>
       </c>
       <c r="B21" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C21" t="s">
         <v>33</v>
       </c>
       <c r="D21" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E21" t="s">
         <v>49</v>
       </c>
       <c r="F21" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="G21" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
@@ -5770,22 +5808,22 @@
         <v>67</v>
       </c>
       <c r="B22" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C22" t="s">
         <v>33</v>
       </c>
       <c r="D22" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E22" t="s">
         <v>49</v>
       </c>
       <c r="F22" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="G22" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
@@ -5793,13 +5831,13 @@
         <v>67</v>
       </c>
       <c r="B23" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C23" t="s">
         <v>34</v>
       </c>
       <c r="D23" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E23" t="s">
         <v>50</v>
@@ -5808,7 +5846,7 @@
         <v>62</v>
       </c>
       <c r="G23" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
@@ -5816,13 +5854,13 @@
         <v>67</v>
       </c>
       <c r="B24" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C24" t="s">
         <v>34</v>
       </c>
       <c r="D24" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E24" t="s">
         <v>50</v>
@@ -5839,22 +5877,22 @@
         <v>67</v>
       </c>
       <c r="B25" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C25" t="s">
         <v>34</v>
       </c>
       <c r="D25" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E25" t="s">
         <v>50</v>
       </c>
       <c r="F25" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="G25" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
@@ -5862,22 +5900,22 @@
         <v>67</v>
       </c>
       <c r="B26" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C26" t="s">
         <v>34</v>
       </c>
       <c r="D26" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E26" t="s">
         <v>50</v>
       </c>
       <c r="F26" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="G26" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
@@ -5885,13 +5923,13 @@
         <v>67</v>
       </c>
       <c r="B27" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C27" t="s">
         <v>35</v>
       </c>
       <c r="D27" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E27" t="s">
         <v>51</v>
@@ -5900,7 +5938,7 @@
         <v>62</v>
       </c>
       <c r="G27" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
@@ -5908,13 +5946,13 @@
         <v>67</v>
       </c>
       <c r="B28" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C28" t="s">
         <v>35</v>
       </c>
       <c r="D28" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E28" t="s">
         <v>51</v>
@@ -5931,22 +5969,22 @@
         <v>67</v>
       </c>
       <c r="B29" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C29" t="s">
         <v>35</v>
       </c>
       <c r="D29" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E29" t="s">
         <v>51</v>
       </c>
       <c r="F29" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="G29" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
@@ -5954,22 +5992,22 @@
         <v>67</v>
       </c>
       <c r="B30" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C30" t="s">
         <v>35</v>
       </c>
       <c r="D30" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E30" t="s">
         <v>51</v>
       </c>
       <c r="F30" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="G30" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
@@ -5977,13 +6015,13 @@
         <v>67</v>
       </c>
       <c r="B31" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C31" t="s">
         <v>36</v>
       </c>
       <c r="D31" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E31" t="s">
         <v>52</v>
@@ -5992,7 +6030,7 @@
         <v>62</v>
       </c>
       <c r="G31" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
@@ -6000,13 +6038,13 @@
         <v>67</v>
       </c>
       <c r="B32" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C32" t="s">
         <v>36</v>
       </c>
       <c r="D32" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E32" t="s">
         <v>52</v>
@@ -6023,22 +6061,22 @@
         <v>67</v>
       </c>
       <c r="B33" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C33" t="s">
         <v>36</v>
       </c>
       <c r="D33" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E33" t="s">
         <v>52</v>
       </c>
       <c r="F33" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="G33" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
@@ -6046,22 +6084,22 @@
         <v>67</v>
       </c>
       <c r="B34" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C34" t="s">
         <v>36</v>
       </c>
       <c r="D34" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E34" t="s">
         <v>52</v>
       </c>
       <c r="F34" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="G34" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
@@ -6069,13 +6107,13 @@
         <v>67</v>
       </c>
       <c r="B35" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C35" t="s">
         <v>37</v>
       </c>
       <c r="D35" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E35" t="s">
         <v>53</v>
@@ -6084,7 +6122,7 @@
         <v>62</v>
       </c>
       <c r="G35" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
@@ -6092,13 +6130,13 @@
         <v>67</v>
       </c>
       <c r="B36" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C36" t="s">
         <v>37</v>
       </c>
       <c r="D36" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E36" t="s">
         <v>53</v>
@@ -6115,22 +6153,22 @@
         <v>67</v>
       </c>
       <c r="B37" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C37" t="s">
         <v>37</v>
       </c>
       <c r="D37" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E37" t="s">
         <v>53</v>
       </c>
       <c r="F37" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="G37" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
@@ -6138,22 +6176,22 @@
         <v>67</v>
       </c>
       <c r="B38" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C38" t="s">
         <v>37</v>
       </c>
       <c r="D38" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E38" t="s">
         <v>53</v>
       </c>
       <c r="F38" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="G38" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.25">
@@ -6161,13 +6199,13 @@
         <v>67</v>
       </c>
       <c r="B39" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C39" t="s">
         <v>38</v>
       </c>
       <c r="D39" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E39" t="s">
         <v>54</v>
@@ -6176,7 +6214,7 @@
         <v>62</v>
       </c>
       <c r="G39" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.25">
@@ -6184,13 +6222,13 @@
         <v>67</v>
       </c>
       <c r="B40" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C40" t="s">
         <v>38</v>
       </c>
       <c r="D40" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E40" t="s">
         <v>54</v>
@@ -6207,22 +6245,22 @@
         <v>67</v>
       </c>
       <c r="B41" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C41" t="s">
         <v>38</v>
       </c>
       <c r="D41" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E41" t="s">
         <v>54</v>
       </c>
       <c r="F41" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="G41" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
@@ -6230,22 +6268,22 @@
         <v>67</v>
       </c>
       <c r="B42" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C42" t="s">
         <v>38</v>
       </c>
       <c r="D42" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E42" t="s">
         <v>54</v>
       </c>
       <c r="F42" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="G42" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
@@ -6253,13 +6291,13 @@
         <v>67</v>
       </c>
       <c r="B43" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C43" t="s">
         <v>39</v>
       </c>
       <c r="D43" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E43" t="s">
         <v>55</v>
@@ -6268,7 +6306,7 @@
         <v>62</v>
       </c>
       <c r="G43" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
@@ -6276,13 +6314,13 @@
         <v>67</v>
       </c>
       <c r="B44" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C44" t="s">
         <v>39</v>
       </c>
       <c r="D44" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E44" t="s">
         <v>55</v>
@@ -6299,22 +6337,22 @@
         <v>67</v>
       </c>
       <c r="B45" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C45" t="s">
         <v>39</v>
       </c>
       <c r="D45" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E45" t="s">
         <v>55</v>
       </c>
       <c r="F45" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="G45" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.25">
@@ -6322,22 +6360,22 @@
         <v>67</v>
       </c>
       <c r="B46" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C46" t="s">
         <v>39</v>
       </c>
       <c r="D46" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E46" t="s">
         <v>55</v>
       </c>
       <c r="F46" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="G46" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.25">
@@ -6345,13 +6383,13 @@
         <v>67</v>
       </c>
       <c r="B47" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C47" t="s">
         <v>40</v>
       </c>
       <c r="D47" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E47" t="s">
         <v>56</v>
@@ -6360,7 +6398,7 @@
         <v>62</v>
       </c>
       <c r="G47" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.25">
@@ -6368,13 +6406,13 @@
         <v>67</v>
       </c>
       <c r="B48" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C48" t="s">
         <v>40</v>
       </c>
       <c r="D48" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E48" t="s">
         <v>56</v>
@@ -6391,22 +6429,22 @@
         <v>67</v>
       </c>
       <c r="B49" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C49" t="s">
         <v>40</v>
       </c>
       <c r="D49" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E49" t="s">
         <v>56</v>
       </c>
       <c r="F49" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="G49" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.25">
@@ -6414,22 +6452,22 @@
         <v>67</v>
       </c>
       <c r="B50" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C50" t="s">
         <v>40</v>
       </c>
       <c r="D50" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E50" t="s">
         <v>56</v>
       </c>
       <c r="F50" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="G50" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.25">
@@ -6437,13 +6475,13 @@
         <v>67</v>
       </c>
       <c r="B52" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C52" t="s">
         <v>49</v>
       </c>
       <c r="D52" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E52" t="s">
         <v>27</v>
@@ -6460,13 +6498,13 @@
         <v>67</v>
       </c>
       <c r="B53" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C53" t="s">
         <v>50</v>
       </c>
       <c r="D53" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E53" t="s">
         <v>27</v>
@@ -6483,13 +6521,13 @@
         <v>67</v>
       </c>
       <c r="B54" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C54" t="s">
         <v>51</v>
       </c>
       <c r="D54" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E54" t="s">
         <v>27</v>
@@ -6506,13 +6544,13 @@
         <v>67</v>
       </c>
       <c r="B55" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C55" t="s">
         <v>52</v>
       </c>
       <c r="D55" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E55" t="s">
         <v>27</v>
@@ -6529,13 +6567,13 @@
         <v>67</v>
       </c>
       <c r="B56" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C56" t="s">
         <v>53</v>
       </c>
       <c r="D56" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E56" t="s">
         <v>27</v>
@@ -6552,13 +6590,13 @@
         <v>67</v>
       </c>
       <c r="B57" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C57" t="s">
         <v>54</v>
       </c>
       <c r="D57" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E57" t="s">
         <v>27</v>
@@ -6575,13 +6613,13 @@
         <v>67</v>
       </c>
       <c r="B58" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C58" t="s">
         <v>55</v>
       </c>
       <c r="D58" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E58" t="s">
         <v>27</v>
@@ -6598,13 +6636,13 @@
         <v>67</v>
       </c>
       <c r="B59" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C59" t="s">
         <v>56</v>
       </c>
       <c r="D59" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E59" t="s">
         <v>27</v>
@@ -6621,13 +6659,13 @@
         <v>67</v>
       </c>
       <c r="B61" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C61" t="s">
         <v>49</v>
       </c>
       <c r="D61" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E61" t="s">
         <v>28</v>
@@ -6636,7 +6674,7 @@
         <v>62</v>
       </c>
       <c r="G61" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.25">
@@ -6644,22 +6682,22 @@
         <v>67</v>
       </c>
       <c r="B62" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C62" t="s">
         <v>49</v>
       </c>
       <c r="D62" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E62" t="s">
         <v>28</v>
       </c>
       <c r="F62" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="G62" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.25">
@@ -6667,22 +6705,22 @@
         <v>67</v>
       </c>
       <c r="B63" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C63" t="s">
         <v>49</v>
       </c>
       <c r="D63" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E63" t="s">
         <v>28</v>
       </c>
       <c r="F63" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="G63" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.25">
@@ -6690,22 +6728,22 @@
         <v>67</v>
       </c>
       <c r="B64" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C64" t="s">
         <v>49</v>
       </c>
       <c r="D64" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E64" t="s">
         <v>28</v>
       </c>
       <c r="F64" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="G64" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.25">
@@ -6713,13 +6751,13 @@
         <v>67</v>
       </c>
       <c r="B65" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C65" t="s">
         <v>50</v>
       </c>
       <c r="D65" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E65" t="s">
         <v>28</v>
@@ -6728,7 +6766,7 @@
         <v>62</v>
       </c>
       <c r="G65" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.25">
@@ -6736,22 +6774,22 @@
         <v>67</v>
       </c>
       <c r="B66" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C66" t="s">
         <v>50</v>
       </c>
       <c r="D66" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E66" t="s">
         <v>28</v>
       </c>
       <c r="F66" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="G66" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.25">
@@ -6759,22 +6797,22 @@
         <v>67</v>
       </c>
       <c r="B67" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C67" t="s">
         <v>50</v>
       </c>
       <c r="D67" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E67" t="s">
         <v>28</v>
       </c>
       <c r="F67" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="G67" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.25">
@@ -6782,22 +6820,22 @@
         <v>67</v>
       </c>
       <c r="B68" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C68" t="s">
         <v>50</v>
       </c>
       <c r="D68" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E68" t="s">
         <v>28</v>
       </c>
       <c r="F68" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="G68" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.25">
@@ -6805,13 +6843,13 @@
         <v>67</v>
       </c>
       <c r="B69" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C69" t="s">
         <v>51</v>
       </c>
       <c r="D69" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E69" t="s">
         <v>28</v>
@@ -6820,7 +6858,7 @@
         <v>62</v>
       </c>
       <c r="G69" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.25">
@@ -6828,22 +6866,22 @@
         <v>67</v>
       </c>
       <c r="B70" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C70" t="s">
         <v>51</v>
       </c>
       <c r="D70" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E70" t="s">
         <v>28</v>
       </c>
       <c r="F70" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="G70" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.25">
@@ -6851,22 +6889,22 @@
         <v>67</v>
       </c>
       <c r="B71" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C71" t="s">
         <v>51</v>
       </c>
       <c r="D71" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E71" t="s">
         <v>28</v>
       </c>
       <c r="F71" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="G71" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.25">
@@ -6874,22 +6912,22 @@
         <v>67</v>
       </c>
       <c r="B72" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C72" t="s">
         <v>51</v>
       </c>
       <c r="D72" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E72" t="s">
         <v>28</v>
       </c>
       <c r="F72" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="G72" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.25">
@@ -6897,13 +6935,13 @@
         <v>67</v>
       </c>
       <c r="B73" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C73" t="s">
         <v>52</v>
       </c>
       <c r="D73" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E73" t="s">
         <v>28</v>
@@ -6912,7 +6950,7 @@
         <v>62</v>
       </c>
       <c r="G73" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.25">
@@ -6920,22 +6958,22 @@
         <v>67</v>
       </c>
       <c r="B74" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C74" t="s">
         <v>52</v>
       </c>
       <c r="D74" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E74" t="s">
         <v>28</v>
       </c>
       <c r="F74" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="G74" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.25">
@@ -6943,22 +6981,22 @@
         <v>67</v>
       </c>
       <c r="B75" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C75" t="s">
         <v>52</v>
       </c>
       <c r="D75" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E75" t="s">
         <v>28</v>
       </c>
       <c r="F75" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="G75" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.25">
@@ -6966,22 +7004,22 @@
         <v>67</v>
       </c>
       <c r="B76" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C76" t="s">
         <v>52</v>
       </c>
       <c r="D76" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E76" t="s">
         <v>28</v>
       </c>
       <c r="F76" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="G76" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.25">
@@ -6989,13 +7027,13 @@
         <v>67</v>
       </c>
       <c r="B77" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C77" t="s">
         <v>53</v>
       </c>
       <c r="D77" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E77" t="s">
         <v>28</v>
@@ -7004,7 +7042,7 @@
         <v>62</v>
       </c>
       <c r="G77" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.25">
@@ -7012,22 +7050,22 @@
         <v>67</v>
       </c>
       <c r="B78" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C78" t="s">
         <v>53</v>
       </c>
       <c r="D78" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E78" t="s">
         <v>28</v>
       </c>
       <c r="F78" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="G78" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.25">
@@ -7035,22 +7073,22 @@
         <v>67</v>
       </c>
       <c r="B79" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C79" t="s">
         <v>53</v>
       </c>
       <c r="D79" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E79" t="s">
         <v>28</v>
       </c>
       <c r="F79" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="G79" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.25">
@@ -7058,22 +7096,22 @@
         <v>67</v>
       </c>
       <c r="B80" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C80" t="s">
         <v>53</v>
       </c>
       <c r="D80" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E80" t="s">
         <v>28</v>
       </c>
       <c r="F80" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="G80" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.25">
@@ -7081,13 +7119,13 @@
         <v>67</v>
       </c>
       <c r="B81" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C81" t="s">
         <v>54</v>
       </c>
       <c r="D81" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E81" t="s">
         <v>28</v>
@@ -7096,7 +7134,7 @@
         <v>62</v>
       </c>
       <c r="G81" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.25">
@@ -7104,22 +7142,22 @@
         <v>67</v>
       </c>
       <c r="B82" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C82" t="s">
         <v>54</v>
       </c>
       <c r="D82" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E82" t="s">
         <v>28</v>
       </c>
       <c r="F82" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="G82" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.25">
@@ -7127,22 +7165,22 @@
         <v>67</v>
       </c>
       <c r="B83" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C83" t="s">
         <v>54</v>
       </c>
       <c r="D83" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E83" t="s">
         <v>28</v>
       </c>
       <c r="F83" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="G83" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.25">
@@ -7150,22 +7188,22 @@
         <v>67</v>
       </c>
       <c r="B84" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C84" t="s">
         <v>54</v>
       </c>
       <c r="D84" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E84" t="s">
         <v>28</v>
       </c>
       <c r="F84" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="G84" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.25">
@@ -7173,13 +7211,13 @@
         <v>67</v>
       </c>
       <c r="B85" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C85" t="s">
         <v>55</v>
       </c>
       <c r="D85" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E85" t="s">
         <v>28</v>
@@ -7188,7 +7226,7 @@
         <v>62</v>
       </c>
       <c r="G85" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.25">
@@ -7196,22 +7234,22 @@
         <v>67</v>
       </c>
       <c r="B86" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C86" t="s">
         <v>55</v>
       </c>
       <c r="D86" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E86" t="s">
         <v>28</v>
       </c>
       <c r="F86" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="G86" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.25">
@@ -7219,22 +7257,22 @@
         <v>67</v>
       </c>
       <c r="B87" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C87" t="s">
         <v>55</v>
       </c>
       <c r="D87" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E87" t="s">
         <v>28</v>
       </c>
       <c r="F87" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="G87" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.25">
@@ -7242,22 +7280,22 @@
         <v>67</v>
       </c>
       <c r="B88" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C88" t="s">
         <v>55</v>
       </c>
       <c r="D88" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E88" t="s">
         <v>28</v>
       </c>
       <c r="F88" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="G88" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.25">
@@ -7265,13 +7303,13 @@
         <v>67</v>
       </c>
       <c r="B89" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C89" t="s">
         <v>56</v>
       </c>
       <c r="D89" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E89" t="s">
         <v>28</v>
@@ -7280,7 +7318,7 @@
         <v>62</v>
       </c>
       <c r="G89" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.25">
@@ -7288,22 +7326,22 @@
         <v>67</v>
       </c>
       <c r="B90" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C90" t="s">
         <v>56</v>
       </c>
       <c r="D90" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E90" t="s">
         <v>28</v>
       </c>
       <c r="F90" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="G90" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.25">
@@ -7311,22 +7349,22 @@
         <v>67</v>
       </c>
       <c r="B91" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C91" t="s">
         <v>56</v>
       </c>
       <c r="D91" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E91" t="s">
         <v>28</v>
       </c>
       <c r="F91" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="G91" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.25">
@@ -7334,22 +7372,22 @@
         <v>67</v>
       </c>
       <c r="B92" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C92" t="s">
         <v>56</v>
       </c>
       <c r="D92" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E92" t="s">
         <v>28</v>
       </c>
       <c r="F92" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="G92" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.25">
@@ -7357,22 +7395,22 @@
         <v>67</v>
       </c>
       <c r="B94" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C94" t="s">
         <v>49</v>
       </c>
       <c r="D94" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E94" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="F94" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="G94" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.25">
@@ -7380,22 +7418,22 @@
         <v>67</v>
       </c>
       <c r="B95" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C95" t="s">
         <v>49</v>
       </c>
       <c r="D95" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E95" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="F95" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="G95" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.25">
@@ -7403,22 +7441,22 @@
         <v>67</v>
       </c>
       <c r="B96" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C96" t="s">
         <v>49</v>
       </c>
       <c r="D96" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E96" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="F96" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="G96" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.25">
@@ -7426,22 +7464,22 @@
         <v>67</v>
       </c>
       <c r="B97" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C97" t="s">
         <v>50</v>
       </c>
       <c r="D97" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E97" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="F97" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="G97" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="98" spans="1:7" x14ac:dyDescent="0.25">
@@ -7449,22 +7487,22 @@
         <v>67</v>
       </c>
       <c r="B98" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C98" t="s">
         <v>50</v>
       </c>
       <c r="D98" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E98" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="F98" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="G98" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.25">
@@ -7472,22 +7510,22 @@
         <v>67</v>
       </c>
       <c r="B99" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C99" t="s">
         <v>50</v>
       </c>
       <c r="D99" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E99" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="F99" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="G99" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="100" spans="1:7" x14ac:dyDescent="0.25">
@@ -7495,22 +7533,22 @@
         <v>67</v>
       </c>
       <c r="B100" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C100" t="s">
         <v>51</v>
       </c>
       <c r="D100" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E100" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="F100" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="G100" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.25">
@@ -7518,22 +7556,22 @@
         <v>67</v>
       </c>
       <c r="B101" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C101" t="s">
         <v>51</v>
       </c>
       <c r="D101" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E101" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="F101" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="G101" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="102" spans="1:7" x14ac:dyDescent="0.25">
@@ -7541,22 +7579,22 @@
         <v>67</v>
       </c>
       <c r="B102" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C102" t="s">
         <v>51</v>
       </c>
       <c r="D102" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E102" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="F102" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="G102" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="103" spans="1:7" x14ac:dyDescent="0.25">
@@ -7564,22 +7602,22 @@
         <v>67</v>
       </c>
       <c r="B103" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C103" t="s">
         <v>52</v>
       </c>
       <c r="D103" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E103" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="F103" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="G103" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="104" spans="1:7" x14ac:dyDescent="0.25">
@@ -7587,22 +7625,22 @@
         <v>67</v>
       </c>
       <c r="B104" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C104" t="s">
         <v>52</v>
       </c>
       <c r="D104" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E104" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="F104" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="G104" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.25">
@@ -7610,22 +7648,22 @@
         <v>67</v>
       </c>
       <c r="B105" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C105" t="s">
         <v>52</v>
       </c>
       <c r="D105" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E105" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="F105" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="G105" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="106" spans="1:7" x14ac:dyDescent="0.25">
@@ -7633,22 +7671,22 @@
         <v>67</v>
       </c>
       <c r="B106" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C106" t="s">
         <v>53</v>
       </c>
       <c r="D106" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E106" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="F106" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="G106" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="107" spans="1:7" x14ac:dyDescent="0.25">
@@ -7656,22 +7694,22 @@
         <v>67</v>
       </c>
       <c r="B107" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C107" t="s">
         <v>53</v>
       </c>
       <c r="D107" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E107" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="F107" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="G107" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="108" spans="1:7" x14ac:dyDescent="0.25">
@@ -7679,22 +7717,22 @@
         <v>67</v>
       </c>
       <c r="B108" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C108" t="s">
         <v>53</v>
       </c>
       <c r="D108" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E108" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="F108" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="G108" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="109" spans="1:7" x14ac:dyDescent="0.25">
@@ -7702,22 +7740,22 @@
         <v>67</v>
       </c>
       <c r="B109" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C109" t="s">
         <v>54</v>
       </c>
       <c r="D109" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E109" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="F109" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="G109" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="110" spans="1:7" x14ac:dyDescent="0.25">
@@ -7725,22 +7763,22 @@
         <v>67</v>
       </c>
       <c r="B110" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C110" t="s">
         <v>54</v>
       </c>
       <c r="D110" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E110" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="F110" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="G110" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="111" spans="1:7" x14ac:dyDescent="0.25">
@@ -7748,22 +7786,22 @@
         <v>67</v>
       </c>
       <c r="B111" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C111" t="s">
         <v>54</v>
       </c>
       <c r="D111" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E111" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="F111" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="G111" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="112" spans="1:7" x14ac:dyDescent="0.25">
@@ -7771,22 +7809,22 @@
         <v>67</v>
       </c>
       <c r="B112" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C112" t="s">
         <v>55</v>
       </c>
       <c r="D112" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E112" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F112" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="G112" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="113" spans="1:7" x14ac:dyDescent="0.25">
@@ -7794,22 +7832,22 @@
         <v>67</v>
       </c>
       <c r="B113" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C113" t="s">
         <v>55</v>
       </c>
       <c r="D113" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E113" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F113" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="G113" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="114" spans="1:7" x14ac:dyDescent="0.25">
@@ -7817,22 +7855,22 @@
         <v>67</v>
       </c>
       <c r="B114" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C114" t="s">
         <v>55</v>
       </c>
       <c r="D114" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E114" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F114" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="G114" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="115" spans="1:7" x14ac:dyDescent="0.25">
@@ -7840,22 +7878,22 @@
         <v>67</v>
       </c>
       <c r="B115" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C115" t="s">
         <v>56</v>
       </c>
       <c r="D115" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E115" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="F115" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="G115" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="116" spans="1:7" x14ac:dyDescent="0.25">
@@ -7863,22 +7901,22 @@
         <v>67</v>
       </c>
       <c r="B116" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C116" t="s">
         <v>56</v>
       </c>
       <c r="D116" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E116" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="F116" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="G116" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="117" spans="1:7" x14ac:dyDescent="0.25">
@@ -7886,22 +7924,22 @@
         <v>67</v>
       </c>
       <c r="B117" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C117" t="s">
         <v>56</v>
       </c>
       <c r="D117" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E117" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="F117" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="G117" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="119" spans="1:7" x14ac:dyDescent="0.25">
@@ -7909,22 +7947,22 @@
         <v>67</v>
       </c>
       <c r="B119" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C119" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D119" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E119" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="F119" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="G119" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="120" spans="1:7" x14ac:dyDescent="0.25">
@@ -7932,22 +7970,22 @@
         <v>67</v>
       </c>
       <c r="B120" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C120" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="D120" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E120" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="F120" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="G120" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="121" spans="1:7" x14ac:dyDescent="0.25">
@@ -7955,22 +7993,22 @@
         <v>67</v>
       </c>
       <c r="B121" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C121" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D121" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E121" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="F121" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="G121" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="122" spans="1:7" x14ac:dyDescent="0.25">
@@ -7978,22 +8016,22 @@
         <v>67</v>
       </c>
       <c r="B122" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C122" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D122" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E122" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="F122" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="G122" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="123" spans="1:7" x14ac:dyDescent="0.25">
@@ -8001,22 +8039,22 @@
         <v>67</v>
       </c>
       <c r="B123" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C123" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="D123" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E123" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="F123" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="G123" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="124" spans="1:7" x14ac:dyDescent="0.25">
@@ -8024,22 +8062,22 @@
         <v>67</v>
       </c>
       <c r="B124" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C124" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D124" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E124" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="F124" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="G124" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="125" spans="1:7" x14ac:dyDescent="0.25">
@@ -8047,22 +8085,22 @@
         <v>67</v>
       </c>
       <c r="B125" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C125" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="D125" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E125" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="F125" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="G125" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="126" spans="1:7" x14ac:dyDescent="0.25">
@@ -8070,22 +8108,22 @@
         <v>67</v>
       </c>
       <c r="B126" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C126" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="D126" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E126" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="F126" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="G126" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="128" spans="1:7" x14ac:dyDescent="0.25">
@@ -8093,22 +8131,22 @@
         <v>67</v>
       </c>
       <c r="B128" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C128" t="s">
         <v>28</v>
       </c>
       <c r="D128" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E128" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="F128" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="G128" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="129" spans="1:7" x14ac:dyDescent="0.25">
@@ -8116,22 +8154,22 @@
         <v>67</v>
       </c>
       <c r="B129" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C129" t="s">
         <v>28</v>
       </c>
       <c r="D129" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E129" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="F129" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="G129" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
     </row>
     <row r="130" spans="1:7" x14ac:dyDescent="0.25">
@@ -8139,22 +8177,22 @@
         <v>67</v>
       </c>
       <c r="B130" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C130" t="s">
         <v>27</v>
       </c>
       <c r="D130" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E130" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="F130" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="G130" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
   </sheetData>
